--- a/Violencia Valle del Cauca Indices con Página con todo junto.xlsx
+++ b/Violencia Valle del Cauca Indices con Página con todo junto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Camilo Gómez\Desktop\universidad\Analítica Computacional\Módulo 1\Proyecto 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26E4363-5318-40FB-A215-F387D3CC02F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A55C3270-D1D7-4719-AF44-BE75A0AE92CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4032" yWindow="3144" windowWidth="17280" windowHeight="8880" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Habitantes" sheetId="49" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="107">
   <si>
     <t>Norte</t>
   </si>
@@ -90,16 +90,7 @@
     <t>CALI</t>
   </si>
   <si>
-    <t>ALCALÁ</t>
-  </si>
-  <si>
-    <t>ANDALUCÍA</t>
-  </si>
-  <si>
     <t>ARGELIA</t>
-  </si>
-  <si>
-    <t>BOLÍVAR</t>
   </si>
   <si>
     <t>CAICEDONIA</t>
@@ -117,9 +108,6 @@
     <t>DAGUA</t>
   </si>
   <si>
-    <t>EL ÁGUILA</t>
-  </si>
-  <si>
     <t>EL CAIRO</t>
   </si>
   <si>
@@ -135,16 +123,7 @@
     <t>GINEBRA</t>
   </si>
   <si>
-    <t>GUACARÍ</t>
-  </si>
-  <si>
-    <t>JAMUNDÍ</t>
-  </si>
-  <si>
     <t>LA CUMBRE</t>
-  </si>
-  <si>
-    <t>LA UNIÓN</t>
   </si>
   <si>
     <t>OBANDO</t>
@@ -157,9 +136,6 @@
   </si>
   <si>
     <t>RESTREPO</t>
-  </si>
-  <si>
-    <t>RIOFRÍO</t>
   </si>
   <si>
     <t>ROLDANILLO</t>
@@ -175,9 +151,6 @@
   </si>
   <si>
     <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TULUÁ</t>
   </si>
   <si>
     <t>ULLOA</t>
@@ -415,6 +388,9 @@
   </si>
   <si>
     <t>cole_mcpio_ubicacion</t>
+  </si>
+  <si>
+    <t>CALIMA EL DARIEN</t>
   </si>
 </sst>
 </file>
@@ -904,10 +880,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -923,7 +899,7 @@
     </row>
     <row r="3" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>0</v>
@@ -934,7 +910,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1</v>
@@ -945,7 +921,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>0</v>
@@ -956,7 +932,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>0</v>
@@ -967,7 +943,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>0</v>
@@ -978,7 +954,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
@@ -989,7 +965,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>1</v>
@@ -1000,7 +976,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1</v>
@@ -1011,7 +987,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>3</v>
@@ -1022,7 +998,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>1</v>
@@ -1033,7 +1009,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -1044,7 +1020,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>0</v>
@@ -1055,7 +1031,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -1066,7 +1042,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>0</v>
@@ -1077,7 +1053,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>0</v>
@@ -1088,7 +1064,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
@@ -1099,7 +1075,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>0</v>
@@ -1110,7 +1086,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>4</v>
@@ -1121,7 +1097,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -1132,7 +1108,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>1</v>
@@ -1143,7 +1119,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>4</v>
@@ -1154,7 +1130,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>4</v>
@@ -1165,7 +1141,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>0</v>
@@ -1176,7 +1152,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>0</v>
@@ -1187,7 +1163,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>0</v>
@@ -1198,7 +1174,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>4</v>
@@ -1209,7 +1185,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>4</v>
@@ -1220,7 +1196,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>1</v>
@@ -1231,7 +1207,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>1</v>
@@ -1242,7 +1218,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>0</v>
@@ -1253,7 +1229,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>1</v>
@@ -1264,7 +1240,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>3</v>
@@ -1275,7 +1251,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>0</v>
@@ -1286,7 +1262,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>1</v>
@@ -1297,7 +1273,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1</v>
@@ -1308,7 +1284,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>0</v>
@@ -1319,7 +1295,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>0</v>
@@ -1330,7 +1306,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>4</v>
@@ -1341,7 +1317,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>1</v>
@@ -1352,7 +1328,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>4</v>
@@ -1363,7 +1339,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>0</v>
@@ -1384,148 +1360,148 @@
   <sheetData>
     <row r="1" spans="1:49" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Z1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AC1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="AF1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AI1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AL1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AN1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AO1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AR1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AS1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AT1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AU1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AV1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AW1" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="AO1" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AQ1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AR1" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AS1" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="AT1" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AU1" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AV1" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AW1" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:49" x14ac:dyDescent="0.3">
@@ -1687,7 +1663,7 @@
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B43" si="0">AVERAGE(C3:G3)</f>
@@ -1844,7 +1820,7 @@
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
@@ -2001,7 +1977,7 @@
     </row>
     <row r="5" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -2158,7 +2134,7 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
@@ -2315,7 +2291,7 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -2472,7 +2448,7 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
@@ -2629,7 +2605,7 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -2786,7 +2762,7 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -2943,7 +2919,7 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -3100,7 +3076,7 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -3257,7 +3233,7 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -3414,7 +3390,7 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -3571,7 +3547,7 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -3728,7 +3704,7 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -3885,7 +3861,7 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -4042,7 +4018,7 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -4199,7 +4175,7 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
@@ -4356,7 +4332,7 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -4513,7 +4489,7 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -4670,7 +4646,7 @@
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
@@ -4827,7 +4803,7 @@
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -4984,7 +4960,7 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
@@ -5141,7 +5117,7 @@
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -5298,7 +5274,7 @@
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
@@ -5455,7 +5431,7 @@
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
@@ -5612,7 +5588,7 @@
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
@@ -5769,7 +5745,7 @@
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
@@ -5926,7 +5902,7 @@
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
@@ -6083,7 +6059,7 @@
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
@@ -6240,7 +6216,7 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
@@ -6397,7 +6373,7 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
@@ -6554,7 +6530,7 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
@@ -6711,7 +6687,7 @@
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
@@ -6868,7 +6844,7 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
@@ -7025,7 +7001,7 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
@@ -7182,7 +7158,7 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
@@ -7339,7 +7315,7 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
@@ -7496,7 +7472,7 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
@@ -7653,7 +7629,7 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
@@ -7810,7 +7786,7 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
@@ -7967,7 +7943,7 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
@@ -8134,124 +8110,124 @@
   <sheetData>
     <row r="1" spans="1:41" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="N1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="S1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="X1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="S1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="T1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="X1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AC1" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AO1" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="AH1" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK1" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL1" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM1" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN1" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO1" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
@@ -8381,7 +8357,7 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>77.590463426677005</v>
@@ -8506,7 +8482,7 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>48.081125972550048</v>
@@ -8631,7 +8607,7 @@
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>74.145896309815768</v>
@@ -8756,7 +8732,7 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>38.153376573826783</v>
@@ -8881,7 +8857,7 @@
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>50.279680724027401</v>
@@ -9006,7 +8982,7 @@
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>35.155173669725059</v>
@@ -9131,7 +9107,7 @@
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>45.954474433994058</v>
@@ -9256,7 +9232,7 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>64.589052155659616</v>
@@ -9381,7 +9357,7 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>58.866304234911183</v>
@@ -9506,7 +9482,7 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>32.441200324412002</v>
@@ -9631,7 +9607,7 @@
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>80.701791160533674</v>
@@ -9756,7 +9732,7 @@
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>28.052306762763799</v>
@@ -9881,7 +9857,7 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>22.163567125385345</v>
@@ -10006,7 +9982,7 @@
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>80.738177623990779</v>
@@ -10131,7 +10107,7 @@
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>151.79113539769278</v>
@@ -10256,7 +10232,7 @@
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>44.943043335465248</v>
@@ -10381,7 +10357,7 @@
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>183.40210912425493</v>
@@ -10506,7 +10482,7 @@
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>52.820801172281001</v>
@@ -10631,7 +10607,7 @@
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>4.284490145672665</v>
@@ -10756,7 +10732,7 @@
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>61.764705882352935</v>
@@ -10881,7 +10857,7 @@
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>60.255198487712661</v>
@@ -11006,7 +10982,7 @@
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>23.929169657812874</v>
@@ -11131,7 +11107,7 @@
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>108.77966392809093</v>
@@ -11256,7 +11232,7 @@
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>24.966711051930758</v>
@@ -11381,7 +11357,7 @@
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>49.208562289838433</v>
@@ -11506,7 +11482,7 @@
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>31.214639666003354</v>
@@ -11631,7 +11607,7 @@
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>55.361902809103952</v>
@@ -11756,7 +11732,7 @@
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>32.266391326794015</v>
@@ -11881,7 +11857,7 @@
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>31.934597943411895</v>
@@ -12006,7 +11982,7 @@
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>61.748281786941583</v>
@@ -12131,7 +12107,7 @@
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>74.626865671641795</v>
@@ -12256,7 +12232,7 @@
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>35.997120230381569</v>
@@ -12381,7 +12357,7 @@
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>102.95126973232671</v>
@@ -12506,7 +12482,7 @@
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>57.232049947970857</v>
@@ -12631,7 +12607,7 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>66.785798090287173</v>
@@ -12756,7 +12732,7 @@
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>18.351991191044231</v>
@@ -12881,7 +12857,7 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>28.421202216853771</v>
@@ -13006,7 +12982,7 @@
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>15.330369461904032</v>
@@ -13131,7 +13107,7 @@
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>54.878048780487802</v>
@@ -13256,7 +13232,7 @@
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>66.383192493316827</v>
@@ -13381,7 +13357,7 @@
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>58.220773171867719</v>
@@ -13562,7 +13538,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <f>'Todos los Datos (2)'!B3*Hoja1!$K$17+'Todos los Datos (2)'!G3*Hoja1!$K$18+'Todos los Datos (2)'!L3*Hoja1!$K$19+'Todos los Datos (2)'!Q3*Hoja1!$K$20+'Todos los Datos (2)'!V3*Hoja1!$K$21+'Todos los Datos (2)'!AA3*Hoja1!$K$22+'Todos los Datos (2)'!AF3*Hoja1!$K$23+'Todos los Datos (2)'!AK3*Hoja1!$K$24</f>
@@ -13587,7 +13563,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <f>'Todos los Datos (2)'!B4*Hoja1!$K$17+'Todos los Datos (2)'!G4*Hoja1!$K$18+'Todos los Datos (2)'!L4*Hoja1!$K$19+'Todos los Datos (2)'!Q4*Hoja1!$K$20+'Todos los Datos (2)'!V4*Hoja1!$K$21+'Todos los Datos (2)'!AA4*Hoja1!$K$22+'Todos los Datos (2)'!AF4*Hoja1!$K$23+'Todos los Datos (2)'!AK4*Hoja1!$K$24</f>
@@ -13612,7 +13588,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <f>'Todos los Datos (2)'!B5*Hoja1!$K$17+'Todos los Datos (2)'!G5*Hoja1!$K$18+'Todos los Datos (2)'!L5*Hoja1!$K$19+'Todos los Datos (2)'!Q5*Hoja1!$K$20+'Todos los Datos (2)'!V5*Hoja1!$K$21+'Todos los Datos (2)'!AA5*Hoja1!$K$22+'Todos los Datos (2)'!AF5*Hoja1!$K$23+'Todos los Datos (2)'!AK5*Hoja1!$K$24</f>
@@ -13637,7 +13613,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <f>'Todos los Datos (2)'!B6*Hoja1!$K$17+'Todos los Datos (2)'!G6*Hoja1!$K$18+'Todos los Datos (2)'!L6*Hoja1!$K$19+'Todos los Datos (2)'!Q6*Hoja1!$K$20+'Todos los Datos (2)'!V6*Hoja1!$K$21+'Todos los Datos (2)'!AA6*Hoja1!$K$22+'Todos los Datos (2)'!AF6*Hoja1!$K$23+'Todos los Datos (2)'!AK6*Hoja1!$K$24</f>
@@ -13662,7 +13638,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <f>'Todos los Datos (2)'!B7*Hoja1!$K$17+'Todos los Datos (2)'!G7*Hoja1!$K$18+'Todos los Datos (2)'!L7*Hoja1!$K$19+'Todos los Datos (2)'!Q7*Hoja1!$K$20+'Todos los Datos (2)'!V7*Hoja1!$K$21+'Todos los Datos (2)'!AA7*Hoja1!$K$22+'Todos los Datos (2)'!AF7*Hoja1!$K$23+'Todos los Datos (2)'!AK7*Hoja1!$K$24</f>
@@ -13687,7 +13663,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>'Todos los Datos (2)'!B8*Hoja1!$K$17+'Todos los Datos (2)'!G8*Hoja1!$K$18+'Todos los Datos (2)'!L8*Hoja1!$K$19+'Todos los Datos (2)'!Q8*Hoja1!$K$20+'Todos los Datos (2)'!V8*Hoja1!$K$21+'Todos los Datos (2)'!AA8*Hoja1!$K$22+'Todos los Datos (2)'!AF8*Hoja1!$K$23+'Todos los Datos (2)'!AK8*Hoja1!$K$24</f>
@@ -13712,7 +13688,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <f>'Todos los Datos (2)'!B9*Hoja1!$K$17+'Todos los Datos (2)'!G9*Hoja1!$K$18+'Todos los Datos (2)'!L9*Hoja1!$K$19+'Todos los Datos (2)'!Q9*Hoja1!$K$20+'Todos los Datos (2)'!V9*Hoja1!$K$21+'Todos los Datos (2)'!AA9*Hoja1!$K$22+'Todos los Datos (2)'!AF9*Hoja1!$K$23+'Todos los Datos (2)'!AK9*Hoja1!$K$24</f>
@@ -13737,7 +13713,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <f>'Todos los Datos (2)'!B10*Hoja1!$K$17+'Todos los Datos (2)'!G10*Hoja1!$K$18+'Todos los Datos (2)'!L10*Hoja1!$K$19+'Todos los Datos (2)'!Q10*Hoja1!$K$20+'Todos los Datos (2)'!V10*Hoja1!$K$21+'Todos los Datos (2)'!AA10*Hoja1!$K$22+'Todos los Datos (2)'!AF10*Hoja1!$K$23+'Todos los Datos (2)'!AK10*Hoja1!$K$24</f>
@@ -13762,7 +13738,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <f>'Todos los Datos (2)'!B11*Hoja1!$K$17+'Todos los Datos (2)'!G11*Hoja1!$K$18+'Todos los Datos (2)'!L11*Hoja1!$K$19+'Todos los Datos (2)'!Q11*Hoja1!$K$20+'Todos los Datos (2)'!V11*Hoja1!$K$21+'Todos los Datos (2)'!AA11*Hoja1!$K$22+'Todos los Datos (2)'!AF11*Hoja1!$K$23+'Todos los Datos (2)'!AK11*Hoja1!$K$24</f>
@@ -13787,7 +13763,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <f>'Todos los Datos (2)'!B12*Hoja1!$K$17+'Todos los Datos (2)'!G12*Hoja1!$K$18+'Todos los Datos (2)'!L12*Hoja1!$K$19+'Todos los Datos (2)'!Q12*Hoja1!$K$20+'Todos los Datos (2)'!V12*Hoja1!$K$21+'Todos los Datos (2)'!AA12*Hoja1!$K$22+'Todos los Datos (2)'!AF12*Hoja1!$K$23+'Todos los Datos (2)'!AK12*Hoja1!$K$24</f>
@@ -13812,7 +13788,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <f>'Todos los Datos (2)'!B13*Hoja1!$K$17+'Todos los Datos (2)'!G13*Hoja1!$K$18+'Todos los Datos (2)'!L13*Hoja1!$K$19+'Todos los Datos (2)'!Q13*Hoja1!$K$20+'Todos los Datos (2)'!V13*Hoja1!$K$21+'Todos los Datos (2)'!AA13*Hoja1!$K$22+'Todos los Datos (2)'!AF13*Hoja1!$K$23+'Todos los Datos (2)'!AK13*Hoja1!$K$24</f>
@@ -13837,7 +13813,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <f>'Todos los Datos (2)'!B14*Hoja1!$K$17+'Todos los Datos (2)'!G14*Hoja1!$K$18+'Todos los Datos (2)'!L14*Hoja1!$K$19+'Todos los Datos (2)'!Q14*Hoja1!$K$20+'Todos los Datos (2)'!V14*Hoja1!$K$21+'Todos los Datos (2)'!AA14*Hoja1!$K$22+'Todos los Datos (2)'!AF14*Hoja1!$K$23+'Todos los Datos (2)'!AK14*Hoja1!$K$24</f>
@@ -13863,7 +13839,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <f>'Todos los Datos (2)'!B15*Hoja1!$K$17+'Todos los Datos (2)'!G15*Hoja1!$K$18+'Todos los Datos (2)'!L15*Hoja1!$K$19+'Todos los Datos (2)'!Q15*Hoja1!$K$20+'Todos los Datos (2)'!V15*Hoja1!$K$21+'Todos los Datos (2)'!AA15*Hoja1!$K$22+'Todos los Datos (2)'!AF15*Hoja1!$K$23+'Todos los Datos (2)'!AK15*Hoja1!$K$24</f>
@@ -13913,7 +13889,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <f>'Todos los Datos (2)'!B16*Hoja1!$K$17+'Todos los Datos (2)'!G16*Hoja1!$K$18+'Todos los Datos (2)'!L16*Hoja1!$K$19+'Todos los Datos (2)'!Q16*Hoja1!$K$20+'Todos los Datos (2)'!V16*Hoja1!$K$21+'Todos los Datos (2)'!AA16*Hoja1!$K$22+'Todos los Datos (2)'!AF16*Hoja1!$K$23+'Todos los Datos (2)'!AK16*Hoja1!$K$24</f>
@@ -13938,7 +13914,7 @@
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <f>'Todos los Datos (2)'!B17*Hoja1!$K$17+'Todos los Datos (2)'!G17*Hoja1!$K$18+'Todos los Datos (2)'!L17*Hoja1!$K$19+'Todos los Datos (2)'!Q17*Hoja1!$K$20+'Todos los Datos (2)'!V17*Hoja1!$K$21+'Todos los Datos (2)'!AA17*Hoja1!$K$22+'Todos los Datos (2)'!AF17*Hoja1!$K$23+'Todos los Datos (2)'!AK17*Hoja1!$K$24</f>
@@ -13961,7 +13937,7 @@
         <v>81.967213114754102</v>
       </c>
       <c r="J17" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="K17" s="9">
         <v>0.25</v>
@@ -14114,7 +14090,7 @@
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <f>'Todos los Datos (2)'!B18*Hoja1!$K$17+'Todos los Datos (2)'!G18*Hoja1!$K$18+'Todos los Datos (2)'!L18*Hoja1!$K$19+'Todos los Datos (2)'!Q18*Hoja1!$K$20+'Todos los Datos (2)'!V18*Hoja1!$K$21+'Todos los Datos (2)'!AA18*Hoja1!$K$22+'Todos los Datos (2)'!AF18*Hoja1!$K$23+'Todos los Datos (2)'!AK18*Hoja1!$K$24</f>
@@ -14137,7 +14113,7 @@
         <v>147.01560906466614</v>
       </c>
       <c r="J18" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="K18" s="9">
         <v>0.05</v>
@@ -14289,7 +14265,7 @@
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <f>'Todos los Datos (2)'!B19*Hoja1!$K$17+'Todos los Datos (2)'!G19*Hoja1!$K$18+'Todos los Datos (2)'!L19*Hoja1!$K$19+'Todos los Datos (2)'!Q19*Hoja1!$K$20+'Todos los Datos (2)'!V19*Hoja1!$K$21+'Todos los Datos (2)'!AA19*Hoja1!$K$22+'Todos los Datos (2)'!AF19*Hoja1!$K$23+'Todos los Datos (2)'!AK19*Hoja1!$K$24</f>
@@ -14312,7 +14288,7 @@
         <v>138.69784502521779</v>
       </c>
       <c r="J19" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K19" s="9">
         <v>0.3</v>
@@ -14464,7 +14440,7 @@
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <f>'Todos los Datos (2)'!B20*Hoja1!$K$17+'Todos los Datos (2)'!G20*Hoja1!$K$18+'Todos los Datos (2)'!L20*Hoja1!$K$19+'Todos los Datos (2)'!Q20*Hoja1!$K$20+'Todos los Datos (2)'!V20*Hoja1!$K$21+'Todos los Datos (2)'!AA20*Hoja1!$K$22+'Todos los Datos (2)'!AF20*Hoja1!$K$23+'Todos los Datos (2)'!AK20*Hoja1!$K$24</f>
@@ -14487,7 +14463,7 @@
         <v>136.90810884492834</v>
       </c>
       <c r="J20" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="K20" s="9">
         <v>0.15</v>
@@ -14639,7 +14615,7 @@
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <f>'Todos los Datos (2)'!B21*Hoja1!$K$17+'Todos los Datos (2)'!G21*Hoja1!$K$18+'Todos los Datos (2)'!L21*Hoja1!$K$19+'Todos los Datos (2)'!Q21*Hoja1!$K$20+'Todos los Datos (2)'!V21*Hoja1!$K$21+'Todos los Datos (2)'!AA21*Hoja1!$K$22+'Todos los Datos (2)'!AF21*Hoja1!$K$23+'Todos los Datos (2)'!AK21*Hoja1!$K$24</f>
@@ -14662,7 +14638,7 @@
         <v>104.54155955441303</v>
       </c>
       <c r="J21" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K21" s="9">
         <v>0.05</v>
@@ -14814,7 +14790,7 @@
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <f>'Todos los Datos (2)'!B22*Hoja1!$K$17+'Todos los Datos (2)'!G22*Hoja1!$K$18+'Todos los Datos (2)'!L22*Hoja1!$K$19+'Todos los Datos (2)'!Q22*Hoja1!$K$20+'Todos los Datos (2)'!V22*Hoja1!$K$21+'Todos los Datos (2)'!AA22*Hoja1!$K$22+'Todos los Datos (2)'!AF22*Hoja1!$K$23+'Todos los Datos (2)'!AK22*Hoja1!$K$24</f>
@@ -14837,7 +14813,7 @@
         <v>186.47058823529409</v>
       </c>
       <c r="J22" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K22" s="9">
         <v>0.05</v>
@@ -14989,7 +14965,7 @@
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <f>'Todos los Datos (2)'!B23*Hoja1!$K$17+'Todos los Datos (2)'!G23*Hoja1!$K$18+'Todos los Datos (2)'!L23*Hoja1!$K$19+'Todos los Datos (2)'!Q23*Hoja1!$K$20+'Todos los Datos (2)'!V23*Hoja1!$K$21+'Todos los Datos (2)'!AA23*Hoja1!$K$22+'Todos los Datos (2)'!AF23*Hoja1!$K$23+'Todos los Datos (2)'!AK23*Hoja1!$K$24</f>
@@ -15012,7 +14988,7 @@
         <v>163.81143667296789</v>
       </c>
       <c r="J23" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="K23" s="9">
         <v>0.1</v>
@@ -15164,7 +15140,7 @@
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <f>'Todos los Datos (2)'!B24*Hoja1!$K$17+'Todos los Datos (2)'!G24*Hoja1!$K$18+'Todos los Datos (2)'!L24*Hoja1!$K$19+'Todos los Datos (2)'!Q24*Hoja1!$K$20+'Todos los Datos (2)'!V24*Hoja1!$K$21+'Todos los Datos (2)'!AA24*Hoja1!$K$22+'Todos los Datos (2)'!AF24*Hoja1!$K$23+'Todos los Datos (2)'!AK24*Hoja1!$K$24</f>
@@ -15187,7 +15163,7 @@
         <v>119.04761904761907</v>
       </c>
       <c r="J24" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="K24" s="9">
         <v>0.05</v>
@@ -15339,7 +15315,7 @@
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <f>'Todos los Datos (2)'!B25*Hoja1!$K$17+'Todos los Datos (2)'!G25*Hoja1!$K$18+'Todos los Datos (2)'!L25*Hoja1!$K$19+'Todos los Datos (2)'!Q25*Hoja1!$K$20+'Todos los Datos (2)'!V25*Hoja1!$K$21+'Todos los Datos (2)'!AA25*Hoja1!$K$22+'Todos los Datos (2)'!AF25*Hoja1!$K$23+'Todos los Datos (2)'!AK25*Hoja1!$K$24</f>
@@ -15364,7 +15340,7 @@
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <f>'Todos los Datos (2)'!B26*Hoja1!$K$17+'Todos los Datos (2)'!G26*Hoja1!$K$18+'Todos los Datos (2)'!L26*Hoja1!$K$19+'Todos los Datos (2)'!Q26*Hoja1!$K$20+'Todos los Datos (2)'!V26*Hoja1!$K$21+'Todos los Datos (2)'!AA26*Hoja1!$K$22+'Todos los Datos (2)'!AF26*Hoja1!$K$23+'Todos los Datos (2)'!AK26*Hoja1!$K$24</f>
@@ -15389,7 +15365,7 @@
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <f>'Todos los Datos (2)'!B27*Hoja1!$K$17+'Todos los Datos (2)'!G27*Hoja1!$K$18+'Todos los Datos (2)'!L27*Hoja1!$K$19+'Todos los Datos (2)'!Q27*Hoja1!$K$20+'Todos los Datos (2)'!V27*Hoja1!$K$21+'Todos los Datos (2)'!AA27*Hoja1!$K$22+'Todos los Datos (2)'!AF27*Hoja1!$K$23+'Todos los Datos (2)'!AK27*Hoja1!$K$24</f>
@@ -15414,7 +15390,7 @@
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <f>'Todos los Datos (2)'!B28*Hoja1!$K$17+'Todos los Datos (2)'!G28*Hoja1!$K$18+'Todos los Datos (2)'!L28*Hoja1!$K$19+'Todos los Datos (2)'!Q28*Hoja1!$K$20+'Todos los Datos (2)'!V28*Hoja1!$K$21+'Todos los Datos (2)'!AA28*Hoja1!$K$22+'Todos los Datos (2)'!AF28*Hoja1!$K$23+'Todos los Datos (2)'!AK28*Hoja1!$K$24</f>
@@ -15439,7 +15415,7 @@
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <f>'Todos los Datos (2)'!B29*Hoja1!$K$17+'Todos los Datos (2)'!G29*Hoja1!$K$18+'Todos los Datos (2)'!L29*Hoja1!$K$19+'Todos los Datos (2)'!Q29*Hoja1!$K$20+'Todos los Datos (2)'!V29*Hoja1!$K$21+'Todos los Datos (2)'!AA29*Hoja1!$K$22+'Todos los Datos (2)'!AF29*Hoja1!$K$23+'Todos los Datos (2)'!AK29*Hoja1!$K$24</f>
@@ -15464,7 +15440,7 @@
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <f>'Todos los Datos (2)'!B30*Hoja1!$K$17+'Todos los Datos (2)'!G30*Hoja1!$K$18+'Todos los Datos (2)'!L30*Hoja1!$K$19+'Todos los Datos (2)'!Q30*Hoja1!$K$20+'Todos los Datos (2)'!V30*Hoja1!$K$21+'Todos los Datos (2)'!AA30*Hoja1!$K$22+'Todos los Datos (2)'!AF30*Hoja1!$K$23+'Todos los Datos (2)'!AK30*Hoja1!$K$24</f>
@@ -15631,7 +15607,7 @@
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <f>'Todos los Datos (2)'!B31*Hoja1!$K$17+'Todos los Datos (2)'!G31*Hoja1!$K$18+'Todos los Datos (2)'!L31*Hoja1!$K$19+'Todos los Datos (2)'!Q31*Hoja1!$K$20+'Todos los Datos (2)'!V31*Hoja1!$K$21+'Todos los Datos (2)'!AA31*Hoja1!$K$22+'Todos los Datos (2)'!AF31*Hoja1!$K$23+'Todos los Datos (2)'!AK31*Hoja1!$K$24</f>
@@ -15656,7 +15632,7 @@
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <f>'Todos los Datos (2)'!B32*Hoja1!$K$17+'Todos los Datos (2)'!G32*Hoja1!$K$18+'Todos los Datos (2)'!L32*Hoja1!$K$19+'Todos los Datos (2)'!Q32*Hoja1!$K$20+'Todos los Datos (2)'!V32*Hoja1!$K$21+'Todos los Datos (2)'!AA32*Hoja1!$K$22+'Todos los Datos (2)'!AF32*Hoja1!$K$23+'Todos los Datos (2)'!AK32*Hoja1!$K$24</f>
@@ -15681,7 +15657,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <f>'Todos los Datos (2)'!B33*Hoja1!$K$17+'Todos los Datos (2)'!G33*Hoja1!$K$18+'Todos los Datos (2)'!L33*Hoja1!$K$19+'Todos los Datos (2)'!Q33*Hoja1!$K$20+'Todos los Datos (2)'!V33*Hoja1!$K$21+'Todos los Datos (2)'!AA33*Hoja1!$K$22+'Todos los Datos (2)'!AF33*Hoja1!$K$23+'Todos los Datos (2)'!AK33*Hoja1!$K$24</f>
@@ -15706,7 +15682,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <f>'Todos los Datos (2)'!B34*Hoja1!$K$17+'Todos los Datos (2)'!G34*Hoja1!$K$18+'Todos los Datos (2)'!L34*Hoja1!$K$19+'Todos los Datos (2)'!Q34*Hoja1!$K$20+'Todos los Datos (2)'!V34*Hoja1!$K$21+'Todos los Datos (2)'!AA34*Hoja1!$K$22+'Todos los Datos (2)'!AF34*Hoja1!$K$23+'Todos los Datos (2)'!AK34*Hoja1!$K$24</f>
@@ -15731,7 +15707,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <f>'Todos los Datos (2)'!B35*Hoja1!$K$17+'Todos los Datos (2)'!G35*Hoja1!$K$18+'Todos los Datos (2)'!L35*Hoja1!$K$19+'Todos los Datos (2)'!Q35*Hoja1!$K$20+'Todos los Datos (2)'!V35*Hoja1!$K$21+'Todos los Datos (2)'!AA35*Hoja1!$K$22+'Todos los Datos (2)'!AF35*Hoja1!$K$23+'Todos los Datos (2)'!AK35*Hoja1!$K$24</f>
@@ -15756,7 +15732,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <f>'Todos los Datos (2)'!B36*Hoja1!$K$17+'Todos los Datos (2)'!G36*Hoja1!$K$18+'Todos los Datos (2)'!L36*Hoja1!$K$19+'Todos los Datos (2)'!Q36*Hoja1!$K$20+'Todos los Datos (2)'!V36*Hoja1!$K$21+'Todos los Datos (2)'!AA36*Hoja1!$K$22+'Todos los Datos (2)'!AF36*Hoja1!$K$23+'Todos los Datos (2)'!AK36*Hoja1!$K$24</f>
@@ -15781,7 +15757,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <f>'Todos los Datos (2)'!B37*Hoja1!$K$17+'Todos los Datos (2)'!G37*Hoja1!$K$18+'Todos los Datos (2)'!L37*Hoja1!$K$19+'Todos los Datos (2)'!Q37*Hoja1!$K$20+'Todos los Datos (2)'!V37*Hoja1!$K$21+'Todos los Datos (2)'!AA37*Hoja1!$K$22+'Todos los Datos (2)'!AF37*Hoja1!$K$23+'Todos los Datos (2)'!AK37*Hoja1!$K$24</f>
@@ -15806,7 +15782,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <f>'Todos los Datos (2)'!B38*Hoja1!$K$17+'Todos los Datos (2)'!G38*Hoja1!$K$18+'Todos los Datos (2)'!L38*Hoja1!$K$19+'Todos los Datos (2)'!Q38*Hoja1!$K$20+'Todos los Datos (2)'!V38*Hoja1!$K$21+'Todos los Datos (2)'!AA38*Hoja1!$K$22+'Todos los Datos (2)'!AF38*Hoja1!$K$23+'Todos los Datos (2)'!AK38*Hoja1!$K$24</f>
@@ -15831,7 +15807,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <f>'Todos los Datos (2)'!B39*Hoja1!$K$17+'Todos los Datos (2)'!G39*Hoja1!$K$18+'Todos los Datos (2)'!L39*Hoja1!$K$19+'Todos los Datos (2)'!Q39*Hoja1!$K$20+'Todos los Datos (2)'!V39*Hoja1!$K$21+'Todos los Datos (2)'!AA39*Hoja1!$K$22+'Todos los Datos (2)'!AF39*Hoja1!$K$23+'Todos los Datos (2)'!AK39*Hoja1!$K$24</f>
@@ -15856,7 +15832,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <f>'Todos los Datos (2)'!B40*Hoja1!$K$17+'Todos los Datos (2)'!G40*Hoja1!$K$18+'Todos los Datos (2)'!L40*Hoja1!$K$19+'Todos los Datos (2)'!Q40*Hoja1!$K$20+'Todos los Datos (2)'!V40*Hoja1!$K$21+'Todos los Datos (2)'!AA40*Hoja1!$K$22+'Todos los Datos (2)'!AF40*Hoja1!$K$23+'Todos los Datos (2)'!AK40*Hoja1!$K$24</f>
@@ -15881,7 +15857,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <f>'Todos los Datos (2)'!B41*Hoja1!$K$17+'Todos los Datos (2)'!G41*Hoja1!$K$18+'Todos los Datos (2)'!L41*Hoja1!$K$19+'Todos los Datos (2)'!Q41*Hoja1!$K$20+'Todos los Datos (2)'!V41*Hoja1!$K$21+'Todos los Datos (2)'!AA41*Hoja1!$K$22+'Todos los Datos (2)'!AF41*Hoja1!$K$23+'Todos los Datos (2)'!AK41*Hoja1!$K$24</f>
@@ -15906,7 +15882,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <f>'Todos los Datos (2)'!B42*Hoja1!$K$17+'Todos los Datos (2)'!G42*Hoja1!$K$18+'Todos los Datos (2)'!L42*Hoja1!$K$19+'Todos los Datos (2)'!Q42*Hoja1!$K$20+'Todos los Datos (2)'!V42*Hoja1!$K$21+'Todos los Datos (2)'!AA42*Hoja1!$K$22+'Todos los Datos (2)'!AF42*Hoja1!$K$23+'Todos los Datos (2)'!AK42*Hoja1!$K$24</f>
@@ -15931,7 +15907,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <f>'Todos los Datos (2)'!B43*Hoja1!$K$17+'Todos los Datos (2)'!G43*Hoja1!$K$18+'Todos los Datos (2)'!L43*Hoja1!$K$19+'Todos los Datos (2)'!Q43*Hoja1!$K$20+'Todos los Datos (2)'!V43*Hoja1!$K$21+'Todos los Datos (2)'!AA43*Hoja1!$K$22+'Todos los Datos (2)'!AF43*Hoja1!$K$23+'Todos los Datos (2)'!AK43*Hoja1!$K$24</f>
@@ -15963,10 +15939,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0CD1DC-5D63-4D74-B3CC-69F3C0169D93}">
   <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -16011,7 +15990,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <f>'Todos los Datos (2)'!B3*Hoja1!$K$17+'Todos los Datos (2)'!G3*Hoja1!$K$18+'Todos los Datos (2)'!L3*Hoja1!$K$19+'Todos los Datos (2)'!Q3*Hoja1!$K$20+'Todos los Datos (2)'!V3*Hoja1!$K$21+'Todos los Datos (2)'!AA3*Hoja1!$K$22+'Todos los Datos (2)'!AF3*Hoja1!$K$23+'Todos los Datos (2)'!AK3*Hoja1!$K$24</f>
@@ -16036,7 +16015,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <f>'Todos los Datos (2)'!B4*Hoja1!$K$17+'Todos los Datos (2)'!G4*Hoja1!$K$18+'Todos los Datos (2)'!L4*Hoja1!$K$19+'Todos los Datos (2)'!Q4*Hoja1!$K$20+'Todos los Datos (2)'!V4*Hoja1!$K$21+'Todos los Datos (2)'!AA4*Hoja1!$K$22+'Todos los Datos (2)'!AF4*Hoja1!$K$23+'Todos los Datos (2)'!AK4*Hoja1!$K$24</f>
@@ -16061,7 +16040,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <f>'Todos los Datos (2)'!B5*Hoja1!$K$17+'Todos los Datos (2)'!G5*Hoja1!$K$18+'Todos los Datos (2)'!L5*Hoja1!$K$19+'Todos los Datos (2)'!Q5*Hoja1!$K$20+'Todos los Datos (2)'!V5*Hoja1!$K$21+'Todos los Datos (2)'!AA5*Hoja1!$K$22+'Todos los Datos (2)'!AF5*Hoja1!$K$23+'Todos los Datos (2)'!AK5*Hoja1!$K$24</f>
@@ -16086,7 +16065,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <f>'Todos los Datos (2)'!B6*Hoja1!$K$17+'Todos los Datos (2)'!G6*Hoja1!$K$18+'Todos los Datos (2)'!L6*Hoja1!$K$19+'Todos los Datos (2)'!Q6*Hoja1!$K$20+'Todos los Datos (2)'!V6*Hoja1!$K$21+'Todos los Datos (2)'!AA6*Hoja1!$K$22+'Todos los Datos (2)'!AF6*Hoja1!$K$23+'Todos los Datos (2)'!AK6*Hoja1!$K$24</f>
@@ -16111,7 +16090,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <f>'Todos los Datos (2)'!B7*Hoja1!$K$17+'Todos los Datos (2)'!G7*Hoja1!$K$18+'Todos los Datos (2)'!L7*Hoja1!$K$19+'Todos los Datos (2)'!Q7*Hoja1!$K$20+'Todos los Datos (2)'!V7*Hoja1!$K$21+'Todos los Datos (2)'!AA7*Hoja1!$K$22+'Todos los Datos (2)'!AF7*Hoja1!$K$23+'Todos los Datos (2)'!AK7*Hoja1!$K$24</f>
@@ -16136,7 +16115,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>'Todos los Datos (2)'!B8*Hoja1!$K$17+'Todos los Datos (2)'!G8*Hoja1!$K$18+'Todos los Datos (2)'!L8*Hoja1!$K$19+'Todos los Datos (2)'!Q8*Hoja1!$K$20+'Todos los Datos (2)'!V8*Hoja1!$K$21+'Todos los Datos (2)'!AA8*Hoja1!$K$22+'Todos los Datos (2)'!AF8*Hoja1!$K$23+'Todos los Datos (2)'!AK8*Hoja1!$K$24</f>
@@ -16161,7 +16140,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <f>'Todos los Datos (2)'!B9*Hoja1!$K$17+'Todos los Datos (2)'!G9*Hoja1!$K$18+'Todos los Datos (2)'!L9*Hoja1!$K$19+'Todos los Datos (2)'!Q9*Hoja1!$K$20+'Todos los Datos (2)'!V9*Hoja1!$K$21+'Todos los Datos (2)'!AA9*Hoja1!$K$22+'Todos los Datos (2)'!AF9*Hoja1!$K$23+'Todos los Datos (2)'!AK9*Hoja1!$K$24</f>
@@ -16186,7 +16165,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <f>'Todos los Datos (2)'!B10*Hoja1!$K$17+'Todos los Datos (2)'!G10*Hoja1!$K$18+'Todos los Datos (2)'!L10*Hoja1!$K$19+'Todos los Datos (2)'!Q10*Hoja1!$K$20+'Todos los Datos (2)'!V10*Hoja1!$K$21+'Todos los Datos (2)'!AA10*Hoja1!$K$22+'Todos los Datos (2)'!AF10*Hoja1!$K$23+'Todos los Datos (2)'!AK10*Hoja1!$K$24</f>
@@ -16211,7 +16190,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <f>'Todos los Datos (2)'!B11*Hoja1!$K$17+'Todos los Datos (2)'!G11*Hoja1!$K$18+'Todos los Datos (2)'!L11*Hoja1!$K$19+'Todos los Datos (2)'!Q11*Hoja1!$K$20+'Todos los Datos (2)'!V11*Hoja1!$K$21+'Todos los Datos (2)'!AA11*Hoja1!$K$22+'Todos los Datos (2)'!AF11*Hoja1!$K$23+'Todos los Datos (2)'!AK11*Hoja1!$K$24</f>
@@ -16236,7 +16215,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <f>'Todos los Datos (2)'!B12*Hoja1!$K$17+'Todos los Datos (2)'!G12*Hoja1!$K$18+'Todos los Datos (2)'!L12*Hoja1!$K$19+'Todos los Datos (2)'!Q12*Hoja1!$K$20+'Todos los Datos (2)'!V12*Hoja1!$K$21+'Todos los Datos (2)'!AA12*Hoja1!$K$22+'Todos los Datos (2)'!AF12*Hoja1!$K$23+'Todos los Datos (2)'!AK12*Hoja1!$K$24</f>
@@ -16261,7 +16240,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <f>'Todos los Datos (2)'!B13*Hoja1!$K$17+'Todos los Datos (2)'!G13*Hoja1!$K$18+'Todos los Datos (2)'!L13*Hoja1!$K$19+'Todos los Datos (2)'!Q13*Hoja1!$K$20+'Todos los Datos (2)'!V13*Hoja1!$K$21+'Todos los Datos (2)'!AA13*Hoja1!$K$22+'Todos los Datos (2)'!AF13*Hoja1!$K$23+'Todos los Datos (2)'!AK13*Hoja1!$K$24</f>
@@ -16286,7 +16265,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <f>'Todos los Datos (2)'!B14*Hoja1!$K$17+'Todos los Datos (2)'!G14*Hoja1!$K$18+'Todos los Datos (2)'!L14*Hoja1!$K$19+'Todos los Datos (2)'!Q14*Hoja1!$K$20+'Todos los Datos (2)'!V14*Hoja1!$K$21+'Todos los Datos (2)'!AA14*Hoja1!$K$22+'Todos los Datos (2)'!AF14*Hoja1!$K$23+'Todos los Datos (2)'!AK14*Hoja1!$K$24</f>
@@ -16311,7 +16290,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <f>'Todos los Datos (2)'!B15*Hoja1!$K$17+'Todos los Datos (2)'!G15*Hoja1!$K$18+'Todos los Datos (2)'!L15*Hoja1!$K$19+'Todos los Datos (2)'!Q15*Hoja1!$K$20+'Todos los Datos (2)'!V15*Hoja1!$K$21+'Todos los Datos (2)'!AA15*Hoja1!$K$22+'Todos los Datos (2)'!AF15*Hoja1!$K$23+'Todos los Datos (2)'!AK15*Hoja1!$K$24</f>
@@ -16336,7 +16315,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <f>'Todos los Datos (2)'!B16*Hoja1!$K$17+'Todos los Datos (2)'!G16*Hoja1!$K$18+'Todos los Datos (2)'!L16*Hoja1!$K$19+'Todos los Datos (2)'!Q16*Hoja1!$K$20+'Todos los Datos (2)'!V16*Hoja1!$K$21+'Todos los Datos (2)'!AA16*Hoja1!$K$22+'Todos los Datos (2)'!AF16*Hoja1!$K$23+'Todos los Datos (2)'!AK16*Hoja1!$K$24</f>
@@ -16361,7 +16340,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <f>'Todos los Datos (2)'!B17*Hoja1!$K$17+'Todos los Datos (2)'!G17*Hoja1!$K$18+'Todos los Datos (2)'!L17*Hoja1!$K$19+'Todos los Datos (2)'!Q17*Hoja1!$K$20+'Todos los Datos (2)'!V17*Hoja1!$K$21+'Todos los Datos (2)'!AA17*Hoja1!$K$22+'Todos los Datos (2)'!AF17*Hoja1!$K$23+'Todos los Datos (2)'!AK17*Hoja1!$K$24</f>
@@ -16386,7 +16365,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <f>'Todos los Datos (2)'!B18*Hoja1!$K$17+'Todos los Datos (2)'!G18*Hoja1!$K$18+'Todos los Datos (2)'!L18*Hoja1!$K$19+'Todos los Datos (2)'!Q18*Hoja1!$K$20+'Todos los Datos (2)'!V18*Hoja1!$K$21+'Todos los Datos (2)'!AA18*Hoja1!$K$22+'Todos los Datos (2)'!AF18*Hoja1!$K$23+'Todos los Datos (2)'!AK18*Hoja1!$K$24</f>
@@ -16411,7 +16390,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <f>'Todos los Datos (2)'!B19*Hoja1!$K$17+'Todos los Datos (2)'!G19*Hoja1!$K$18+'Todos los Datos (2)'!L19*Hoja1!$K$19+'Todos los Datos (2)'!Q19*Hoja1!$K$20+'Todos los Datos (2)'!V19*Hoja1!$K$21+'Todos los Datos (2)'!AA19*Hoja1!$K$22+'Todos los Datos (2)'!AF19*Hoja1!$K$23+'Todos los Datos (2)'!AK19*Hoja1!$K$24</f>
@@ -16436,7 +16415,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <f>'Todos los Datos (2)'!B20*Hoja1!$K$17+'Todos los Datos (2)'!G20*Hoja1!$K$18+'Todos los Datos (2)'!L20*Hoja1!$K$19+'Todos los Datos (2)'!Q20*Hoja1!$K$20+'Todos los Datos (2)'!V20*Hoja1!$K$21+'Todos los Datos (2)'!AA20*Hoja1!$K$22+'Todos los Datos (2)'!AF20*Hoja1!$K$23+'Todos los Datos (2)'!AK20*Hoja1!$K$24</f>
@@ -16461,7 +16440,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <f>'Todos los Datos (2)'!B21*Hoja1!$K$17+'Todos los Datos (2)'!G21*Hoja1!$K$18+'Todos los Datos (2)'!L21*Hoja1!$K$19+'Todos los Datos (2)'!Q21*Hoja1!$K$20+'Todos los Datos (2)'!V21*Hoja1!$K$21+'Todos los Datos (2)'!AA21*Hoja1!$K$22+'Todos los Datos (2)'!AF21*Hoja1!$K$23+'Todos los Datos (2)'!AK21*Hoja1!$K$24</f>
@@ -16486,7 +16465,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <f>'Todos los Datos (2)'!B22*Hoja1!$K$17+'Todos los Datos (2)'!G22*Hoja1!$K$18+'Todos los Datos (2)'!L22*Hoja1!$K$19+'Todos los Datos (2)'!Q22*Hoja1!$K$20+'Todos los Datos (2)'!V22*Hoja1!$K$21+'Todos los Datos (2)'!AA22*Hoja1!$K$22+'Todos los Datos (2)'!AF22*Hoja1!$K$23+'Todos los Datos (2)'!AK22*Hoja1!$K$24</f>
@@ -16511,7 +16490,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <f>'Todos los Datos (2)'!B23*Hoja1!$K$17+'Todos los Datos (2)'!G23*Hoja1!$K$18+'Todos los Datos (2)'!L23*Hoja1!$K$19+'Todos los Datos (2)'!Q23*Hoja1!$K$20+'Todos los Datos (2)'!V23*Hoja1!$K$21+'Todos los Datos (2)'!AA23*Hoja1!$K$22+'Todos los Datos (2)'!AF23*Hoja1!$K$23+'Todos los Datos (2)'!AK23*Hoja1!$K$24</f>
@@ -16536,7 +16515,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <f>'Todos los Datos (2)'!B24*Hoja1!$K$17+'Todos los Datos (2)'!G24*Hoja1!$K$18+'Todos los Datos (2)'!L24*Hoja1!$K$19+'Todos los Datos (2)'!Q24*Hoja1!$K$20+'Todos los Datos (2)'!V24*Hoja1!$K$21+'Todos los Datos (2)'!AA24*Hoja1!$K$22+'Todos los Datos (2)'!AF24*Hoja1!$K$23+'Todos los Datos (2)'!AK24*Hoja1!$K$24</f>
@@ -16561,7 +16540,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <f>'Todos los Datos (2)'!B25*Hoja1!$K$17+'Todos los Datos (2)'!G25*Hoja1!$K$18+'Todos los Datos (2)'!L25*Hoja1!$K$19+'Todos los Datos (2)'!Q25*Hoja1!$K$20+'Todos los Datos (2)'!V25*Hoja1!$K$21+'Todos los Datos (2)'!AA25*Hoja1!$K$22+'Todos los Datos (2)'!AF25*Hoja1!$K$23+'Todos los Datos (2)'!AK25*Hoja1!$K$24</f>
@@ -16586,7 +16565,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <f>'Todos los Datos (2)'!B26*Hoja1!$K$17+'Todos los Datos (2)'!G26*Hoja1!$K$18+'Todos los Datos (2)'!L26*Hoja1!$K$19+'Todos los Datos (2)'!Q26*Hoja1!$K$20+'Todos los Datos (2)'!V26*Hoja1!$K$21+'Todos los Datos (2)'!AA26*Hoja1!$K$22+'Todos los Datos (2)'!AF26*Hoja1!$K$23+'Todos los Datos (2)'!AK26*Hoja1!$K$24</f>
@@ -16611,7 +16590,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <f>'Todos los Datos (2)'!B27*Hoja1!$K$17+'Todos los Datos (2)'!G27*Hoja1!$K$18+'Todos los Datos (2)'!L27*Hoja1!$K$19+'Todos los Datos (2)'!Q27*Hoja1!$K$20+'Todos los Datos (2)'!V27*Hoja1!$K$21+'Todos los Datos (2)'!AA27*Hoja1!$K$22+'Todos los Datos (2)'!AF27*Hoja1!$K$23+'Todos los Datos (2)'!AK27*Hoja1!$K$24</f>
@@ -16636,7 +16615,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <f>'Todos los Datos (2)'!B28*Hoja1!$K$17+'Todos los Datos (2)'!G28*Hoja1!$K$18+'Todos los Datos (2)'!L28*Hoja1!$K$19+'Todos los Datos (2)'!Q28*Hoja1!$K$20+'Todos los Datos (2)'!V28*Hoja1!$K$21+'Todos los Datos (2)'!AA28*Hoja1!$K$22+'Todos los Datos (2)'!AF28*Hoja1!$K$23+'Todos los Datos (2)'!AK28*Hoja1!$K$24</f>
@@ -16661,7 +16640,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <f>'Todos los Datos (2)'!B29*Hoja1!$K$17+'Todos los Datos (2)'!G29*Hoja1!$K$18+'Todos los Datos (2)'!L29*Hoja1!$K$19+'Todos los Datos (2)'!Q29*Hoja1!$K$20+'Todos los Datos (2)'!V29*Hoja1!$K$21+'Todos los Datos (2)'!AA29*Hoja1!$K$22+'Todos los Datos (2)'!AF29*Hoja1!$K$23+'Todos los Datos (2)'!AK29*Hoja1!$K$24</f>
@@ -16686,7 +16665,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <f>'Todos los Datos (2)'!B30*Hoja1!$K$17+'Todos los Datos (2)'!G30*Hoja1!$K$18+'Todos los Datos (2)'!L30*Hoja1!$K$19+'Todos los Datos (2)'!Q30*Hoja1!$K$20+'Todos los Datos (2)'!V30*Hoja1!$K$21+'Todos los Datos (2)'!AA30*Hoja1!$K$22+'Todos los Datos (2)'!AF30*Hoja1!$K$23+'Todos los Datos (2)'!AK30*Hoja1!$K$24</f>
@@ -16711,7 +16690,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <f>'Todos los Datos (2)'!B31*Hoja1!$K$17+'Todos los Datos (2)'!G31*Hoja1!$K$18+'Todos los Datos (2)'!L31*Hoja1!$K$19+'Todos los Datos (2)'!Q31*Hoja1!$K$20+'Todos los Datos (2)'!V31*Hoja1!$K$21+'Todos los Datos (2)'!AA31*Hoja1!$K$22+'Todos los Datos (2)'!AF31*Hoja1!$K$23+'Todos los Datos (2)'!AK31*Hoja1!$K$24</f>
@@ -16736,7 +16715,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <f>'Todos los Datos (2)'!B32*Hoja1!$K$17+'Todos los Datos (2)'!G32*Hoja1!$K$18+'Todos los Datos (2)'!L32*Hoja1!$K$19+'Todos los Datos (2)'!Q32*Hoja1!$K$20+'Todos los Datos (2)'!V32*Hoja1!$K$21+'Todos los Datos (2)'!AA32*Hoja1!$K$22+'Todos los Datos (2)'!AF32*Hoja1!$K$23+'Todos los Datos (2)'!AK32*Hoja1!$K$24</f>
@@ -16761,7 +16740,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <f>'Todos los Datos (2)'!B33*Hoja1!$K$17+'Todos los Datos (2)'!G33*Hoja1!$K$18+'Todos los Datos (2)'!L33*Hoja1!$K$19+'Todos los Datos (2)'!Q33*Hoja1!$K$20+'Todos los Datos (2)'!V33*Hoja1!$K$21+'Todos los Datos (2)'!AA33*Hoja1!$K$22+'Todos los Datos (2)'!AF33*Hoja1!$K$23+'Todos los Datos (2)'!AK33*Hoja1!$K$24</f>
@@ -16786,7 +16765,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <f>'Todos los Datos (2)'!B34*Hoja1!$K$17+'Todos los Datos (2)'!G34*Hoja1!$K$18+'Todos los Datos (2)'!L34*Hoja1!$K$19+'Todos los Datos (2)'!Q34*Hoja1!$K$20+'Todos los Datos (2)'!V34*Hoja1!$K$21+'Todos los Datos (2)'!AA34*Hoja1!$K$22+'Todos los Datos (2)'!AF34*Hoja1!$K$23+'Todos los Datos (2)'!AK34*Hoja1!$K$24</f>
@@ -16811,7 +16790,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <f>'Todos los Datos (2)'!B35*Hoja1!$K$17+'Todos los Datos (2)'!G35*Hoja1!$K$18+'Todos los Datos (2)'!L35*Hoja1!$K$19+'Todos los Datos (2)'!Q35*Hoja1!$K$20+'Todos los Datos (2)'!V35*Hoja1!$K$21+'Todos los Datos (2)'!AA35*Hoja1!$K$22+'Todos los Datos (2)'!AF35*Hoja1!$K$23+'Todos los Datos (2)'!AK35*Hoja1!$K$24</f>
@@ -16836,7 +16815,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <f>'Todos los Datos (2)'!B36*Hoja1!$K$17+'Todos los Datos (2)'!G36*Hoja1!$K$18+'Todos los Datos (2)'!L36*Hoja1!$K$19+'Todos los Datos (2)'!Q36*Hoja1!$K$20+'Todos los Datos (2)'!V36*Hoja1!$K$21+'Todos los Datos (2)'!AA36*Hoja1!$K$22+'Todos los Datos (2)'!AF36*Hoja1!$K$23+'Todos los Datos (2)'!AK36*Hoja1!$K$24</f>
@@ -16861,7 +16840,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <f>'Todos los Datos (2)'!B37*Hoja1!$K$17+'Todos los Datos (2)'!G37*Hoja1!$K$18+'Todos los Datos (2)'!L37*Hoja1!$K$19+'Todos los Datos (2)'!Q37*Hoja1!$K$20+'Todos los Datos (2)'!V37*Hoja1!$K$21+'Todos los Datos (2)'!AA37*Hoja1!$K$22+'Todos los Datos (2)'!AF37*Hoja1!$K$23+'Todos los Datos (2)'!AK37*Hoja1!$K$24</f>
@@ -16886,7 +16865,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <f>'Todos los Datos (2)'!B38*Hoja1!$K$17+'Todos los Datos (2)'!G38*Hoja1!$K$18+'Todos los Datos (2)'!L38*Hoja1!$K$19+'Todos los Datos (2)'!Q38*Hoja1!$K$20+'Todos los Datos (2)'!V38*Hoja1!$K$21+'Todos los Datos (2)'!AA38*Hoja1!$K$22+'Todos los Datos (2)'!AF38*Hoja1!$K$23+'Todos los Datos (2)'!AK38*Hoja1!$K$24</f>
@@ -16911,7 +16890,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <f>'Todos los Datos (2)'!B39*Hoja1!$K$17+'Todos los Datos (2)'!G39*Hoja1!$K$18+'Todos los Datos (2)'!L39*Hoja1!$K$19+'Todos los Datos (2)'!Q39*Hoja1!$K$20+'Todos los Datos (2)'!V39*Hoja1!$K$21+'Todos los Datos (2)'!AA39*Hoja1!$K$22+'Todos los Datos (2)'!AF39*Hoja1!$K$23+'Todos los Datos (2)'!AK39*Hoja1!$K$24</f>
@@ -16936,7 +16915,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <f>'Todos los Datos (2)'!B40*Hoja1!$K$17+'Todos los Datos (2)'!G40*Hoja1!$K$18+'Todos los Datos (2)'!L40*Hoja1!$K$19+'Todos los Datos (2)'!Q40*Hoja1!$K$20+'Todos los Datos (2)'!V40*Hoja1!$K$21+'Todos los Datos (2)'!AA40*Hoja1!$K$22+'Todos los Datos (2)'!AF40*Hoja1!$K$23+'Todos los Datos (2)'!AK40*Hoja1!$K$24</f>
@@ -16961,7 +16940,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <f>'Todos los Datos (2)'!B41*Hoja1!$K$17+'Todos los Datos (2)'!G41*Hoja1!$K$18+'Todos los Datos (2)'!L41*Hoja1!$K$19+'Todos los Datos (2)'!Q41*Hoja1!$K$20+'Todos los Datos (2)'!V41*Hoja1!$K$21+'Todos los Datos (2)'!AA41*Hoja1!$K$22+'Todos los Datos (2)'!AF41*Hoja1!$K$23+'Todos los Datos (2)'!AK41*Hoja1!$K$24</f>
@@ -16986,7 +16965,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <f>'Todos los Datos (2)'!B42*Hoja1!$K$17+'Todos los Datos (2)'!G42*Hoja1!$K$18+'Todos los Datos (2)'!L42*Hoja1!$K$19+'Todos los Datos (2)'!Q42*Hoja1!$K$20+'Todos los Datos (2)'!V42*Hoja1!$K$21+'Todos los Datos (2)'!AA42*Hoja1!$K$22+'Todos los Datos (2)'!AF42*Hoja1!$K$23+'Todos los Datos (2)'!AK42*Hoja1!$K$24</f>
@@ -17011,7 +16990,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <f>'Todos los Datos (2)'!B43*Hoja1!$K$17+'Todos los Datos (2)'!G43*Hoja1!$K$18+'Todos los Datos (2)'!L43*Hoja1!$K$19+'Todos los Datos (2)'!Q43*Hoja1!$K$20+'Todos los Datos (2)'!V43*Hoja1!$K$21+'Todos los Datos (2)'!AA43*Hoja1!$K$22+'Todos los Datos (2)'!AF43*Hoja1!$K$23+'Todos los Datos (2)'!AK43*Hoja1!$K$24</f>
@@ -17049,7 +17028,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -17089,7 +17068,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>77.590463426677005</v>
@@ -17109,7 +17088,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>48.081125972550048</v>
@@ -17129,7 +17108,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>74.145896309815768</v>
@@ -17149,7 +17128,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>38.153376573826783</v>
@@ -17169,7 +17148,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>50.279680724027401</v>
@@ -17189,7 +17168,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>35.155173669725059</v>
@@ -17209,7 +17188,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>45.954474433994058</v>
@@ -17229,7 +17208,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>64.589052155659616</v>
@@ -17249,7 +17228,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>58.866304234911183</v>
@@ -17269,7 +17248,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>32.441200324412002</v>
@@ -17289,7 +17268,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>80.701791160533674</v>
@@ -17309,7 +17288,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>28.052306762763799</v>
@@ -17329,7 +17308,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>22.163567125385345</v>
@@ -17349,7 +17328,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>80.738177623990779</v>
@@ -17369,7 +17348,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>151.79113539769278</v>
@@ -17389,7 +17368,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>44.943043335465248</v>
@@ -17409,7 +17388,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>183.40210912425493</v>
@@ -17429,7 +17408,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>52.820801172281001</v>
@@ -17449,7 +17428,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>4.284490145672665</v>
@@ -17469,7 +17448,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>61.764705882352935</v>
@@ -17489,7 +17468,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>60.255198487712661</v>
@@ -17509,7 +17488,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>23.929169657812874</v>
@@ -17529,7 +17508,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>108.77966392809093</v>
@@ -17549,7 +17528,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>24.966711051930758</v>
@@ -17569,7 +17548,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>49.208562289838433</v>
@@ -17589,7 +17568,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>31.214639666003354</v>
@@ -17609,7 +17588,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>55.361902809103952</v>
@@ -17629,7 +17608,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>32.266391326794015</v>
@@ -17649,7 +17628,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>31.934597943411895</v>
@@ -17669,7 +17648,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>61.748281786941583</v>
@@ -17689,7 +17668,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>74.626865671641795</v>
@@ -17709,7 +17688,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>35.997120230381569</v>
@@ -17729,7 +17708,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>102.95126973232671</v>
@@ -17749,7 +17728,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>57.232049947970857</v>
@@ -17769,7 +17748,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>66.785798090287173</v>
@@ -17789,7 +17768,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>18.351991191044231</v>
@@ -17809,7 +17788,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>28.421202216853771</v>
@@ -17829,7 +17808,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>15.330369461904032</v>
@@ -17849,7 +17828,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>54.878048780487802</v>
@@ -17869,7 +17848,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>66.383192493316827</v>
@@ -17889,7 +17868,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>58.220773171867719</v>
@@ -17925,7 +17904,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -17965,7 +17944,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>183.39564082669111</v>
@@ -17985,7 +17964,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>100.53326339715009</v>
@@ -18005,7 +17984,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>85.552957280556654</v>
@@ -18025,7 +18004,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>57.230064860740171</v>
@@ -18045,7 +18024,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>100.5593614480548</v>
@@ -18065,7 +18044,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>83.295591667907118</v>
@@ -18085,7 +18064,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>240.49508287123558</v>
@@ -18105,7 +18084,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>193.76715646697886</v>
@@ -18125,7 +18104,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>221.61432182554799</v>
@@ -18145,7 +18124,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>162.20600162206</v>
@@ -18165,7 +18144,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>158.25935669143618</v>
@@ -18185,7 +18164,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>102.13916821313998</v>
@@ -18205,7 +18184,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>132.98140275231208</v>
@@ -18225,7 +18204,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>69.20415224913495</v>
@@ -18245,7 +18224,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>75.895567698846392</v>
@@ -18265,7 +18244,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>165.94354462325632</v>
@@ -18285,7 +18264,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>103.16368638239339</v>
@@ -18305,7 +18284,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>187.42864932099712</v>
@@ -18325,7 +18304,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>184.2330762639246</v>
@@ -18345,7 +18324,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>223.52941176470586</v>
@@ -18365,7 +18344,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>170.72306238185254</v>
@@ -18385,7 +18364,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>119.64584828906436</v>
@@ -18405,7 +18384,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>140.2685140125383</v>
@@ -18425,7 +18404,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>149.80026631158455</v>
@@ -18445,7 +18424,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>106.61855162798327</v>
@@ -18465,7 +18444,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>192.30447651377068</v>
@@ -18485,7 +18464,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>186.59011687512813</v>
@@ -18505,7 +18484,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>161.33195663397007</v>
@@ -18525,7 +18504,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>236.31602478124802</v>
@@ -18545,7 +18524,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>166.45189003436428</v>
@@ -18565,7 +18544,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>137.77267508610794</v>
@@ -18585,7 +18564,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>211.18310535157187</v>
@@ -18605,7 +18584,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>130.40494166094715</v>
@@ -18625,7 +18604,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>52.029136316337144</v>
@@ -18645,7 +18624,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>123.19272215302973</v>
@@ -18665,7 +18644,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>55.05597357313269</v>
@@ -18685,7 +18664,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>127.89540997584197</v>
@@ -18705,7 +18684,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>114.97777096428024</v>
@@ -18725,7 +18704,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>164.63414634146341</v>
@@ -18745,7 +18724,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>214.39977035003676</v>
@@ -18765,7 +18744,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>167.67582673497904</v>
@@ -18796,7 +18775,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -18836,7 +18815,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>204.55667630669393</v>
@@ -18856,7 +18835,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>113.6462977533001</v>
@@ -18876,7 +18855,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>28.517652426852219</v>
@@ -18896,7 +18875,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>190.76688286913392</v>
@@ -18916,7 +18895,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>106.84432153855823</v>
@@ -18936,7 +18915,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>99.131255483098585</v>
@@ -18956,7 +18935,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>250.45188566526764</v>
@@ -18976,7 +18955,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>92.846762473760705</v>
@@ -18996,7 +18975,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>197.37525537587868</v>
@@ -19016,7 +18995,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>118.95106785617735</v>
@@ -19036,7 +19015,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>253.63420079024871</v>
@@ -19056,7 +19035,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>194.20827758836475</v>
@@ -19076,7 +19055,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>159.17470935504019</v>
@@ -19096,7 +19075,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>11.534025374855824</v>
@@ -19116,7 +19095,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>182.14936247723134</v>
@@ -19136,7 +19115,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>124.45765846744223</v>
@@ -19156,7 +19135,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>126.08895002292526</v>
@@ -19176,7 +19155,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>66.451975668353526</v>
@@ -19196,7 +19175,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>141.38817480719794</v>
@@ -19216,7 +19195,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>111.76470588235293</v>
@@ -19236,7 +19215,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>126.41776937618147</v>
@@ -19256,7 +19235,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>83.752093802345058</v>
@@ -19276,7 +19255,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>85.878682048492834</v>
@@ -19296,7 +19275,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>291.27829560585883</v>
@@ -19316,7 +19295,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>180.43139506274093</v>
@@ -19336,7 +19315,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>115.10398376838738</v>
@@ -19356,7 +19335,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>112.77424646298954</v>
@@ -19376,7 +19355,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>154.87867836861128</v>
@@ -19396,7 +19375,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>185.22066807178899</v>
@@ -19416,7 +19395,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>144.97422680412373</v>
@@ -19436,7 +19415,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>172.21584385763492</v>
@@ -19456,7 +19435,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>196.78425725941923</v>
@@ -19476,7 +19455,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>48.043925875085797</v>
@@ -19496,7 +19475,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>171.69614984391259</v>
@@ -19516,7 +19495,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>110.10631577047346</v>
@@ -19536,7 +19515,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>110.11194714626538</v>
@@ -19556,7 +19535,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>156.31661219269574</v>
@@ -19576,7 +19555,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>107.31258623332823</v>
@@ -19596,7 +19575,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>140.2439024390244</v>
@@ -19616,7 +19595,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>221.57633170066561</v>
@@ -19636,7 +19615,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>223.56776897997204</v>
@@ -19667,7 +19646,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -19707,7 +19686,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>63.483106440008463</v>
@@ -19727,7 +19706,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>61.194160328700058</v>
@@ -19747,7 +19726,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>51.331774368333996</v>
@@ -19767,7 +19746,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>38.153376573826783</v>
@@ -19787,7 +19766,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>75.419521086041101</v>
@@ -19807,7 +19786,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>38.322306432763355</v>
@@ -19827,7 +19806,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>52.84764559909317</v>
@@ -19847,7 +19826,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>56.515420636202165</v>
@@ -19867,7 +19846,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>51.940856677862811</v>
@@ -19887,7 +19866,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>75.696134090294677</v>
@@ -19907,7 +19886,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>48.211459654344793</v>
@@ -19927,7 +19906,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>62.578222778473091</v>
@@ -19947,7 +19926,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>78.5799198081844</v>
@@ -19967,7 +19946,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>23.068050749711649</v>
@@ -19987,7 +19966,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>121.43290831815423</v>
@@ -20007,7 +19986,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>32.842993206686145</v>
@@ -20027,7 +20006,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>22.925263640531867</v>
@@ -20047,7 +20026,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>23.854555368126906</v>
@@ -20067,7 +20046,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>21.422450728363327</v>
@@ -20087,7 +20066,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>61.764705882352935</v>
@@ -20107,7 +20086,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>61.436672967863892</v>
@@ -20127,7 +20106,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>107.68126346015794</v>
@@ -20147,7 +20126,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>57.252454698995223</v>
@@ -20167,7 +20146,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>66.577896138482018</v>
@@ -20187,7 +20166,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>57.40998933814484</v>
@@ -20207,7 +20186,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>45.985853079379943</v>
@@ -20227,7 +20206,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>59.462784498667212</v>
@@ -20247,7 +20226,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>25.81311306143521</v>
@@ -20267,7 +20246,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>114.96455259628283</v>
@@ -20287,7 +20266,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>88.595360824742272</v>
@@ -20307,7 +20286,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>57.405281285878303</v>
@@ -20327,7 +20306,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>100.79193664506839</v>
@@ -20347,7 +20326,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>41.180507892930677</v>
@@ -20367,7 +20346,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>78.043704474505716</v>
@@ -20387,7 +20366,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>57.760690240248373</v>
@@ -20407,7 +20386,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>110.11194714626538</v>
@@ -20427,7 +20406,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>14.210601108426886</v>
@@ -20447,7 +20426,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>61.32147784761613</v>
@@ -20467,7 +20446,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>54.878048780487802</v>
@@ -20487,7 +20466,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>69.074402999802643</v>
@@ -20507,7 +20486,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>48.905449464368886</v>
@@ -20538,7 +20517,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -20578,7 +20557,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>14.107356986668547</v>
@@ -20598,7 +20577,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>39.339103068450036</v>
@@ -20618,7 +20597,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>17.110591456111333</v>
@@ -20638,7 +20617,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>19.076688286913392</v>
@@ -20658,7 +20637,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>6.2849600905034251</v>
@@ -20678,7 +20657,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>31.988040906686766</v>
@@ -20698,7 +20677,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>22.211329309763794</v>
@@ -20718,7 +20697,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>32.294526077829808</v>
@@ -20738,7 +20717,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>13.850895114096749</v>
@@ -20758,7 +20737,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>27.034333603676668</v>
@@ -20778,7 +20757,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>14.67305293827885</v>
@@ -20798,7 +20777,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>20.859407592824365</v>
@@ -20818,7 +20797,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>6.0446092160141847</v>
@@ -20838,7 +20817,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -20858,7 +20837,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -20878,7 +20857,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>8.6428929491279334</v>
@@ -20898,7 +20877,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -20918,7 +20897,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>6.8155872480362589</v>
@@ -20938,7 +20917,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>17.13796058269066</v>
@@ -20958,7 +20937,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>20.588235294117645</v>
@@ -20978,7 +20957,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>29.536862003780715</v>
@@ -20998,7 +20977,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>5.9822924144532186</v>
@@ -21018,7 +20997,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>8.5878682048492827</v>
@@ -21038,7 +21017,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>8.3222370173102522</v>
@@ -21058,7 +21037,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>8.2014270483064049</v>
@@ -21078,7 +21057,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>10.311979175376109</v>
@@ -21098,7 +21077,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>14.353085913471396</v>
@@ -21118,7 +21097,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>19.359834796076409</v>
@@ -21138,7 +21117,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>19.160758766047138</v>
@@ -21158,7 +21137,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>16.108247422680414</v>
@@ -21178,7 +21157,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>22.962112514351322</v>
@@ -21198,7 +21177,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>31.197504199664024</v>
@@ -21218,7 +21197,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>6.8634179821551138</v>
@@ -21238,7 +21217,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>15.608740894901144</v>
@@ -21258,7 +21237,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>39.710474540170758</v>
@@ -21278,7 +21257,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -21298,7 +21277,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -21318,7 +21297,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>7.6651847309520162</v>
@@ -21338,7 +21317,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>24.390243902439025</v>
@@ -21358,7 +21337,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>8.9707016882860575</v>
@@ -21378,7 +21357,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>2.3288309268747089</v>
@@ -21412,7 +21391,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -21452,7 +21431,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>303.30817521337377</v>
@@ -21472,7 +21451,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>113.6462977533001</v>
@@ -21492,7 +21471,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>68.442365824445332</v>
@@ -21512,7 +21491,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>19.076688286913392</v>
@@ -21532,7 +21511,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>69.134560995537683</v>
@@ -21552,7 +21531,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>66.826501300107992</v>
@@ -21572,7 +21551,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>99.568027940320462</v>
@@ -21592,7 +21571,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>149.36218310996287</v>
@@ -21612,7 +21591,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>58.866304234911183</v>
@@ -21632,7 +21611,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>113.54420113544201</v>
@@ -21652,7 +21631,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>113.19212266672255</v>
@@ -21672,7 +21651,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>33.087336181721405</v>
@@ -21692,7 +21671,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>118.87731458161231</v>
@@ -21712,7 +21691,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>11.534025374855824</v>
@@ -21732,7 +21711,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>60.716454159077117</v>
@@ -21752,7 +21731,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>82.971772311628158</v>
@@ -21772,7 +21751,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>57.313159101329667</v>
@@ -21792,7 +21771,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>92.010427848489485</v>
@@ -21812,7 +21791,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>55.698371893744643</v>
@@ -21832,7 +21811,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>79.411764705882348</v>
@@ -21852,7 +21831,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>162.45274102079395</v>
@@ -21872,7 +21851,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>47.858339315625749</v>
@@ -21892,7 +21871,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>105.91704119314116</v>
@@ -21912,7 +21891,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>33.288948069241009</v>
@@ -21932,7 +21911,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>82.014270483064053</v>
@@ -21952,7 +21931,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>91.414301879009827</v>
@@ -21972,7 +21951,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>104.57248308386302</v>
@@ -21992,7 +21971,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>64.532782653588029</v>
@@ -22012,7 +21991,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>146.89915053969472</v>
@@ -22032,7 +22011,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>102.01890034364261</v>
@@ -22052,7 +22031,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>126.29161882893227</v>
@@ -22072,7 +22051,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>71.994240460763137</v>
@@ -22092,7 +22071,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>82.361015785861355</v>
@@ -22112,7 +22091,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>41.623309053069718</v>
@@ -22132,7 +22111,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>84.836013790364788</v>
@@ -22152,7 +22131,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>183.51991191044229</v>
@@ -22172,7 +22151,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>14.210601108426886</v>
@@ -22192,7 +22171,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>91.982216771424191</v>
@@ -22212,7 +22191,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>97.560975609756099</v>
@@ -22232,7 +22211,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>99.574788739975233</v>
@@ -22252,7 +22231,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>95.48206800186307</v>
@@ -22283,7 +22262,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -22323,7 +22302,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>338.57656768004512</v>
@@ -22343,7 +22322,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>192.32450389020019</v>
@@ -22363,7 +22342,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>125.47767067814976</v>
@@ -22383,7 +22362,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>95.383441434566961</v>
@@ -22403,7 +22382,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>56.564640814530826</v>
@@ -22423,7 +22402,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>322.73082855360212</v>
@@ -22443,7 +22422,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>328.5744922030575</v>
@@ -22463,7 +22442,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>177.61989342806393</v>
@@ -22483,7 +22462,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>214.6888742684996</v>
@@ -22503,7 +22482,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>281.15706947823736</v>
@@ -22523,7 +22502,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>520.89337930889917</v>
@@ -22543,7 +22522,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>279.80377771064406</v>
@@ -22563,7 +22542,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>173.27879752573998</v>
@@ -22583,7 +22562,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>34.602076124567475</v>
@@ -22603,7 +22582,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>151.79113539769278</v>
@@ -22623,7 +22602,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>267.92968142296593</v>
@@ -22643,7 +22622,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>57.313159101329667</v>
@@ -22663,7 +22642,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>320.33260065770418</v>
@@ -22683,7 +22662,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>197.08654670094259</v>
@@ -22703,7 +22682,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>220.58823529411762</v>
@@ -22723,7 +22702,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>517.48582230623811</v>
@@ -22743,7 +22722,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>269.20315865039481</v>
@@ -22763,7 +22742,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>123.09277760283973</v>
@@ -22783,7 +22762,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>99.866844207723034</v>
@@ -22803,7 +22782,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>65.611416386451239</v>
@@ -22823,7 +22802,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>542.91176847655834</v>
@@ -22843,7 +22822,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>268.60775066639326</v>
@@ -22863,7 +22842,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>232.3180175529169</v>
@@ -22883,7 +22862,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>197.99450724915374</v>
@@ -22903,7 +22882,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>139.60481099656357</v>
@@ -22923,7 +22902,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>264.0642939150402</v>
@@ -22943,7 +22922,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>165.58675305975521</v>
@@ -22963,7 +22942,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>68.634179821551129</v>
@@ -22983,7 +22962,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>88.449531737773142</v>
@@ -23003,7 +22982,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>359.6505478240465</v>
@@ -23023,7 +23002,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>110.11194714626538</v>
@@ -23043,7 +23022,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>71.053005542134429</v>
@@ -23063,7 +23042,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>206.95998773570443</v>
@@ -23083,7 +23062,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>274.39024390243901</v>
@@ -23103,7 +23082,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>722.14148590702757</v>
@@ -23123,7 +23102,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>153.70284117373077</v>
@@ -23157,7 +23136,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -23197,7 +23176,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -23217,7 +23196,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -23237,7 +23216,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>5.703530485370444</v>
@@ -23257,7 +23236,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -23277,7 +23256,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -23297,7 +23276,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>1.9002796578229761</v>
@@ -23317,7 +23296,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -23337,7 +23316,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -23357,7 +23336,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -23377,7 +23356,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -23397,7 +23376,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>2.0961504197541214</v>
@@ -23417,7 +23396,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -23437,7 +23416,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -23457,7 +23436,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -23477,7 +23456,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -23497,7 +23476,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -23517,7 +23496,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -23537,7 +23516,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -23557,7 +23536,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -23577,7 +23556,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -23597,7 +23576,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -23617,7 +23596,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -23637,7 +23616,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -23657,7 +23636,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -23677,7 +23656,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -23697,7 +23676,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>0.27870213987502995</v>
@@ -23717,7 +23696,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -23737,7 +23716,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -23757,7 +23736,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -23777,7 +23756,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>2.684707903780069</v>
@@ -23797,7 +23776,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -23817,7 +23796,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -23837,7 +23816,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -23857,7 +23836,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -23877,7 +23856,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -23897,7 +23876,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -23917,7 +23896,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -23937,7 +23916,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>7.6651847309520162</v>
@@ -23957,7 +23936,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -23977,7 +23956,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>0.89707016882860569</v>
@@ -23997,7 +23976,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>0</v>

--- a/Violencia Valle del Cauca Indices con Página con todo junto.xlsx
+++ b/Violencia Valle del Cauca Indices con Página con todo junto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Camilo Gómez\Desktop\universidad\Analítica Computacional\Módulo 1\Proyecto 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A55C3270-D1D7-4719-AF44-BE75A0AE92CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163BDB71-7574-41DF-9D96-2525BCDED7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4032" yWindow="3144" windowWidth="17280" windowHeight="8880" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Habitantes" sheetId="49" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Todos los Datos (2)" sheetId="52" r:id="rId11"/>
     <sheet name="Hoja1" sheetId="51" r:id="rId12"/>
     <sheet name="Indices" sheetId="53" r:id="rId13"/>
+    <sheet name="Porcentajes" sheetId="54" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="119">
   <si>
     <t>Norte</t>
   </si>
@@ -366,15 +367,6 @@
     <t>Homicidios</t>
   </si>
   <si>
-    <t>Lesiones Personales</t>
-  </si>
-  <si>
-    <t>Violencia Intrafamiliar</t>
-  </si>
-  <si>
-    <t>Delitos Sexuales</t>
-  </si>
-  <si>
     <t>Extorsión</t>
   </si>
   <si>
@@ -384,20 +376,69 @@
     <t>Hurtos</t>
   </si>
   <si>
-    <t>Secuestro</t>
-  </si>
-  <si>
     <t>cole_mcpio_ubicacion</t>
   </si>
   <si>
     <t>CALIMA EL DARIEN</t>
+  </si>
+  <si>
+    <t>lectura critica</t>
+  </si>
+  <si>
+    <t>sociales</t>
+  </si>
+  <si>
+    <t>naturales</t>
+  </si>
+  <si>
+    <t>matematicas</t>
+  </si>
+  <si>
+    <t>ingles</t>
+  </si>
+  <si>
+    <t>global</t>
+  </si>
+  <si>
+    <t>educacion padres</t>
+  </si>
+  <si>
+    <t>recursos hogar</t>
+  </si>
+  <si>
+    <t>promedio</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Delitos Sex</t>
+  </si>
+  <si>
+    <t>Violencia Intra</t>
+  </si>
+  <si>
+    <t>Lesiones P</t>
+  </si>
+  <si>
+    <t>Porcentajes</t>
+  </si>
+  <si>
+    <t>Correlaciones con los puntajes</t>
+  </si>
+  <si>
+    <t>Elevar ^2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="177" formatCode="0.00000"/>
+    <numFmt numFmtId="182" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,8 +484,23 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -457,8 +513,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -520,11 +582,158 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -552,9 +761,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -875,6 +1106,7 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3076,7 +3308,7 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -9482,7 +9714,7 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>32.441200324412002</v>
@@ -13517,23 +13749,23 @@
       </c>
       <c r="B2">
         <f>'Todos los Datos (2)'!B2*Hoja1!$K$17+'Todos los Datos (2)'!G2*Hoja1!$K$18+'Todos los Datos (2)'!L2*Hoja1!$K$19+'Todos los Datos (2)'!Q2*Hoja1!$K$20+'Todos los Datos (2)'!V2*Hoja1!$K$21+'Todos los Datos (2)'!AA2*Hoja1!$K$22+'Todos los Datos (2)'!AF2*Hoja1!$K$23+'Todos los Datos (2)'!AK2*Hoja1!$K$24</f>
-        <v>206.51872259587967</v>
+        <v>489.366037019202</v>
       </c>
       <c r="C2">
         <f>'Todos los Datos (2)'!C2*Hoja1!$K$17+'Todos los Datos (2)'!H2*Hoja1!$K$18+'Todos los Datos (2)'!M2*Hoja1!$K$19+'Todos los Datos (2)'!R2*Hoja1!$K$20+'Todos los Datos (2)'!W2*Hoja1!$K$21+'Todos los Datos (2)'!AB2*Hoja1!$K$22+'Todos los Datos (2)'!AG2*Hoja1!$K$23+'Todos los Datos (2)'!AL2*Hoja1!$K$24</f>
-        <v>247.25032629563597</v>
+        <v>599.9971193790866</v>
       </c>
       <c r="D2">
         <f>'Todos los Datos (2)'!D2*Hoja1!$K$17+'Todos los Datos (2)'!I2*Hoja1!$K$18+'Todos los Datos (2)'!N2*Hoja1!$K$19+'Todos los Datos (2)'!S2*Hoja1!$K$20+'Todos los Datos (2)'!X2*Hoja1!$K$21+'Todos los Datos (2)'!AC2*Hoja1!$K$22+'Todos los Datos (2)'!AH2*Hoja1!$K$23+'Todos los Datos (2)'!AM2*Hoja1!$K$24</f>
-        <v>253.76308635117525</v>
+        <v>658.36706114535104</v>
       </c>
       <c r="E2">
         <f>'Todos los Datos (2)'!E2*Hoja1!$K$17+'Todos los Datos (2)'!J2*Hoja1!$K$18+'Todos los Datos (2)'!O2*Hoja1!$K$19+'Todos los Datos (2)'!T2*Hoja1!$K$20+'Todos los Datos (2)'!Y2*Hoja1!$K$21+'Todos los Datos (2)'!AD2*Hoja1!$K$22+'Todos los Datos (2)'!AI2*Hoja1!$K$23+'Todos los Datos (2)'!AN2*Hoja1!$K$24</f>
-        <v>243.79994449576424</v>
+        <v>627.77554524057075</v>
       </c>
       <c r="F2">
         <f>'Todos los Datos (2)'!F2*Hoja1!$K$17+'Todos los Datos (2)'!K2*Hoja1!$K$18+'Todos los Datos (2)'!P2*Hoja1!$K$19+'Todos los Datos (2)'!U2*Hoja1!$K$20+'Todos los Datos (2)'!Z2*Hoja1!$K$21+'Todos los Datos (2)'!AE2*Hoja1!$K$22+'Todos los Datos (2)'!AJ2*Hoja1!$K$23+'Todos los Datos (2)'!AO2*Hoja1!$K$24</f>
-        <v>249.71425840685308</v>
+        <v>621.9009438841299</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -13542,23 +13774,23 @@
       </c>
       <c r="B3">
         <f>'Todos los Datos (2)'!B3*Hoja1!$K$17+'Todos los Datos (2)'!G3*Hoja1!$K$18+'Todos los Datos (2)'!L3*Hoja1!$K$19+'Todos los Datos (2)'!Q3*Hoja1!$K$20+'Todos los Datos (2)'!V3*Hoja1!$K$21+'Todos los Datos (2)'!AA3*Hoja1!$K$22+'Todos los Datos (2)'!AF3*Hoja1!$K$23+'Todos los Datos (2)'!AK3*Hoja1!$K$24</f>
-        <v>149.18530013401988</v>
+        <v>229.03479981817298</v>
       </c>
       <c r="C3">
         <f>'Todos los Datos (2)'!C3*Hoja1!$K$17+'Todos los Datos (2)'!H3*Hoja1!$K$18+'Todos los Datos (2)'!M3*Hoja1!$K$19+'Todos los Datos (2)'!R3*Hoja1!$K$20+'Todos los Datos (2)'!W3*Hoja1!$K$21+'Todos los Datos (2)'!AB3*Hoja1!$K$22+'Todos los Datos (2)'!AG3*Hoja1!$K$23+'Todos los Datos (2)'!AL3*Hoja1!$K$24</f>
-        <v>150.24335190802003</v>
+        <v>260.95522307330214</v>
       </c>
       <c r="D3">
         <f>'Todos los Datos (2)'!D3*Hoja1!$K$17+'Todos los Datos (2)'!I3*Hoja1!$K$18+'Todos los Datos (2)'!N3*Hoja1!$K$19+'Todos los Datos (2)'!S3*Hoja1!$K$20+'Todos los Datos (2)'!X3*Hoja1!$K$21+'Todos los Datos (2)'!AC3*Hoja1!$K$22+'Todos los Datos (2)'!AH3*Hoja1!$K$23+'Todos los Datos (2)'!AM3*Hoja1!$K$24</f>
-        <v>131.19841997601748</v>
+        <v>231.84047368966679</v>
       </c>
       <c r="E3">
         <f>'Todos los Datos (2)'!E3*Hoja1!$K$17+'Todos los Datos (2)'!J3*Hoja1!$K$18+'Todos los Datos (2)'!O3*Hoja1!$K$19+'Todos los Datos (2)'!T3*Hoja1!$K$20+'Todos los Datos (2)'!Y3*Hoja1!$K$21+'Todos los Datos (2)'!AD3*Hoja1!$K$22+'Todos los Datos (2)'!AI3*Hoja1!$K$23+'Todos los Datos (2)'!AN3*Hoja1!$K$24</f>
-        <v>130.49305212668406</v>
+        <v>187.39011369267519</v>
       </c>
       <c r="F3">
         <f>'Todos los Datos (2)'!F3*Hoja1!$K$17+'Todos los Datos (2)'!K3*Hoja1!$K$18+'Todos los Datos (2)'!P3*Hoja1!$K$19+'Todos los Datos (2)'!U3*Hoja1!$K$20+'Todos los Datos (2)'!Z3*Hoja1!$K$21+'Todos los Datos (2)'!AE3*Hoja1!$K$22+'Todos los Datos (2)'!AJ3*Hoja1!$K$23+'Todos los Datos (2)'!AO3*Hoja1!$K$24</f>
-        <v>195.03421034069265</v>
+        <v>293.24003292779446</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -13567,23 +13799,23 @@
       </c>
       <c r="B4">
         <f>'Todos los Datos (2)'!B4*Hoja1!$K$17+'Todos los Datos (2)'!G4*Hoja1!$K$18+'Todos los Datos (2)'!L4*Hoja1!$K$19+'Todos los Datos (2)'!Q4*Hoja1!$K$20+'Todos los Datos (2)'!V4*Hoja1!$K$21+'Todos los Datos (2)'!AA4*Hoja1!$K$22+'Todos los Datos (2)'!AF4*Hoja1!$K$23+'Todos los Datos (2)'!AK4*Hoja1!$K$24</f>
-        <v>87.201678468397574</v>
+        <v>132.8841652027308</v>
       </c>
       <c r="C4">
         <f>'Todos los Datos (2)'!C4*Hoja1!$K$17+'Todos los Datos (2)'!H4*Hoja1!$K$18+'Todos los Datos (2)'!M4*Hoja1!$K$19+'Todos los Datos (2)'!R4*Hoja1!$K$20+'Todos los Datos (2)'!W4*Hoja1!$K$21+'Todos los Datos (2)'!AB4*Hoja1!$K$22+'Todos los Datos (2)'!AG4*Hoja1!$K$23+'Todos los Datos (2)'!AL4*Hoja1!$K$24</f>
-        <v>127.19643325465512</v>
+        <v>196.3792939315428</v>
       </c>
       <c r="D4">
         <f>'Todos los Datos (2)'!D4*Hoja1!$K$17+'Todos los Datos (2)'!I4*Hoja1!$K$18+'Todos los Datos (2)'!N4*Hoja1!$K$19+'Todos los Datos (2)'!S4*Hoja1!$K$20+'Todos los Datos (2)'!X4*Hoja1!$K$21+'Todos los Datos (2)'!AC4*Hoja1!$K$22+'Todos los Datos (2)'!AH4*Hoja1!$K$23+'Todos los Datos (2)'!AM4*Hoja1!$K$24</f>
-        <v>111.24224145467261</v>
+        <v>183.43467002793011</v>
       </c>
       <c r="E4">
         <f>'Todos los Datos (2)'!E4*Hoja1!$K$17+'Todos los Datos (2)'!J4*Hoja1!$K$18+'Todos los Datos (2)'!O4*Hoja1!$K$19+'Todos los Datos (2)'!T4*Hoja1!$K$20+'Todos los Datos (2)'!Y4*Hoja1!$K$21+'Todos los Datos (2)'!AD4*Hoja1!$K$22+'Todos los Datos (2)'!AI4*Hoja1!$K$23+'Todos los Datos (2)'!AN4*Hoja1!$K$24</f>
-        <v>157.79351341900519</v>
+        <v>241.20209003401277</v>
       </c>
       <c r="F4">
         <f>'Todos los Datos (2)'!F4*Hoja1!$K$17+'Todos los Datos (2)'!K4*Hoja1!$K$18+'Todos los Datos (2)'!P4*Hoja1!$K$19+'Todos los Datos (2)'!U4*Hoja1!$K$20+'Todos los Datos (2)'!Z4*Hoja1!$K$21+'Todos los Datos (2)'!AE4*Hoja1!$K$22+'Todos los Datos (2)'!AJ4*Hoja1!$K$23+'Todos los Datos (2)'!AO4*Hoja1!$K$24</f>
-        <v>126.32223096424514</v>
+        <v>185.35654317540389</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -13592,23 +13824,23 @@
       </c>
       <c r="B5">
         <f>'Todos los Datos (2)'!B5*Hoja1!$K$17+'Todos los Datos (2)'!G5*Hoja1!$K$18+'Todos los Datos (2)'!L5*Hoja1!$K$19+'Todos los Datos (2)'!Q5*Hoja1!$K$20+'Todos los Datos (2)'!V5*Hoja1!$K$21+'Todos los Datos (2)'!AA5*Hoja1!$K$22+'Todos los Datos (2)'!AF5*Hoja1!$K$23+'Todos los Datos (2)'!AK5*Hoja1!$K$24</f>
-        <v>56.17977528089888</v>
+        <v>68.447361065615041</v>
       </c>
       <c r="C5">
         <f>'Todos los Datos (2)'!C5*Hoja1!$K$17+'Todos los Datos (2)'!H5*Hoja1!$K$18+'Todos los Datos (2)'!M5*Hoja1!$K$19+'Todos los Datos (2)'!R5*Hoja1!$K$20+'Todos los Datos (2)'!W5*Hoja1!$K$21+'Todos los Datos (2)'!AB5*Hoja1!$K$22+'Todos los Datos (2)'!AG5*Hoja1!$K$23+'Todos los Datos (2)'!AL5*Hoja1!$K$24</f>
-        <v>68.442365824445332</v>
+        <v>101.04396232257588</v>
       </c>
       <c r="D5">
         <f>'Todos los Datos (2)'!D5*Hoja1!$K$17+'Todos los Datos (2)'!I5*Hoja1!$K$18+'Todos los Datos (2)'!N5*Hoja1!$K$19+'Todos los Datos (2)'!S5*Hoja1!$K$20+'Todos los Datos (2)'!X5*Hoja1!$K$21+'Todos los Datos (2)'!AC5*Hoja1!$K$22+'Todos los Datos (2)'!AH5*Hoja1!$K$23+'Todos los Datos (2)'!AM5*Hoja1!$K$24</f>
-        <v>120.05931671704784</v>
+        <v>134.97895205722611</v>
       </c>
       <c r="E5">
         <f>'Todos los Datos (2)'!E5*Hoja1!$K$17+'Todos los Datos (2)'!J5*Hoja1!$K$18+'Todos los Datos (2)'!O5*Hoja1!$K$19+'Todos los Datos (2)'!T5*Hoja1!$K$20+'Todos los Datos (2)'!Y5*Hoja1!$K$21+'Todos los Datos (2)'!AD5*Hoja1!$K$22+'Todos los Datos (2)'!AI5*Hoja1!$K$23+'Todos los Datos (2)'!AN5*Hoja1!$K$24</f>
-        <v>126.90355329949239</v>
+        <v>129.73198594611603</v>
       </c>
       <c r="F5">
         <f>'Todos los Datos (2)'!F5*Hoja1!$K$17+'Todos los Datos (2)'!K5*Hoja1!$K$18+'Todos los Datos (2)'!P5*Hoja1!$K$19+'Todos los Datos (2)'!U5*Hoja1!$K$20+'Todos los Datos (2)'!Z5*Hoja1!$K$21+'Todos los Datos (2)'!AE5*Hoja1!$K$22+'Todos los Datos (2)'!AJ5*Hoja1!$K$23+'Todos los Datos (2)'!AO5*Hoja1!$K$24</f>
-        <v>116.63719842582557</v>
+        <v>104.2573413488456</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -13617,23 +13849,23 @@
       </c>
       <c r="B6">
         <f>'Todos los Datos (2)'!B6*Hoja1!$K$17+'Todos los Datos (2)'!G6*Hoja1!$K$18+'Todos los Datos (2)'!L6*Hoja1!$K$19+'Todos los Datos (2)'!Q6*Hoja1!$K$20+'Todos los Datos (2)'!V6*Hoja1!$K$21+'Todos los Datos (2)'!AA6*Hoja1!$K$22+'Todos los Datos (2)'!AF6*Hoja1!$K$23+'Todos los Datos (2)'!AK6*Hoja1!$K$24</f>
-        <v>86.798931705455914</v>
+        <v>123.60570967360098</v>
       </c>
       <c r="C6">
         <f>'Todos los Datos (2)'!C6*Hoja1!$K$17+'Todos los Datos (2)'!H6*Hoja1!$K$18+'Todos los Datos (2)'!M6*Hoja1!$K$19+'Todos los Datos (2)'!R6*Hoja1!$K$20+'Todos los Datos (2)'!W6*Hoja1!$K$21+'Todos los Datos (2)'!AB6*Hoja1!$K$22+'Todos los Datos (2)'!AG6*Hoja1!$K$23+'Todos los Datos (2)'!AL6*Hoja1!$K$24</f>
-        <v>131.62914917970241</v>
+        <v>194.56313689377745</v>
       </c>
       <c r="D6">
         <f>'Todos los Datos (2)'!D6*Hoja1!$K$17+'Todos los Datos (2)'!I6*Hoja1!$K$18+'Todos los Datos (2)'!N6*Hoja1!$K$19+'Todos los Datos (2)'!S6*Hoja1!$K$20+'Todos los Datos (2)'!X6*Hoja1!$K$21+'Todos los Datos (2)'!AC6*Hoja1!$K$22+'Todos los Datos (2)'!AH6*Hoja1!$K$23+'Todos los Datos (2)'!AM6*Hoja1!$K$24</f>
-        <v>50.55322396032048</v>
+        <v>68.3637647180568</v>
       </c>
       <c r="E6">
         <f>'Todos los Datos (2)'!E6*Hoja1!$K$17+'Todos los Datos (2)'!J6*Hoja1!$K$18+'Todos los Datos (2)'!O6*Hoja1!$K$19+'Todos los Datos (2)'!T6*Hoja1!$K$20+'Todos los Datos (2)'!Y6*Hoja1!$K$21+'Todos los Datos (2)'!AD6*Hoja1!$K$22+'Todos los Datos (2)'!AI6*Hoja1!$K$23+'Todos los Datos (2)'!AN6*Hoja1!$K$24</f>
-        <v>53.414727203357501</v>
+        <v>61.536606210833298</v>
       </c>
       <c r="F6">
         <f>'Todos los Datos (2)'!F6*Hoja1!$K$17+'Todos los Datos (2)'!K6*Hoja1!$K$18+'Todos los Datos (2)'!P6*Hoja1!$K$19+'Todos los Datos (2)'!U6*Hoja1!$K$20+'Todos los Datos (2)'!Z6*Hoja1!$K$21+'Todos los Datos (2)'!AE6*Hoja1!$K$22+'Todos los Datos (2)'!AJ6*Hoja1!$K$23+'Todos los Datos (2)'!AO6*Hoja1!$K$24</f>
-        <v>69.629912247233889</v>
+        <v>69.452140972632364</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -13642,23 +13874,23 @@
       </c>
       <c r="B7">
         <f>'Todos los Datos (2)'!B7*Hoja1!$K$17+'Todos los Datos (2)'!G7*Hoja1!$K$18+'Todos los Datos (2)'!L7*Hoja1!$K$19+'Todos los Datos (2)'!Q7*Hoja1!$K$20+'Todos los Datos (2)'!V7*Hoja1!$K$21+'Todos los Datos (2)'!AA7*Hoja1!$K$22+'Todos los Datos (2)'!AF7*Hoja1!$K$23+'Todos los Datos (2)'!AK7*Hoja1!$K$24</f>
-        <v>70.391553013638358</v>
+        <v>78.162230802237971</v>
       </c>
       <c r="C7">
         <f>'Todos los Datos (2)'!C7*Hoja1!$K$17+'Todos los Datos (2)'!H7*Hoja1!$K$18+'Todos los Datos (2)'!M7*Hoja1!$K$19+'Todos los Datos (2)'!R7*Hoja1!$K$20+'Todos los Datos (2)'!W7*Hoja1!$K$21+'Todos los Datos (2)'!AB7*Hoja1!$K$22+'Todos los Datos (2)'!AG7*Hoja1!$K$23+'Todos los Datos (2)'!AL7*Hoja1!$K$24</f>
-        <v>73.534033058890088</v>
+        <v>94.807833641398162</v>
       </c>
       <c r="D7">
         <f>'Todos los Datos (2)'!D7*Hoja1!$K$17+'Todos los Datos (2)'!I7*Hoja1!$K$18+'Todos los Datos (2)'!N7*Hoja1!$K$19+'Todos los Datos (2)'!S7*Hoja1!$K$20+'Todos los Datos (2)'!X7*Hoja1!$K$21+'Todos los Datos (2)'!AC7*Hoja1!$K$22+'Todos los Datos (2)'!AH7*Hoja1!$K$23+'Todos los Datos (2)'!AM7*Hoja1!$K$24</f>
-        <v>104.0160894978317</v>
+        <v>158.1501948587989</v>
       </c>
       <c r="E7">
         <f>'Todos los Datos (2)'!E7*Hoja1!$K$17+'Todos los Datos (2)'!J7*Hoja1!$K$18+'Todos los Datos (2)'!O7*Hoja1!$K$19+'Todos los Datos (2)'!T7*Hoja1!$K$20+'Todos los Datos (2)'!Y7*Hoja1!$K$21+'Todos los Datos (2)'!AD7*Hoja1!$K$22+'Todos los Datos (2)'!AI7*Hoja1!$K$23+'Todos los Datos (2)'!AN7*Hoja1!$K$24</f>
-        <v>133.24115391867261</v>
+        <v>180.05673315048932</v>
       </c>
       <c r="F7">
         <f>'Todos los Datos (2)'!F7*Hoja1!$K$17+'Todos los Datos (2)'!K7*Hoja1!$K$18+'Todos los Datos (2)'!P7*Hoja1!$K$19+'Todos los Datos (2)'!U7*Hoja1!$K$20+'Todos los Datos (2)'!Z7*Hoja1!$K$21+'Todos los Datos (2)'!AE7*Hoja1!$K$22+'Todos los Datos (2)'!AJ7*Hoja1!$K$23+'Todos los Datos (2)'!AO7*Hoja1!$K$24</f>
-        <v>129.47017786437056</v>
+        <v>135.63503243219526</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -13667,23 +13899,23 @@
       </c>
       <c r="B8">
         <f>'Todos los Datos (2)'!B8*Hoja1!$K$17+'Todos los Datos (2)'!G8*Hoja1!$K$18+'Todos los Datos (2)'!L8*Hoja1!$K$19+'Todos los Datos (2)'!Q8*Hoja1!$K$20+'Todos los Datos (2)'!V8*Hoja1!$K$21+'Todos los Datos (2)'!AA8*Hoja1!$K$22+'Todos los Datos (2)'!AF8*Hoja1!$K$23+'Todos los Datos (2)'!AK8*Hoja1!$K$24</f>
-        <v>85.750119559261805</v>
+        <v>171.95079727766449</v>
       </c>
       <c r="C8">
         <f>'Todos los Datos (2)'!C8*Hoja1!$K$17+'Todos los Datos (2)'!H8*Hoja1!$K$18+'Todos los Datos (2)'!M8*Hoja1!$K$19+'Todos los Datos (2)'!R8*Hoja1!$K$20+'Todos los Datos (2)'!W8*Hoja1!$K$21+'Todos los Datos (2)'!AB8*Hoja1!$K$22+'Todos los Datos (2)'!AG8*Hoja1!$K$23+'Todos los Datos (2)'!AL8*Hoja1!$K$24</f>
-        <v>101.34824841722542</v>
+        <v>195.63441740435553</v>
       </c>
       <c r="D8">
         <f>'Todos los Datos (2)'!D8*Hoja1!$K$17+'Todos los Datos (2)'!I8*Hoja1!$K$18+'Todos los Datos (2)'!N8*Hoja1!$K$19+'Todos los Datos (2)'!S8*Hoja1!$K$20+'Todos los Datos (2)'!X8*Hoja1!$K$21+'Todos los Datos (2)'!AC8*Hoja1!$K$22+'Todos los Datos (2)'!AH8*Hoja1!$K$23+'Todos los Datos (2)'!AM8*Hoja1!$K$24</f>
-        <v>90.659175341971164</v>
+        <v>176.54359905541239</v>
       </c>
       <c r="E8">
         <f>'Todos los Datos (2)'!E8*Hoja1!$K$17+'Todos los Datos (2)'!J8*Hoja1!$K$18+'Todos los Datos (2)'!O8*Hoja1!$K$19+'Todos los Datos (2)'!T8*Hoja1!$K$20+'Todos los Datos (2)'!Y8*Hoja1!$K$21+'Todos los Datos (2)'!AD8*Hoja1!$K$22+'Todos los Datos (2)'!AI8*Hoja1!$K$23+'Todos los Datos (2)'!AN8*Hoja1!$K$24</f>
-        <v>92.670304646500469</v>
+        <v>184.37683184898941</v>
       </c>
       <c r="F8">
         <f>'Todos los Datos (2)'!F8*Hoja1!$K$17+'Todos los Datos (2)'!K8*Hoja1!$K$18+'Todos los Datos (2)'!P8*Hoja1!$K$19+'Todos los Datos (2)'!U8*Hoja1!$K$20+'Todos los Datos (2)'!Z8*Hoja1!$K$21+'Todos los Datos (2)'!AE8*Hoja1!$K$22+'Todos los Datos (2)'!AJ8*Hoja1!$K$23+'Todos los Datos (2)'!AO8*Hoja1!$K$24</f>
-        <v>79.305004386478871</v>
+        <v>157.63120407946221</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -13692,23 +13924,23 @@
       </c>
       <c r="B9">
         <f>'Todos los Datos (2)'!B9*Hoja1!$K$17+'Todos los Datos (2)'!G9*Hoja1!$K$18+'Todos los Datos (2)'!L9*Hoja1!$K$19+'Todos los Datos (2)'!Q9*Hoja1!$K$20+'Todos los Datos (2)'!V9*Hoja1!$K$21+'Todos los Datos (2)'!AA9*Hoja1!$K$22+'Todos los Datos (2)'!AF9*Hoja1!$K$23+'Todos los Datos (2)'!AK9*Hoja1!$K$24</f>
-        <v>145.52250237431451</v>
+        <v>242.79617839341779</v>
       </c>
       <c r="C9">
         <f>'Todos los Datos (2)'!C9*Hoja1!$K$17+'Todos los Datos (2)'!H9*Hoja1!$K$18+'Todos los Datos (2)'!M9*Hoja1!$K$19+'Todos los Datos (2)'!R9*Hoja1!$K$20+'Todos los Datos (2)'!W9*Hoja1!$K$21+'Todos los Datos (2)'!AB9*Hoja1!$K$22+'Todos los Datos (2)'!AG9*Hoja1!$K$23+'Todos los Datos (2)'!AL9*Hoja1!$K$24</f>
-        <v>172.59734689500937</v>
+        <v>300.26413663836126</v>
       </c>
       <c r="D9">
         <f>'Todos los Datos (2)'!D9*Hoja1!$K$17+'Todos los Datos (2)'!I9*Hoja1!$K$18+'Todos los Datos (2)'!N9*Hoja1!$K$19+'Todos los Datos (2)'!S9*Hoja1!$K$20+'Todos los Datos (2)'!X9*Hoja1!$K$21+'Todos los Datos (2)'!AC9*Hoja1!$K$22+'Todos los Datos (2)'!AH9*Hoja1!$K$23+'Todos los Datos (2)'!AM9*Hoja1!$K$24</f>
-        <v>185.46459973652767</v>
+        <v>361.88580215129372</v>
       </c>
       <c r="E9">
         <f>'Todos los Datos (2)'!E9*Hoja1!$K$17+'Todos los Datos (2)'!J9*Hoja1!$K$18+'Todos los Datos (2)'!O9*Hoja1!$K$19+'Todos los Datos (2)'!T9*Hoja1!$K$20+'Todos los Datos (2)'!Y9*Hoja1!$K$21+'Todos los Datos (2)'!AD9*Hoja1!$K$22+'Todos los Datos (2)'!AI9*Hoja1!$K$23+'Todos los Datos (2)'!AN9*Hoja1!$K$24</f>
-        <v>197.10639992647285</v>
+        <v>372.4616776274367</v>
       </c>
       <c r="F9">
         <f>'Todos los Datos (2)'!F9*Hoja1!$K$17+'Todos los Datos (2)'!K9*Hoja1!$K$18+'Todos los Datos (2)'!P9*Hoja1!$K$19+'Todos los Datos (2)'!U9*Hoja1!$K$20+'Todos los Datos (2)'!Z9*Hoja1!$K$21+'Todos los Datos (2)'!AE9*Hoja1!$K$22+'Todos los Datos (2)'!AJ9*Hoja1!$K$23+'Todos los Datos (2)'!AO9*Hoja1!$K$24</f>
-        <v>202.31457369565882</v>
+        <v>362.68046413426953</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -13717,23 +13949,23 @@
       </c>
       <c r="B10">
         <f>'Todos los Datos (2)'!B10*Hoja1!$K$17+'Todos los Datos (2)'!G10*Hoja1!$K$18+'Todos los Datos (2)'!L10*Hoja1!$K$19+'Todos los Datos (2)'!Q10*Hoja1!$K$20+'Todos los Datos (2)'!V10*Hoja1!$K$21+'Todos los Datos (2)'!AA10*Hoja1!$K$22+'Todos los Datos (2)'!AF10*Hoja1!$K$23+'Todos los Datos (2)'!AK10*Hoja1!$K$24</f>
-        <v>89.011787502018421</v>
+        <v>119.71600125248605</v>
       </c>
       <c r="C10">
         <f>'Todos los Datos (2)'!C10*Hoja1!$K$17+'Todos los Datos (2)'!H10*Hoja1!$K$18+'Todos los Datos (2)'!M10*Hoja1!$K$19+'Todos los Datos (2)'!R10*Hoja1!$K$20+'Todos los Datos (2)'!W10*Hoja1!$K$21+'Todos los Datos (2)'!AB10*Hoja1!$K$22+'Todos los Datos (2)'!AG10*Hoja1!$K$23+'Todos los Datos (2)'!AL10*Hoja1!$K$24</f>
-        <v>111.01243339253996</v>
+        <v>199.08430976779448</v>
       </c>
       <c r="D10">
         <f>'Todos los Datos (2)'!D10*Hoja1!$K$17+'Todos los Datos (2)'!I10*Hoja1!$K$18+'Todos los Datos (2)'!N10*Hoja1!$K$19+'Todos los Datos (2)'!S10*Hoja1!$K$20+'Todos los Datos (2)'!X10*Hoja1!$K$21+'Todos los Datos (2)'!AC10*Hoja1!$K$22+'Todos los Datos (2)'!AH10*Hoja1!$K$23+'Todos los Datos (2)'!AM10*Hoja1!$K$24</f>
-        <v>123.12288067172616</v>
+        <v>212.36509719254843</v>
       </c>
       <c r="E10">
         <f>'Todos los Datos (2)'!E10*Hoja1!$K$17+'Todos los Datos (2)'!J10*Hoja1!$K$18+'Todos los Datos (2)'!O10*Hoja1!$K$19+'Todos los Datos (2)'!T10*Hoja1!$K$20+'Todos los Datos (2)'!Y10*Hoja1!$K$21+'Todos los Datos (2)'!AD10*Hoja1!$K$22+'Todos los Datos (2)'!AI10*Hoja1!$K$23+'Todos los Datos (2)'!AN10*Hoja1!$K$24</f>
-        <v>130.38914903923785</v>
+        <v>199.44166856096382</v>
       </c>
       <c r="F10">
         <f>'Todos los Datos (2)'!F10*Hoja1!$K$17+'Todos los Datos (2)'!K10*Hoja1!$K$18+'Todos los Datos (2)'!P10*Hoja1!$K$19+'Todos los Datos (2)'!U10*Hoja1!$K$20+'Todos los Datos (2)'!Z10*Hoja1!$K$21+'Todos los Datos (2)'!AE10*Hoja1!$K$22+'Todos los Datos (2)'!AJ10*Hoja1!$K$23+'Todos los Datos (2)'!AO10*Hoja1!$K$24</f>
-        <v>135.03148716292591</v>
+        <v>221.85775580242341</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -13742,48 +13974,48 @@
       </c>
       <c r="B11">
         <f>'Todos los Datos (2)'!B11*Hoja1!$K$17+'Todos los Datos (2)'!G11*Hoja1!$K$18+'Todos los Datos (2)'!L11*Hoja1!$K$19+'Todos los Datos (2)'!Q11*Hoja1!$K$20+'Todos los Datos (2)'!V11*Hoja1!$K$21+'Todos los Datos (2)'!AA11*Hoja1!$K$22+'Todos los Datos (2)'!AF11*Hoja1!$K$23+'Todos los Datos (2)'!AK11*Hoja1!$K$24</f>
-        <v>117.90574465874859</v>
+        <v>176.03415173272174</v>
       </c>
       <c r="C11">
         <f>'Todos los Datos (2)'!C11*Hoja1!$K$17+'Todos los Datos (2)'!H11*Hoja1!$K$18+'Todos los Datos (2)'!M11*Hoja1!$K$19+'Todos los Datos (2)'!R11*Hoja1!$K$20+'Todos los Datos (2)'!W11*Hoja1!$K$21+'Todos los Datos (2)'!AB11*Hoja1!$K$22+'Todos los Datos (2)'!AG11*Hoja1!$K$23+'Todos los Datos (2)'!AL11*Hoja1!$K$24</f>
-        <v>105.78621143391391</v>
+        <v>175.7466452960316</v>
       </c>
       <c r="D11">
         <f>'Todos los Datos (2)'!D11*Hoja1!$K$17+'Todos los Datos (2)'!I11*Hoja1!$K$18+'Todos los Datos (2)'!N11*Hoja1!$K$19+'Todos los Datos (2)'!S11*Hoja1!$K$20+'Todos los Datos (2)'!X11*Hoja1!$K$21+'Todos los Datos (2)'!AC11*Hoja1!$K$22+'Todos los Datos (2)'!AH11*Hoja1!$K$23+'Todos los Datos (2)'!AM11*Hoja1!$K$24</f>
-        <v>121.02219605942034</v>
+        <v>215.52725979091309</v>
       </c>
       <c r="E11">
         <f>'Todos los Datos (2)'!E11*Hoja1!$K$17+'Todos los Datos (2)'!J11*Hoja1!$K$18+'Todos los Datos (2)'!O11*Hoja1!$K$19+'Todos los Datos (2)'!T11*Hoja1!$K$20+'Todos los Datos (2)'!Y11*Hoja1!$K$21+'Todos los Datos (2)'!AD11*Hoja1!$K$22+'Todos los Datos (2)'!AI11*Hoja1!$K$23+'Todos los Datos (2)'!AN11*Hoja1!$K$24</f>
-        <v>115.82811039163408</v>
+        <v>200.27979462891523</v>
       </c>
       <c r="F11">
         <f>'Todos los Datos (2)'!F11*Hoja1!$K$17+'Todos los Datos (2)'!K11*Hoja1!$K$18+'Todos los Datos (2)'!P11*Hoja1!$K$19+'Todos los Datos (2)'!U11*Hoja1!$K$20+'Todos los Datos (2)'!Z11*Hoja1!$K$21+'Todos los Datos (2)'!AE11*Hoja1!$K$22+'Todos los Datos (2)'!AJ11*Hoja1!$K$23+'Todos los Datos (2)'!AO11*Hoja1!$K$24</f>
-        <v>111.49970566847882</v>
+        <v>185.83455285400947</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <f>'Todos los Datos (2)'!B12*Hoja1!$K$17+'Todos los Datos (2)'!G12*Hoja1!$K$18+'Todos los Datos (2)'!L12*Hoja1!$K$19+'Todos los Datos (2)'!Q12*Hoja1!$K$20+'Todos los Datos (2)'!V12*Hoja1!$K$21+'Todos los Datos (2)'!AA12*Hoja1!$K$22+'Todos los Datos (2)'!AF12*Hoja1!$K$23+'Todos los Datos (2)'!AK12*Hoja1!$K$24</f>
-        <v>98.404974317383079</v>
+        <v>170.61349374281775</v>
       </c>
       <c r="C12">
         <f>'Todos los Datos (2)'!C12*Hoja1!$K$17+'Todos los Datos (2)'!H12*Hoja1!$K$18+'Todos los Datos (2)'!M12*Hoja1!$K$19+'Todos los Datos (2)'!R12*Hoja1!$K$20+'Todos los Datos (2)'!W12*Hoja1!$K$21+'Todos los Datos (2)'!AB12*Hoja1!$K$22+'Todos los Datos (2)'!AG12*Hoja1!$K$23+'Todos los Datos (2)'!AL12*Hoja1!$K$24</f>
-        <v>136.52338469856718</v>
+        <v>266.64971884138856</v>
       </c>
       <c r="D12">
         <f>'Todos los Datos (2)'!D12*Hoja1!$K$17+'Todos los Datos (2)'!I12*Hoja1!$K$18+'Todos los Datos (2)'!N12*Hoja1!$K$19+'Todos los Datos (2)'!S12*Hoja1!$K$20+'Todos los Datos (2)'!X12*Hoja1!$K$21+'Todos los Datos (2)'!AC12*Hoja1!$K$22+'Todos los Datos (2)'!AH12*Hoja1!$K$23+'Todos los Datos (2)'!AM12*Hoja1!$K$24</f>
-        <v>144.09299810759663</v>
+        <v>315.57819015484063</v>
       </c>
       <c r="E12">
         <f>'Todos los Datos (2)'!E12*Hoja1!$K$17+'Todos los Datos (2)'!J12*Hoja1!$K$18+'Todos los Datos (2)'!O12*Hoja1!$K$19+'Todos los Datos (2)'!T12*Hoja1!$K$20+'Todos los Datos (2)'!Y12*Hoja1!$K$21+'Todos los Datos (2)'!AD12*Hoja1!$K$22+'Todos los Datos (2)'!AI12*Hoja1!$K$23+'Todos los Datos (2)'!AN12*Hoja1!$K$24</f>
-        <v>148.68883482022167</v>
+        <v>302.46081656813823</v>
       </c>
       <c r="F12">
         <f>'Todos los Datos (2)'!F12*Hoja1!$K$17+'Todos los Datos (2)'!K12*Hoja1!$K$18+'Todos los Datos (2)'!P12*Hoja1!$K$19+'Todos los Datos (2)'!U12*Hoja1!$K$20+'Todos los Datos (2)'!Z12*Hoja1!$K$21+'Todos los Datos (2)'!AE12*Hoja1!$K$22+'Todos los Datos (2)'!AJ12*Hoja1!$K$23+'Todos los Datos (2)'!AO12*Hoja1!$K$24</f>
-        <v>149.77020816436874</v>
+        <v>274.70612550281589</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -13792,23 +14024,23 @@
       </c>
       <c r="B13">
         <f>'Todos los Datos (2)'!B13*Hoja1!$K$17+'Todos los Datos (2)'!G13*Hoja1!$K$18+'Todos los Datos (2)'!L13*Hoja1!$K$19+'Todos los Datos (2)'!Q13*Hoja1!$K$20+'Todos los Datos (2)'!V13*Hoja1!$K$21+'Todos los Datos (2)'!AA13*Hoja1!$K$22+'Todos los Datos (2)'!AF13*Hoja1!$K$23+'Todos los Datos (2)'!AK13*Hoja1!$K$24</f>
-        <v>169.99779904205928</v>
+        <v>314.23195215284989</v>
       </c>
       <c r="C13">
         <f>'Todos los Datos (2)'!C13*Hoja1!$K$17+'Todos los Datos (2)'!H13*Hoja1!$K$18+'Todos los Datos (2)'!M13*Hoja1!$K$19+'Todos los Datos (2)'!R13*Hoja1!$K$20+'Todos los Datos (2)'!W13*Hoja1!$K$21+'Todos los Datos (2)'!AB13*Hoja1!$K$22+'Todos los Datos (2)'!AG13*Hoja1!$K$23+'Todos los Datos (2)'!AL13*Hoja1!$K$24</f>
-        <v>206.41841258528711</v>
+        <v>392.3482294176971</v>
       </c>
       <c r="D13">
         <f>'Todos los Datos (2)'!D13*Hoja1!$K$17+'Todos los Datos (2)'!I13*Hoja1!$K$18+'Todos los Datos (2)'!N13*Hoja1!$K$19+'Todos los Datos (2)'!S13*Hoja1!$K$20+'Todos los Datos (2)'!X13*Hoja1!$K$21+'Todos los Datos (2)'!AC13*Hoja1!$K$22+'Todos los Datos (2)'!AH13*Hoja1!$K$23+'Todos los Datos (2)'!AM13*Hoja1!$K$24</f>
-        <v>212.91647888652489</v>
+        <v>434.71182764492733</v>
       </c>
       <c r="E13">
         <f>'Todos los Datos (2)'!E13*Hoja1!$K$17+'Todos los Datos (2)'!J13*Hoja1!$K$18+'Todos los Datos (2)'!O13*Hoja1!$K$19+'Todos los Datos (2)'!T13*Hoja1!$K$20+'Todos los Datos (2)'!Y13*Hoja1!$K$21+'Todos los Datos (2)'!AD13*Hoja1!$K$22+'Todos los Datos (2)'!AI13*Hoja1!$K$23+'Todos los Datos (2)'!AN13*Hoja1!$K$24</f>
-        <v>207.25687275318879</v>
+        <v>421.29054162159235</v>
       </c>
       <c r="F13">
         <f>'Todos los Datos (2)'!F13*Hoja1!$K$17+'Todos los Datos (2)'!K13*Hoja1!$K$18+'Todos los Datos (2)'!P13*Hoja1!$K$19+'Todos los Datos (2)'!U13*Hoja1!$K$20+'Todos los Datos (2)'!Z13*Hoja1!$K$21+'Todos los Datos (2)'!AE13*Hoja1!$K$22+'Todos los Datos (2)'!AJ13*Hoja1!$K$23+'Todos los Datos (2)'!AO13*Hoja1!$K$24</f>
-        <v>220.41021663714588</v>
+        <v>464.33515236040625</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -13817,74 +14049,74 @@
       </c>
       <c r="B14">
         <f>'Todos los Datos (2)'!B14*Hoja1!$K$17+'Todos los Datos (2)'!G14*Hoja1!$K$18+'Todos los Datos (2)'!L14*Hoja1!$K$19+'Todos los Datos (2)'!Q14*Hoja1!$K$20+'Todos los Datos (2)'!V14*Hoja1!$K$21+'Todos los Datos (2)'!AA14*Hoja1!$K$22+'Todos los Datos (2)'!AF14*Hoja1!$K$23+'Todos los Datos (2)'!AK14*Hoja1!$K$24</f>
-        <v>110.44696675442003</v>
+        <v>198.26550811340488</v>
       </c>
       <c r="C14">
         <f>'Todos los Datos (2)'!C14*Hoja1!$K$17+'Todos los Datos (2)'!H14*Hoja1!$K$18+'Todos los Datos (2)'!M14*Hoja1!$K$19+'Todos los Datos (2)'!R14*Hoja1!$K$20+'Todos los Datos (2)'!W14*Hoja1!$K$21+'Todos los Datos (2)'!AB14*Hoja1!$K$22+'Todos los Datos (2)'!AG14*Hoja1!$K$23+'Todos los Datos (2)'!AL14*Hoja1!$K$24</f>
-        <v>132.88881216463108</v>
+        <v>230.66625938013681</v>
       </c>
       <c r="D14">
         <f>'Todos los Datos (2)'!D14*Hoja1!$K$17+'Todos los Datos (2)'!I14*Hoja1!$K$18+'Todos los Datos (2)'!N14*Hoja1!$K$19+'Todos los Datos (2)'!S14*Hoja1!$K$20+'Todos los Datos (2)'!X14*Hoja1!$K$21+'Todos los Datos (2)'!AC14*Hoja1!$K$22+'Todos los Datos (2)'!AH14*Hoja1!$K$23+'Todos los Datos (2)'!AM14*Hoja1!$K$24</f>
-        <v>124.50908463165163</v>
+        <v>227.71930594983829</v>
       </c>
       <c r="E14">
         <f>'Todos los Datos (2)'!E14*Hoja1!$K$17+'Todos los Datos (2)'!J14*Hoja1!$K$18+'Todos los Datos (2)'!O14*Hoja1!$K$19+'Todos los Datos (2)'!T14*Hoja1!$K$20+'Todos los Datos (2)'!Y14*Hoja1!$K$21+'Todos los Datos (2)'!AD14*Hoja1!$K$22+'Todos los Datos (2)'!AI14*Hoja1!$K$23+'Todos los Datos (2)'!AN14*Hoja1!$K$24</f>
-        <v>132.13355775178744</v>
+        <v>252.50014120192085</v>
       </c>
       <c r="F14">
         <f>'Todos los Datos (2)'!F14*Hoja1!$K$17+'Todos los Datos (2)'!K14*Hoja1!$K$18+'Todos los Datos (2)'!P14*Hoja1!$K$19+'Todos los Datos (2)'!U14*Hoja1!$K$20+'Todos los Datos (2)'!Z14*Hoja1!$K$21+'Todos los Datos (2)'!AE14*Hoja1!$K$22+'Todos los Datos (2)'!AJ14*Hoja1!$K$23+'Todos los Datos (2)'!AO14*Hoja1!$K$24</f>
-        <v>136.55719074130019</v>
+        <v>250.30237288757877</v>
       </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B15">
         <f>'Todos los Datos (2)'!B15*Hoja1!$K$17+'Todos los Datos (2)'!G15*Hoja1!$K$18+'Todos los Datos (2)'!L15*Hoja1!$K$19+'Todos los Datos (2)'!Q15*Hoja1!$K$20+'Todos los Datos (2)'!V15*Hoja1!$K$21+'Todos los Datos (2)'!AA15*Hoja1!$K$22+'Todos los Datos (2)'!AF15*Hoja1!$K$23+'Todos los Datos (2)'!AK15*Hoja1!$K$24</f>
-        <v>95.303338639156976</v>
+        <v>145.77624556420346</v>
       </c>
       <c r="C15">
         <f>'Todos los Datos (2)'!C15*Hoja1!$K$17+'Todos los Datos (2)'!H15*Hoja1!$K$18+'Todos los Datos (2)'!M15*Hoja1!$K$19+'Todos los Datos (2)'!R15*Hoja1!$K$20+'Todos los Datos (2)'!W15*Hoja1!$K$21+'Todos los Datos (2)'!AB15*Hoja1!$K$22+'Todos los Datos (2)'!AG15*Hoja1!$K$23+'Todos los Datos (2)'!AL15*Hoja1!$K$24</f>
-        <v>118.474340633878</v>
+        <v>183.07148040890073</v>
       </c>
       <c r="D15">
         <f>'Todos los Datos (2)'!D15*Hoja1!$K$17+'Todos los Datos (2)'!I15*Hoja1!$K$18+'Todos los Datos (2)'!N15*Hoja1!$K$19+'Todos los Datos (2)'!S15*Hoja1!$K$20+'Todos los Datos (2)'!X15*Hoja1!$K$21+'Todos los Datos (2)'!AC15*Hoja1!$K$22+'Todos los Datos (2)'!AH15*Hoja1!$K$23+'Todos los Datos (2)'!AM15*Hoja1!$K$24</f>
-        <v>109.5081702967903</v>
+        <v>173.42277829688612</v>
       </c>
       <c r="E15">
         <f>'Todos los Datos (2)'!E15*Hoja1!$K$17+'Todos los Datos (2)'!J15*Hoja1!$K$18+'Todos los Datos (2)'!O15*Hoja1!$K$19+'Todos los Datos (2)'!T15*Hoja1!$K$20+'Todos los Datos (2)'!Y15*Hoja1!$K$21+'Todos los Datos (2)'!AD15*Hoja1!$K$22+'Todos los Datos (2)'!AI15*Hoja1!$K$23+'Todos los Datos (2)'!AN15*Hoja1!$K$24</f>
-        <v>102.35538272450685</v>
+        <v>174.50029403919939</v>
       </c>
       <c r="F15">
         <f>'Todos los Datos (2)'!F15*Hoja1!$K$17+'Todos los Datos (2)'!K15*Hoja1!$K$18+'Todos los Datos (2)'!P15*Hoja1!$K$19+'Todos los Datos (2)'!U15*Hoja1!$K$20+'Todos los Datos (2)'!Z15*Hoja1!$K$21+'Todos los Datos (2)'!AE15*Hoja1!$K$22+'Todos los Datos (2)'!AJ15*Hoja1!$K$23+'Todos los Datos (2)'!AO15*Hoja1!$K$24</f>
-        <v>95.706312586891258</v>
+        <v>149.29121343278842</v>
       </c>
       <c r="K15" cm="1">
         <f t="array" ref="K15:R15">TRANSPOSE(INDEX(IF(ISNUMBER(IFERROR(FIND(J17:J24,IF(IFERROR(FIND(B$1,'Todos los Datos (2)'!B1:AO1),0)&lt;&gt;0,'Todos los Datos (2)'!B1:AO1)),"")),1,0)*$K$17:$K$24,_xlfn.SEQUENCE(8),_xlfn.SEQUENCE(8)*5-4))</f>
-        <v>0.25</v>
+        <v>8.8834166558848858E-4</v>
       </c>
       <c r="L15">
-        <v>0.05</v>
+        <v>1.837315589343563E-2</v>
       </c>
       <c r="M15">
-        <v>0.3</v>
+        <v>0.42496023238732389</v>
       </c>
       <c r="N15">
-        <v>0.15</v>
+        <v>0.11221089961793768</v>
       </c>
       <c r="O15">
-        <v>0.05</v>
+        <v>5.6231867720128684E-2</v>
       </c>
       <c r="P15">
-        <v>0.05</v>
+        <v>1.110458858212284E-2</v>
       </c>
       <c r="Q15">
-        <v>0.1</v>
+        <v>0.37623091413346282</v>
       </c>
       <c r="R15">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -13893,24 +14125,28 @@
       </c>
       <c r="B16">
         <f>'Todos los Datos (2)'!B16*Hoja1!$K$17+'Todos los Datos (2)'!G16*Hoja1!$K$18+'Todos los Datos (2)'!L16*Hoja1!$K$19+'Todos los Datos (2)'!Q16*Hoja1!$K$20+'Todos los Datos (2)'!V16*Hoja1!$K$21+'Todos los Datos (2)'!AA16*Hoja1!$K$22+'Todos los Datos (2)'!AF16*Hoja1!$K$23+'Todos los Datos (2)'!AK16*Hoja1!$K$24</f>
-        <v>34.602076124567475</v>
+        <v>21.979661933396123</v>
       </c>
       <c r="C16">
         <f>'Todos los Datos (2)'!C16*Hoja1!$K$17+'Todos los Datos (2)'!H16*Hoja1!$K$18+'Todos los Datos (2)'!M16*Hoja1!$K$19+'Todos los Datos (2)'!R16*Hoja1!$K$20+'Todos los Datos (2)'!W16*Hoja1!$K$21+'Todos los Datos (2)'!AB16*Hoja1!$K$22+'Todos los Datos (2)'!AG16*Hoja1!$K$23+'Todos los Datos (2)'!AL16*Hoja1!$K$24</f>
-        <v>49.019607843137251</v>
+        <v>45.501434335526447</v>
       </c>
       <c r="D16">
         <f>'Todos los Datos (2)'!D16*Hoja1!$K$17+'Todos los Datos (2)'!I16*Hoja1!$K$18+'Todos los Datos (2)'!N16*Hoja1!$K$19+'Todos los Datos (2)'!S16*Hoja1!$K$20+'Todos los Datos (2)'!X16*Hoja1!$K$21+'Todos los Datos (2)'!AC16*Hoja1!$K$22+'Todos los Datos (2)'!AH16*Hoja1!$K$23+'Todos los Datos (2)'!AM16*Hoja1!$K$24</f>
-        <v>108.99653979238754</v>
+        <v>52.130748282087318</v>
       </c>
       <c r="E16">
         <f>'Todos los Datos (2)'!E16*Hoja1!$K$17+'Todos los Datos (2)'!J16*Hoja1!$K$18+'Todos los Datos (2)'!O16*Hoja1!$K$19+'Todos los Datos (2)'!T16*Hoja1!$K$20+'Todos los Datos (2)'!Y16*Hoja1!$K$21+'Todos los Datos (2)'!AD16*Hoja1!$K$22+'Todos los Datos (2)'!AI16*Hoja1!$K$23+'Todos los Datos (2)'!AN16*Hoja1!$K$24</f>
-        <v>77.277970011534009</v>
+        <v>73.038101777740266</v>
       </c>
       <c r="F16">
         <f>'Todos los Datos (2)'!F16*Hoja1!$K$17+'Todos los Datos (2)'!K16*Hoja1!$K$18+'Todos los Datos (2)'!P16*Hoja1!$K$19+'Todos los Datos (2)'!U16*Hoja1!$K$20+'Todos los Datos (2)'!Z16*Hoja1!$K$21+'Todos los Datos (2)'!AE16*Hoja1!$K$22+'Todos los Datos (2)'!AJ16*Hoja1!$K$23+'Todos los Datos (2)'!AO16*Hoja1!$K$24</f>
-        <v>90.542099192618224</v>
-      </c>
+        <v>71.531472530610557</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="K16" s="20"/>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -13918,48 +14154,48 @@
       </c>
       <c r="B17">
         <f>'Todos los Datos (2)'!B17*Hoja1!$K$17+'Todos los Datos (2)'!G17*Hoja1!$K$18+'Todos los Datos (2)'!L17*Hoja1!$K$19+'Todos los Datos (2)'!Q17*Hoja1!$K$20+'Todos los Datos (2)'!V17*Hoja1!$K$21+'Todos los Datos (2)'!AA17*Hoja1!$K$22+'Todos los Datos (2)'!AF17*Hoja1!$K$23+'Todos los Datos (2)'!AK17*Hoja1!$K$24</f>
-        <v>132.81724347298118</v>
+        <v>150.34436365175426</v>
       </c>
       <c r="C17">
         <f>'Todos los Datos (2)'!C17*Hoja1!$K$17+'Todos los Datos (2)'!H17*Hoja1!$K$18+'Todos los Datos (2)'!M17*Hoja1!$K$19+'Todos los Datos (2)'!R17*Hoja1!$K$20+'Todos los Datos (2)'!W17*Hoja1!$K$21+'Todos los Datos (2)'!AB17*Hoja1!$K$22+'Todos los Datos (2)'!AG17*Hoja1!$K$23+'Todos los Datos (2)'!AL17*Hoja1!$K$24</f>
-        <v>103.21797207043109</v>
+        <v>117.02752901720447</v>
       </c>
       <c r="D17">
         <f>'Todos los Datos (2)'!D17*Hoja1!$K$17+'Todos los Datos (2)'!I17*Hoja1!$K$18+'Todos los Datos (2)'!N17*Hoja1!$K$19+'Todos los Datos (2)'!S17*Hoja1!$K$20+'Todos los Datos (2)'!X17*Hoja1!$K$21+'Todos los Datos (2)'!AC17*Hoja1!$K$22+'Todos los Datos (2)'!AH17*Hoja1!$K$23+'Todos los Datos (2)'!AM17*Hoja1!$K$24</f>
-        <v>70.582877959927146</v>
+        <v>65.902728282524691</v>
       </c>
       <c r="E17">
         <f>'Todos los Datos (2)'!E17*Hoja1!$K$17+'Todos los Datos (2)'!J17*Hoja1!$K$18+'Todos los Datos (2)'!O17*Hoja1!$K$19+'Todos los Datos (2)'!T17*Hoja1!$K$20+'Todos los Datos (2)'!Y17*Hoja1!$K$21+'Todos los Datos (2)'!AD17*Hoja1!$K$22+'Todos los Datos (2)'!AI17*Hoja1!$K$23+'Todos los Datos (2)'!AN17*Hoja1!$K$24</f>
-        <v>85.761991499696421</v>
+        <v>82.570410223227356</v>
       </c>
       <c r="F17">
         <f>'Todos los Datos (2)'!F17*Hoja1!$K$17+'Todos los Datos (2)'!K17*Hoja1!$K$18+'Todos los Datos (2)'!P17*Hoja1!$K$19+'Todos los Datos (2)'!U17*Hoja1!$K$20+'Todos los Datos (2)'!Z17*Hoja1!$K$21+'Todos los Datos (2)'!AE17*Hoja1!$K$22+'Todos los Datos (2)'!AJ17*Hoja1!$K$23+'Todos los Datos (2)'!AO17*Hoja1!$K$24</f>
-        <v>81.967213114754102</v>
-      </c>
-      <c r="J17" t="s">
+        <v>94.940954048694636</v>
+      </c>
+      <c r="J17" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="9">
-        <v>0.25</v>
+      <c r="K17" s="16">
+        <v>8.8834166558848858E-4</v>
       </c>
       <c r="M17" cm="1">
         <f t="array" ref="M17:BH24">IFERROR(IF(FIND(J17:J24,'Todos los Datos'!$B$1:$AW$1)=8,1,0),0)*$K$17:$K$24</f>
         <v>0</v>
       </c>
       <c r="N17">
-        <v>0.25</v>
+        <v>8.8834166558848858E-4</v>
       </c>
       <c r="O17">
-        <v>0.25</v>
+        <v>8.8834166558848858E-4</v>
       </c>
       <c r="P17">
-        <v>0.25</v>
+        <v>8.8834166558848858E-4</v>
       </c>
       <c r="Q17">
-        <v>0.25</v>
+        <v>8.8834166558848858E-4</v>
       </c>
       <c r="R17">
-        <v>0.25</v>
+        <v>8.8834166558848858E-4</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -14094,29 +14330,29 @@
       </c>
       <c r="B18">
         <f>'Todos los Datos (2)'!B18*Hoja1!$K$17+'Todos los Datos (2)'!G18*Hoja1!$K$18+'Todos los Datos (2)'!L18*Hoja1!$K$19+'Todos los Datos (2)'!Q18*Hoja1!$K$20+'Todos los Datos (2)'!V18*Hoja1!$K$21+'Todos los Datos (2)'!AA18*Hoja1!$K$22+'Todos los Datos (2)'!AF18*Hoja1!$K$23+'Todos los Datos (2)'!AK18*Hoja1!$K$24</f>
-        <v>93.170385991599119</v>
+        <v>161.87453104515487</v>
       </c>
       <c r="C18">
         <f>'Todos los Datos (2)'!C18*Hoja1!$K$17+'Todos los Datos (2)'!H18*Hoja1!$K$18+'Todos los Datos (2)'!M18*Hoja1!$K$19+'Todos los Datos (2)'!R18*Hoja1!$K$20+'Todos los Datos (2)'!W18*Hoja1!$K$21+'Todos los Datos (2)'!AB18*Hoja1!$K$22+'Todos los Datos (2)'!AG18*Hoja1!$K$23+'Todos los Datos (2)'!AL18*Hoja1!$K$24</f>
-        <v>137.59485575011669</v>
+        <v>267.28700779264017</v>
       </c>
       <c r="D18">
         <f>'Todos los Datos (2)'!D18*Hoja1!$K$17+'Todos los Datos (2)'!I18*Hoja1!$K$18+'Todos los Datos (2)'!N18*Hoja1!$K$19+'Todos los Datos (2)'!S18*Hoja1!$K$20+'Todos los Datos (2)'!X18*Hoja1!$K$21+'Todos los Datos (2)'!AC18*Hoja1!$K$22+'Todos los Datos (2)'!AH18*Hoja1!$K$23+'Todos los Datos (2)'!AM18*Hoja1!$K$24</f>
-        <v>119.87692520440442</v>
+        <v>246.00314419005574</v>
       </c>
       <c r="E18">
         <f>'Todos los Datos (2)'!E18*Hoja1!$K$17+'Todos los Datos (2)'!J18*Hoja1!$K$18+'Todos los Datos (2)'!O18*Hoja1!$K$19+'Todos los Datos (2)'!T18*Hoja1!$K$20+'Todos los Datos (2)'!Y18*Hoja1!$K$21+'Todos los Datos (2)'!AD18*Hoja1!$K$22+'Todos los Datos (2)'!AI18*Hoja1!$K$23+'Todos los Datos (2)'!AN18*Hoja1!$K$24</f>
-        <v>132.58197783962248</v>
+        <v>282.05227484512125</v>
       </c>
       <c r="F18">
         <f>'Todos los Datos (2)'!F18*Hoja1!$K$17+'Todos los Datos (2)'!K18*Hoja1!$K$18+'Todos los Datos (2)'!P18*Hoja1!$K$19+'Todos los Datos (2)'!U18*Hoja1!$K$20+'Todos los Datos (2)'!Z18*Hoja1!$K$21+'Todos los Datos (2)'!AE18*Hoja1!$K$22+'Todos los Datos (2)'!AJ18*Hoja1!$K$23+'Todos los Datos (2)'!AO18*Hoja1!$K$24</f>
-        <v>147.01560906466614</v>
-      </c>
-      <c r="J18" t="s">
-        <v>98</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0.05</v>
+        <v>305.23796885345729</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="K18" s="16">
+        <v>1.837315589343563E-2</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -14140,19 +14376,19 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0.05</v>
+        <v>1.837315589343563E-2</v>
       </c>
       <c r="U18">
-        <v>0.05</v>
+        <v>1.837315589343563E-2</v>
       </c>
       <c r="V18">
-        <v>0.05</v>
+        <v>1.837315589343563E-2</v>
       </c>
       <c r="W18">
-        <v>0.05</v>
+        <v>1.837315589343563E-2</v>
       </c>
       <c r="X18">
-        <v>0.05</v>
+        <v>1.837315589343563E-2</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -14269,29 +14505,29 @@
       </c>
       <c r="B19">
         <f>'Todos los Datos (2)'!B19*Hoja1!$K$17+'Todos los Datos (2)'!G19*Hoja1!$K$18+'Todos los Datos (2)'!L19*Hoja1!$K$19+'Todos los Datos (2)'!Q19*Hoja1!$K$20+'Todos los Datos (2)'!V19*Hoja1!$K$21+'Todos los Datos (2)'!AA19*Hoja1!$K$22+'Todos los Datos (2)'!AF19*Hoja1!$K$23+'Todos los Datos (2)'!AK19*Hoja1!$K$24</f>
-        <v>100.87116001834019</v>
+        <v>80.413041480567429</v>
       </c>
       <c r="C19">
         <f>'Todos los Datos (2)'!C19*Hoja1!$K$17+'Todos los Datos (2)'!H19*Hoja1!$K$18+'Todos los Datos (2)'!M19*Hoja1!$K$19+'Todos los Datos (2)'!R19*Hoja1!$K$20+'Todos los Datos (2)'!W19*Hoja1!$K$21+'Todos los Datos (2)'!AB19*Hoja1!$K$22+'Todos los Datos (2)'!AG19*Hoja1!$K$23+'Todos los Datos (2)'!AL19*Hoja1!$K$24</f>
-        <v>88.262265016047692</v>
+        <v>111.52343689314559</v>
       </c>
       <c r="D19">
         <f>'Todos los Datos (2)'!D19*Hoja1!$K$17+'Todos los Datos (2)'!I19*Hoja1!$K$18+'Todos los Datos (2)'!N19*Hoja1!$K$19+'Todos los Datos (2)'!S19*Hoja1!$K$20+'Todos los Datos (2)'!X19*Hoja1!$K$21+'Todos los Datos (2)'!AC19*Hoja1!$K$22+'Todos los Datos (2)'!AH19*Hoja1!$K$23+'Todos los Datos (2)'!AM19*Hoja1!$K$24</f>
-        <v>73.93397524071527</v>
+        <v>107.09400022530397</v>
       </c>
       <c r="E19">
         <f>'Todos los Datos (2)'!E19*Hoja1!$K$17+'Todos los Datos (2)'!J19*Hoja1!$K$18+'Todos los Datos (2)'!O19*Hoja1!$K$19+'Todos los Datos (2)'!T19*Hoja1!$K$20+'Todos los Datos (2)'!Y19*Hoja1!$K$21+'Todos los Datos (2)'!AD19*Hoja1!$K$22+'Todos los Datos (2)'!AI19*Hoja1!$K$23+'Todos los Datos (2)'!AN19*Hoja1!$K$24</f>
-        <v>141.56350298028428</v>
+        <v>187.16049759988755</v>
       </c>
       <c r="F19">
         <f>'Todos los Datos (2)'!F19*Hoja1!$K$17+'Todos los Datos (2)'!K19*Hoja1!$K$18+'Todos los Datos (2)'!P19*Hoja1!$K$19+'Todos los Datos (2)'!U19*Hoja1!$K$20+'Todos los Datos (2)'!Z19*Hoja1!$K$21+'Todos los Datos (2)'!AE19*Hoja1!$K$22+'Todos los Datos (2)'!AJ19*Hoja1!$K$23+'Todos los Datos (2)'!AO19*Hoja1!$K$24</f>
-        <v>138.69784502521779</v>
-      </c>
-      <c r="J19" t="s">
-        <v>99</v>
-      </c>
-      <c r="K19" s="9">
-        <v>0.3</v>
+        <v>175.79167486981308</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="K19" s="16">
+        <v>0.42496023238732389</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -14333,19 +14569,19 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>0.3</v>
+        <v>0.42496023238732389</v>
       </c>
       <c r="AA19">
-        <v>0.3</v>
+        <v>0.42496023238732389</v>
       </c>
       <c r="AB19">
-        <v>0.3</v>
+        <v>0.42496023238732389</v>
       </c>
       <c r="AC19">
-        <v>0.3</v>
+        <v>0.42496023238732389</v>
       </c>
       <c r="AD19">
-        <v>0.3</v>
+        <v>0.42496023238732389</v>
       </c>
       <c r="AE19">
         <v>0</v>
@@ -14444,29 +14680,29 @@
       </c>
       <c r="B20">
         <f>'Todos los Datos (2)'!B20*Hoja1!$K$17+'Todos los Datos (2)'!G20*Hoja1!$K$18+'Todos los Datos (2)'!L20*Hoja1!$K$19+'Todos los Datos (2)'!Q20*Hoja1!$K$20+'Todos los Datos (2)'!V20*Hoja1!$K$21+'Todos los Datos (2)'!AA20*Hoja1!$K$22+'Todos los Datos (2)'!AF20*Hoja1!$K$23+'Todos los Datos (2)'!AK20*Hoja1!$K$24</f>
-        <v>83.064969585441901</v>
+        <v>156.33078517111227</v>
       </c>
       <c r="C20">
         <f>'Todos los Datos (2)'!C20*Hoja1!$K$17+'Todos los Datos (2)'!H20*Hoja1!$K$18+'Todos los Datos (2)'!M20*Hoja1!$K$19+'Todos los Datos (2)'!R20*Hoja1!$K$20+'Todos los Datos (2)'!W20*Hoja1!$K$21+'Todos los Datos (2)'!AB20*Hoja1!$K$22+'Todos los Datos (2)'!AG20*Hoja1!$K$23+'Todos los Datos (2)'!AL20*Hoja1!$K$24</f>
-        <v>115.35381417301367</v>
+        <v>215.20136463209923</v>
       </c>
       <c r="D20">
         <f>'Todos los Datos (2)'!D20*Hoja1!$K$17+'Todos los Datos (2)'!I20*Hoja1!$K$18+'Todos los Datos (2)'!N20*Hoja1!$K$19+'Todos los Datos (2)'!S20*Hoja1!$K$20+'Todos los Datos (2)'!X20*Hoja1!$K$21+'Todos los Datos (2)'!AC20*Hoja1!$K$22+'Todos los Datos (2)'!AH20*Hoja1!$K$23+'Todos los Datos (2)'!AM20*Hoja1!$K$24</f>
-        <v>125.15122084206581</v>
+        <v>242.68929036732672</v>
       </c>
       <c r="E20">
         <f>'Todos los Datos (2)'!E20*Hoja1!$K$17+'Todos los Datos (2)'!J20*Hoja1!$K$18+'Todos los Datos (2)'!O20*Hoja1!$K$19+'Todos los Datos (2)'!T20*Hoja1!$K$20+'Todos los Datos (2)'!Y20*Hoja1!$K$21+'Todos los Datos (2)'!AD20*Hoja1!$K$22+'Todos los Datos (2)'!AI20*Hoja1!$K$23+'Todos los Datos (2)'!AN20*Hoja1!$K$24</f>
-        <v>121.06186849324405</v>
+        <v>250.75504752289376</v>
       </c>
       <c r="F20">
         <f>'Todos los Datos (2)'!F20*Hoja1!$K$17+'Todos los Datos (2)'!K20*Hoja1!$K$18+'Todos los Datos (2)'!P20*Hoja1!$K$19+'Todos los Datos (2)'!U20*Hoja1!$K$20+'Todos los Datos (2)'!Z20*Hoja1!$K$21+'Todos los Datos (2)'!AE20*Hoja1!$K$22+'Todos los Datos (2)'!AJ20*Hoja1!$K$23+'Todos los Datos (2)'!AO20*Hoja1!$K$24</f>
-        <v>136.90810884492834</v>
-      </c>
-      <c r="J20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0.15</v>
+        <v>275.52224902924581</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="16">
+        <v>0.11221089961793768</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -14526,19 +14762,19 @@
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.15</v>
+        <v>0.11221089961793768</v>
       </c>
       <c r="AG20">
-        <v>0.15</v>
+        <v>0.11221089961793768</v>
       </c>
       <c r="AH20">
-        <v>0.15</v>
+        <v>0.11221089961793768</v>
       </c>
       <c r="AI20">
-        <v>0.15</v>
+        <v>0.11221089961793768</v>
       </c>
       <c r="AJ20">
-        <v>0.15</v>
+        <v>0.11221089961793768</v>
       </c>
       <c r="AK20">
         <v>0</v>
@@ -14619,29 +14855,29 @@
       </c>
       <c r="B21">
         <f>'Todos los Datos (2)'!B21*Hoja1!$K$17+'Todos los Datos (2)'!G21*Hoja1!$K$18+'Todos los Datos (2)'!L21*Hoja1!$K$19+'Todos los Datos (2)'!Q21*Hoja1!$K$20+'Todos los Datos (2)'!V21*Hoja1!$K$21+'Todos los Datos (2)'!AA21*Hoja1!$K$22+'Todos los Datos (2)'!AF21*Hoja1!$K$23+'Todos los Datos (2)'!AK21*Hoja1!$K$24</f>
-        <v>79.263067694944311</v>
+        <v>141.60919187892932</v>
       </c>
       <c r="C21">
         <f>'Todos los Datos (2)'!C21*Hoja1!$K$17+'Todos los Datos (2)'!H21*Hoja1!$K$18+'Todos los Datos (2)'!M21*Hoja1!$K$19+'Todos los Datos (2)'!R21*Hoja1!$K$20+'Todos los Datos (2)'!W21*Hoja1!$K$21+'Todos los Datos (2)'!AB21*Hoja1!$K$22+'Todos los Datos (2)'!AG21*Hoja1!$K$23+'Todos los Datos (2)'!AL21*Hoja1!$K$24</f>
-        <v>135.38988860325625</v>
+        <v>225.5777373946928</v>
       </c>
       <c r="D21">
         <f>'Todos los Datos (2)'!D21*Hoja1!$K$17+'Todos los Datos (2)'!I21*Hoja1!$K$18+'Todos los Datos (2)'!N21*Hoja1!$K$19+'Todos los Datos (2)'!S21*Hoja1!$K$20+'Todos los Datos (2)'!X21*Hoja1!$K$21+'Todos los Datos (2)'!AC21*Hoja1!$K$22+'Todos los Datos (2)'!AH21*Hoja1!$K$23+'Todos los Datos (2)'!AM21*Hoja1!$K$24</f>
-        <v>122.10796915167094</v>
+        <v>254.52021096511967</v>
       </c>
       <c r="E21">
         <f>'Todos los Datos (2)'!E21*Hoja1!$K$17+'Todos los Datos (2)'!J21*Hoja1!$K$18+'Todos los Datos (2)'!O21*Hoja1!$K$19+'Todos los Datos (2)'!T21*Hoja1!$K$20+'Todos los Datos (2)'!Y21*Hoja1!$K$21+'Todos los Datos (2)'!AD21*Hoja1!$K$22+'Todos los Datos (2)'!AI21*Hoja1!$K$23+'Todos los Datos (2)'!AN21*Hoja1!$K$24</f>
-        <v>116.10968294772921</v>
+        <v>219.81964212534015</v>
       </c>
       <c r="F21">
         <f>'Todos los Datos (2)'!F21*Hoja1!$K$17+'Todos los Datos (2)'!K21*Hoja1!$K$18+'Todos los Datos (2)'!P21*Hoja1!$K$19+'Todos los Datos (2)'!U21*Hoja1!$K$20+'Todos los Datos (2)'!Z21*Hoja1!$K$21+'Todos los Datos (2)'!AE21*Hoja1!$K$22+'Todos los Datos (2)'!AJ21*Hoja1!$K$23+'Todos los Datos (2)'!AO21*Hoja1!$K$24</f>
-        <v>104.54155955441303</v>
-      </c>
-      <c r="J21" t="s">
-        <v>101</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0.05</v>
+        <v>182.03852507222371</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="K21" s="16">
+        <v>5.6231867720128684E-2</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -14719,19 +14955,19 @@
         <v>0</v>
       </c>
       <c r="AL21">
-        <v>0.05</v>
+        <v>5.6231867720128684E-2</v>
       </c>
       <c r="AM21">
-        <v>0.05</v>
+        <v>5.6231867720128684E-2</v>
       </c>
       <c r="AN21">
-        <v>0.05</v>
+        <v>5.6231867720128684E-2</v>
       </c>
       <c r="AO21">
-        <v>0.05</v>
+        <v>5.6231867720128684E-2</v>
       </c>
       <c r="AP21">
-        <v>0.05</v>
+        <v>5.6231867720128684E-2</v>
       </c>
       <c r="AQ21">
         <v>0</v>
@@ -14794,29 +15030,29 @@
       </c>
       <c r="B22">
         <f>'Todos los Datos (2)'!B22*Hoja1!$K$17+'Todos los Datos (2)'!G22*Hoja1!$K$18+'Todos los Datos (2)'!L22*Hoja1!$K$19+'Todos los Datos (2)'!Q22*Hoja1!$K$20+'Todos los Datos (2)'!V22*Hoja1!$K$21+'Todos los Datos (2)'!AA22*Hoja1!$K$22+'Todos los Datos (2)'!AF22*Hoja1!$K$23+'Todos los Datos (2)'!AK22*Hoja1!$K$24</f>
-        <v>96.470588235294116</v>
+        <v>143.61970079806289</v>
       </c>
       <c r="C22">
         <f>'Todos los Datos (2)'!C22*Hoja1!$K$17+'Todos los Datos (2)'!H22*Hoja1!$K$18+'Todos los Datos (2)'!M22*Hoja1!$K$19+'Todos los Datos (2)'!R22*Hoja1!$K$20+'Todos los Datos (2)'!W22*Hoja1!$K$21+'Todos los Datos (2)'!AB22*Hoja1!$K$22+'Todos los Datos (2)'!AG22*Hoja1!$K$23+'Todos los Datos (2)'!AL22*Hoja1!$K$24</f>
-        <v>142.05882352941174</v>
+        <v>211.20019270710537</v>
       </c>
       <c r="D22">
         <f>'Todos los Datos (2)'!D22*Hoja1!$K$17+'Todos los Datos (2)'!I22*Hoja1!$K$18+'Todos los Datos (2)'!N22*Hoja1!$K$19+'Todos los Datos (2)'!S22*Hoja1!$K$20+'Todos los Datos (2)'!X22*Hoja1!$K$21+'Todos los Datos (2)'!AC22*Hoja1!$K$22+'Todos los Datos (2)'!AH22*Hoja1!$K$23+'Todos los Datos (2)'!AM22*Hoja1!$K$24</f>
-        <v>166.61764705882354</v>
+        <v>301.75077471745101</v>
       </c>
       <c r="E22">
         <f>'Todos los Datos (2)'!E22*Hoja1!$K$17+'Todos los Datos (2)'!J22*Hoja1!$K$18+'Todos los Datos (2)'!O22*Hoja1!$K$19+'Todos los Datos (2)'!T22*Hoja1!$K$20+'Todos los Datos (2)'!Y22*Hoja1!$K$21+'Todos los Datos (2)'!AD22*Hoja1!$K$22+'Todos los Datos (2)'!AI22*Hoja1!$K$23+'Todos los Datos (2)'!AN22*Hoja1!$K$24</f>
-        <v>170.4411764705882</v>
+        <v>291.17355452912449</v>
       </c>
       <c r="F22">
         <f>'Todos los Datos (2)'!F22*Hoja1!$K$17+'Todos los Datos (2)'!K22*Hoja1!$K$18+'Todos los Datos (2)'!P22*Hoja1!$K$19+'Todos los Datos (2)'!U22*Hoja1!$K$20+'Todos los Datos (2)'!Z22*Hoja1!$K$21+'Todos los Datos (2)'!AE22*Hoja1!$K$22+'Todos los Datos (2)'!AJ22*Hoja1!$K$23+'Todos los Datos (2)'!AO22*Hoja1!$K$24</f>
-        <v>186.47058823529409</v>
-      </c>
-      <c r="J22" t="s">
-        <v>102</v>
-      </c>
-      <c r="K22" s="9">
-        <v>0.05</v>
+        <v>271.36796646054177</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="16">
+        <v>1.110458858212284E-2</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -14912,19 +15148,19 @@
         <v>0</v>
       </c>
       <c r="AR22">
-        <v>0.05</v>
+        <v>1.110458858212284E-2</v>
       </c>
       <c r="AS22">
-        <v>0.05</v>
+        <v>1.110458858212284E-2</v>
       </c>
       <c r="AT22">
-        <v>0.05</v>
+        <v>1.110458858212284E-2</v>
       </c>
       <c r="AU22">
-        <v>0.05</v>
+        <v>1.110458858212284E-2</v>
       </c>
       <c r="AV22">
-        <v>0.05</v>
+        <v>1.110458858212284E-2</v>
       </c>
       <c r="AW22">
         <v>0</v>
@@ -14963,35 +15199,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B23">
         <f>'Todos los Datos (2)'!B23*Hoja1!$K$17+'Todos los Datos (2)'!G23*Hoja1!$K$18+'Todos los Datos (2)'!L23*Hoja1!$K$19+'Todos los Datos (2)'!Q23*Hoja1!$K$20+'Todos los Datos (2)'!V23*Hoja1!$K$21+'Todos los Datos (2)'!AA23*Hoja1!$K$22+'Todos los Datos (2)'!AF23*Hoja1!$K$23+'Todos los Datos (2)'!AK23*Hoja1!$K$24</f>
-        <v>132.08884688090734</v>
+        <v>261.96568538589872</v>
       </c>
       <c r="C23">
         <f>'Todos los Datos (2)'!C23*Hoja1!$K$17+'Todos los Datos (2)'!H23*Hoja1!$K$18+'Todos los Datos (2)'!M23*Hoja1!$K$19+'Todos los Datos (2)'!R23*Hoja1!$K$20+'Todos los Datos (2)'!W23*Hoja1!$K$21+'Todos los Datos (2)'!AB23*Hoja1!$K$22+'Todos los Datos (2)'!AG23*Hoja1!$K$23+'Todos los Datos (2)'!AL23*Hoja1!$K$24</f>
-        <v>157.72684310018906</v>
+        <v>322.2228289004737</v>
       </c>
       <c r="D23">
         <f>'Todos los Datos (2)'!D23*Hoja1!$K$17+'Todos los Datos (2)'!I23*Hoja1!$K$18+'Todos los Datos (2)'!N23*Hoja1!$K$19+'Todos los Datos (2)'!S23*Hoja1!$K$20+'Todos los Datos (2)'!X23*Hoja1!$K$21+'Todos los Datos (2)'!AC23*Hoja1!$K$22+'Todos los Datos (2)'!AH23*Hoja1!$K$23+'Todos los Datos (2)'!AM23*Hoja1!$K$24</f>
-        <v>167.09002835538752</v>
+        <v>363.90708262681915</v>
       </c>
       <c r="E23">
         <f>'Todos los Datos (2)'!E23*Hoja1!$K$17+'Todos los Datos (2)'!J23*Hoja1!$K$18+'Todos los Datos (2)'!O23*Hoja1!$K$19+'Todos los Datos (2)'!T23*Hoja1!$K$20+'Todos los Datos (2)'!Y23*Hoja1!$K$21+'Todos los Datos (2)'!AD23*Hoja1!$K$22+'Todos los Datos (2)'!AI23*Hoja1!$K$23+'Todos los Datos (2)'!AN23*Hoja1!$K$24</f>
-        <v>156.78166351606808</v>
+        <v>324.92003853055422</v>
       </c>
       <c r="F23">
         <f>'Todos los Datos (2)'!F23*Hoja1!$K$17+'Todos los Datos (2)'!K23*Hoja1!$K$18+'Todos los Datos (2)'!P23*Hoja1!$K$19+'Todos los Datos (2)'!U23*Hoja1!$K$20+'Todos los Datos (2)'!Z23*Hoja1!$K$21+'Todos los Datos (2)'!AE23*Hoja1!$K$22+'Todos los Datos (2)'!AJ23*Hoja1!$K$23+'Todos los Datos (2)'!AO23*Hoja1!$K$24</f>
-        <v>163.81143667296789</v>
-      </c>
-      <c r="J23" t="s">
-        <v>103</v>
-      </c>
-      <c r="K23" s="9">
-        <v>0.1</v>
+        <v>333.81401230519839</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="K23" s="18">
+        <v>0.37623091413346282</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -15105,19 +15341,19 @@
         <v>0</v>
       </c>
       <c r="AX23">
-        <v>0.1</v>
+        <v>0.37623091413346282</v>
       </c>
       <c r="AY23">
-        <v>0.1</v>
+        <v>0.37623091413346282</v>
       </c>
       <c r="AZ23">
-        <v>0.1</v>
+        <v>0.37623091413346282</v>
       </c>
       <c r="BA23">
-        <v>0.1</v>
+        <v>0.37623091413346282</v>
       </c>
       <c r="BB23">
-        <v>0.1</v>
+        <v>0.37623091413346282</v>
       </c>
       <c r="BC23">
         <v>0</v>
@@ -15144,30 +15380,25 @@
       </c>
       <c r="B24">
         <f>'Todos los Datos (2)'!B24*Hoja1!$K$17+'Todos los Datos (2)'!G24*Hoja1!$K$18+'Todos los Datos (2)'!L24*Hoja1!$K$19+'Todos los Datos (2)'!Q24*Hoja1!$K$20+'Todos los Datos (2)'!V24*Hoja1!$K$21+'Todos los Datos (2)'!AA24*Hoja1!$K$22+'Todos los Datos (2)'!AF24*Hoja1!$K$23+'Todos los Datos (2)'!AK24*Hoja1!$K$24</f>
-        <v>82.854749940177072</v>
+        <v>152.04424290176726</v>
       </c>
       <c r="C24">
         <f>'Todos los Datos (2)'!C24*Hoja1!$K$17+'Todos los Datos (2)'!H24*Hoja1!$K$18+'Todos los Datos (2)'!M24*Hoja1!$K$19+'Todos los Datos (2)'!R24*Hoja1!$K$20+'Todos los Datos (2)'!W24*Hoja1!$K$21+'Todos los Datos (2)'!AB24*Hoja1!$K$22+'Todos los Datos (2)'!AG24*Hoja1!$K$23+'Todos los Datos (2)'!AL24*Hoja1!$K$24</f>
-        <v>149.85642498205311</v>
+        <v>236.57624495392758</v>
       </c>
       <c r="D24">
         <f>'Todos los Datos (2)'!D24*Hoja1!$K$17+'Todos los Datos (2)'!I24*Hoja1!$K$18+'Todos los Datos (2)'!N24*Hoja1!$K$19+'Todos los Datos (2)'!S24*Hoja1!$K$20+'Todos los Datos (2)'!X24*Hoja1!$K$21+'Todos los Datos (2)'!AC24*Hoja1!$K$22+'Todos los Datos (2)'!AH24*Hoja1!$K$23+'Todos los Datos (2)'!AM24*Hoja1!$K$24</f>
-        <v>117.85116056472839</v>
+        <v>217.64119464355474</v>
       </c>
       <c r="E24">
         <f>'Todos los Datos (2)'!E24*Hoja1!$K$17+'Todos los Datos (2)'!J24*Hoja1!$K$18+'Todos los Datos (2)'!O24*Hoja1!$K$19+'Todos los Datos (2)'!T24*Hoja1!$K$20+'Todos los Datos (2)'!Y24*Hoja1!$K$21+'Todos los Datos (2)'!AD24*Hoja1!$K$22+'Todos los Datos (2)'!AI24*Hoja1!$K$23+'Todos los Datos (2)'!AN24*Hoja1!$K$24</f>
-        <v>106.18569035654463</v>
+        <v>186.94631657001187</v>
       </c>
       <c r="F24">
         <f>'Todos los Datos (2)'!F24*Hoja1!$K$17+'Todos los Datos (2)'!K24*Hoja1!$K$18+'Todos los Datos (2)'!P24*Hoja1!$K$19+'Todos los Datos (2)'!U24*Hoja1!$K$20+'Todos los Datos (2)'!Z24*Hoja1!$K$21+'Todos los Datos (2)'!AE24*Hoja1!$K$22+'Todos los Datos (2)'!AJ24*Hoja1!$K$23+'Todos los Datos (2)'!AO24*Hoja1!$K$24</f>
-        <v>119.04761904761907</v>
-      </c>
-      <c r="J24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K24" s="9">
-        <v>0.05</v>
-      </c>
+        <v>216.15768581889324</v>
+      </c>
+      <c r="K24" s="9"/>
       <c r="M24">
         <v>0</v>
       </c>
@@ -15298,19 +15529,19 @@
         <v>0</v>
       </c>
       <c r="BD24">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="BE24">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="BF24">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="BG24">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="BH24">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -15319,23 +15550,23 @@
       </c>
       <c r="B25">
         <f>'Todos los Datos (2)'!B25*Hoja1!$K$17+'Todos los Datos (2)'!G25*Hoja1!$K$18+'Todos los Datos (2)'!L25*Hoja1!$K$19+'Todos los Datos (2)'!Q25*Hoja1!$K$20+'Todos los Datos (2)'!V25*Hoja1!$K$21+'Todos los Datos (2)'!AA25*Hoja1!$K$22+'Todos los Datos (2)'!AF25*Hoja1!$K$23+'Todos los Datos (2)'!AK25*Hoja1!$K$24</f>
-        <v>86.594337732230287</v>
+        <v>93.56356818620506</v>
       </c>
       <c r="C25">
         <f>'Todos los Datos (2)'!C25*Hoja1!$K$17+'Todos los Datos (2)'!H25*Hoja1!$K$18+'Todos los Datos (2)'!M25*Hoja1!$K$19+'Todos los Datos (2)'!R25*Hoja1!$K$20+'Todos los Datos (2)'!W25*Hoja1!$K$21+'Todos los Datos (2)'!AB25*Hoja1!$K$22+'Todos los Datos (2)'!AG25*Hoja1!$K$23+'Todos los Datos (2)'!AL25*Hoja1!$K$24</f>
-        <v>87.882517962957664</v>
+        <v>120.64307002864987</v>
       </c>
       <c r="D25">
         <f>'Todos los Datos (2)'!D25*Hoja1!$K$17+'Todos los Datos (2)'!I25*Hoja1!$K$18+'Todos los Datos (2)'!N25*Hoja1!$K$19+'Todos los Datos (2)'!S25*Hoja1!$K$20+'Todos los Datos (2)'!X25*Hoja1!$K$21+'Todos los Datos (2)'!AC25*Hoja1!$K$22+'Todos los Datos (2)'!AH25*Hoja1!$K$23+'Todos los Datos (2)'!AM25*Hoja1!$K$24</f>
-        <v>92.748976612372275</v>
+        <v>137.31514771876812</v>
       </c>
       <c r="E25">
         <f>'Todos los Datos (2)'!E25*Hoja1!$K$17+'Todos los Datos (2)'!J25*Hoja1!$K$18+'Todos los Datos (2)'!O25*Hoja1!$K$19+'Todos los Datos (2)'!T25*Hoja1!$K$20+'Todos los Datos (2)'!Y25*Hoja1!$K$21+'Todos los Datos (2)'!AD25*Hoja1!$K$22+'Todos los Datos (2)'!AI25*Hoja1!$K$23+'Todos los Datos (2)'!AN25*Hoja1!$K$24</f>
-        <v>110.64036870580827</v>
+        <v>150.57445726089801</v>
       </c>
       <c r="F25">
         <f>'Todos los Datos (2)'!F25*Hoja1!$K$17+'Todos los Datos (2)'!K25*Hoja1!$K$18+'Todos los Datos (2)'!P25*Hoja1!$K$19+'Todos los Datos (2)'!U25*Hoja1!$K$20+'Todos los Datos (2)'!Z25*Hoja1!$K$21+'Todos los Datos (2)'!AE25*Hoja1!$K$22+'Todos los Datos (2)'!AJ25*Hoja1!$K$23+'Todos los Datos (2)'!AO25*Hoja1!$K$24</f>
-        <v>145.4212349354479</v>
+        <v>179.1453659726688</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -15344,23 +15575,23 @@
       </c>
       <c r="B26">
         <f>'Todos los Datos (2)'!B26*Hoja1!$K$17+'Todos los Datos (2)'!G26*Hoja1!$K$18+'Todos los Datos (2)'!L26*Hoja1!$K$19+'Todos los Datos (2)'!Q26*Hoja1!$K$20+'Todos los Datos (2)'!V26*Hoja1!$K$21+'Todos los Datos (2)'!AA26*Hoja1!$K$22+'Todos los Datos (2)'!AF26*Hoja1!$K$23+'Todos los Datos (2)'!AK26*Hoja1!$K$24</f>
-        <v>123.16910785619174</v>
+        <v>172.43756951754841</v>
       </c>
       <c r="C26">
         <f>'Todos los Datos (2)'!C26*Hoja1!$K$17+'Todos los Datos (2)'!H26*Hoja1!$K$18+'Todos los Datos (2)'!M26*Hoja1!$K$19+'Todos los Datos (2)'!R26*Hoja1!$K$20+'Todos los Datos (2)'!W26*Hoja1!$K$21+'Todos los Datos (2)'!AB26*Hoja1!$K$22+'Todos los Datos (2)'!AG26*Hoja1!$K$23+'Todos los Datos (2)'!AL26*Hoja1!$K$24</f>
-        <v>95.705725699067898</v>
+        <v>125.42859943791828</v>
       </c>
       <c r="D26">
         <f>'Todos los Datos (2)'!D26*Hoja1!$K$17+'Todos los Datos (2)'!I26*Hoja1!$K$18+'Todos los Datos (2)'!N26*Hoja1!$K$19+'Todos los Datos (2)'!S26*Hoja1!$K$20+'Todos los Datos (2)'!X26*Hoja1!$K$21+'Todos los Datos (2)'!AC26*Hoja1!$K$22+'Todos los Datos (2)'!AH26*Hoja1!$K$23+'Todos los Datos (2)'!AM26*Hoja1!$K$24</f>
-        <v>70.322902796271649</v>
+        <v>116.03234880106839</v>
       </c>
       <c r="E26">
         <f>'Todos los Datos (2)'!E26*Hoja1!$K$17+'Todos los Datos (2)'!J26*Hoja1!$K$18+'Todos los Datos (2)'!O26*Hoja1!$K$19+'Todos los Datos (2)'!T26*Hoja1!$K$20+'Todos los Datos (2)'!Y26*Hoja1!$K$21+'Todos los Datos (2)'!AD26*Hoja1!$K$22+'Todos los Datos (2)'!AI26*Hoja1!$K$23+'Todos los Datos (2)'!AN26*Hoja1!$K$24</f>
-        <v>64.913448735019969</v>
+        <v>125.06743357138109</v>
       </c>
       <c r="F26">
         <f>'Todos los Datos (2)'!F26*Hoja1!$K$17+'Todos los Datos (2)'!K26*Hoja1!$K$18+'Todos los Datos (2)'!P26*Hoja1!$K$19+'Todos los Datos (2)'!U26*Hoja1!$K$20+'Todos los Datos (2)'!Z26*Hoja1!$K$21+'Todos los Datos (2)'!AE26*Hoja1!$K$22+'Todos los Datos (2)'!AJ26*Hoja1!$K$23+'Todos los Datos (2)'!AO26*Hoja1!$K$24</f>
-        <v>120.25632490013315</v>
+        <v>144.30767270348812</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -15369,23 +15600,23 @@
       </c>
       <c r="B27">
         <f>'Todos los Datos (2)'!B27*Hoja1!$K$17+'Todos los Datos (2)'!G27*Hoja1!$K$18+'Todos los Datos (2)'!L27*Hoja1!$K$19+'Todos los Datos (2)'!Q27*Hoja1!$K$20+'Todos los Datos (2)'!V27*Hoja1!$K$21+'Todos los Datos (2)'!AA27*Hoja1!$K$22+'Todos los Datos (2)'!AF27*Hoja1!$K$23+'Todos los Datos (2)'!AK27*Hoja1!$K$24</f>
-        <v>91.445911588616426</v>
+        <v>111.17778687003972</v>
       </c>
       <c r="C27">
         <f>'Todos los Datos (2)'!C27*Hoja1!$K$17+'Todos los Datos (2)'!H27*Hoja1!$K$18+'Todos los Datos (2)'!M27*Hoja1!$K$19+'Todos los Datos (2)'!R27*Hoja1!$K$20+'Todos los Datos (2)'!W27*Hoja1!$K$21+'Todos los Datos (2)'!AB27*Hoja1!$K$22+'Todos los Datos (2)'!AG27*Hoja1!$K$23+'Todos los Datos (2)'!AL27*Hoja1!$K$24</f>
-        <v>84.064627245140656</v>
+        <v>102.77629756912111</v>
       </c>
       <c r="D27">
         <f>'Todos los Datos (2)'!D27*Hoja1!$K$17+'Todos los Datos (2)'!I27*Hoja1!$K$18+'Todos los Datos (2)'!N27*Hoja1!$K$19+'Todos los Datos (2)'!S27*Hoja1!$K$20+'Todos los Datos (2)'!X27*Hoja1!$K$21+'Todos los Datos (2)'!AC27*Hoja1!$K$22+'Todos los Datos (2)'!AH27*Hoja1!$K$23+'Todos los Datos (2)'!AM27*Hoja1!$K$24</f>
-        <v>96.776839170015577</v>
+        <v>97.524159333706933</v>
       </c>
       <c r="E27">
         <f>'Todos los Datos (2)'!E27*Hoja1!$K$17+'Todos los Datos (2)'!J27*Hoja1!$K$18+'Todos los Datos (2)'!O27*Hoja1!$K$19+'Todos los Datos (2)'!T27*Hoja1!$K$20+'Todos los Datos (2)'!Y27*Hoja1!$K$21+'Todos los Datos (2)'!AD27*Hoja1!$K$22+'Todos los Datos (2)'!AI27*Hoja1!$K$23+'Todos los Datos (2)'!AN27*Hoja1!$K$24</f>
-        <v>131.22283277290248</v>
+        <v>152.33491006751265</v>
       </c>
       <c r="F27">
         <f>'Todos los Datos (2)'!F27*Hoja1!$K$17+'Todos los Datos (2)'!K27*Hoja1!$K$18+'Todos los Datos (2)'!P27*Hoja1!$K$19+'Todos los Datos (2)'!U27*Hoja1!$K$20+'Todos los Datos (2)'!Z27*Hoja1!$K$21+'Todos los Datos (2)'!AE27*Hoja1!$K$22+'Todos los Datos (2)'!AJ27*Hoja1!$K$23+'Todos los Datos (2)'!AO27*Hoja1!$K$24</f>
-        <v>163.20839826129748</v>
+        <v>199.26009024175696</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -15394,23 +15625,23 @@
       </c>
       <c r="B28">
         <f>'Todos los Datos (2)'!B28*Hoja1!$K$17+'Todos los Datos (2)'!G28*Hoja1!$K$18+'Todos los Datos (2)'!L28*Hoja1!$K$19+'Todos los Datos (2)'!Q28*Hoja1!$K$20+'Todos los Datos (2)'!V28*Hoja1!$K$21+'Todos los Datos (2)'!AA28*Hoja1!$K$22+'Todos los Datos (2)'!AF28*Hoja1!$K$23+'Todos los Datos (2)'!AK28*Hoja1!$K$24</f>
-        <v>118.23938284198147</v>
+        <v>263.49087003520219</v>
       </c>
       <c r="C28">
         <f>'Todos los Datos (2)'!C28*Hoja1!$K$17+'Todos los Datos (2)'!H28*Hoja1!$K$18+'Todos los Datos (2)'!M28*Hoja1!$K$19+'Todos los Datos (2)'!R28*Hoja1!$K$20+'Todos los Datos (2)'!W28*Hoja1!$K$21+'Todos los Datos (2)'!AB28*Hoja1!$K$22+'Todos los Datos (2)'!AG28*Hoja1!$K$23+'Todos los Datos (2)'!AL28*Hoja1!$K$24</f>
-        <v>154.1501535648791</v>
+        <v>336.31230503252112</v>
       </c>
       <c r="D28">
         <f>'Todos los Datos (2)'!D28*Hoja1!$K$17+'Todos los Datos (2)'!I28*Hoja1!$K$18+'Todos los Datos (2)'!N28*Hoja1!$K$19+'Todos los Datos (2)'!S28*Hoja1!$K$20+'Todos los Datos (2)'!X28*Hoja1!$K$21+'Todos los Datos (2)'!AC28*Hoja1!$K$22+'Todos los Datos (2)'!AH28*Hoja1!$K$23+'Todos los Datos (2)'!AM28*Hoja1!$K$24</f>
-        <v>186.40992625541378</v>
+        <v>425.97890035843784</v>
       </c>
       <c r="E28">
         <f>'Todos los Datos (2)'!E28*Hoja1!$K$17+'Todos los Datos (2)'!J28*Hoja1!$K$18+'Todos los Datos (2)'!O28*Hoja1!$K$19+'Todos los Datos (2)'!T28*Hoja1!$K$20+'Todos los Datos (2)'!Y28*Hoja1!$K$21+'Todos los Datos (2)'!AD28*Hoja1!$K$22+'Todos los Datos (2)'!AI28*Hoja1!$K$23+'Todos los Datos (2)'!AN28*Hoja1!$K$24</f>
-        <v>191.0363817773393</v>
+        <v>457.16003817331864</v>
       </c>
       <c r="F28">
         <f>'Todos los Datos (2)'!F28*Hoja1!$K$17+'Todos los Datos (2)'!K28*Hoja1!$K$18+'Todos los Datos (2)'!P28*Hoja1!$K$19+'Todos los Datos (2)'!U28*Hoja1!$K$20+'Todos los Datos (2)'!Z28*Hoja1!$K$21+'Todos los Datos (2)'!AE28*Hoja1!$K$22+'Todos los Datos (2)'!AJ28*Hoja1!$K$23+'Todos los Datos (2)'!AO28*Hoja1!$K$24</f>
-        <v>214.94902537861685</v>
+        <v>492.43855722328988</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -15419,23 +15650,23 @@
       </c>
       <c r="B29">
         <f>'Todos los Datos (2)'!B29*Hoja1!$K$17+'Todos los Datos (2)'!G29*Hoja1!$K$18+'Todos los Datos (2)'!L29*Hoja1!$K$19+'Todos los Datos (2)'!Q29*Hoja1!$K$20+'Todos los Datos (2)'!V29*Hoja1!$K$21+'Todos los Datos (2)'!AA29*Hoja1!$K$22+'Todos los Datos (2)'!AF29*Hoja1!$K$23+'Todos los Datos (2)'!AK29*Hoja1!$K$24</f>
-        <v>98.728726676235397</v>
+        <v>161.10124692374274</v>
       </c>
       <c r="C29">
         <f>'Todos los Datos (2)'!C29*Hoja1!$K$17+'Todos los Datos (2)'!H29*Hoja1!$K$18+'Todos los Datos (2)'!M29*Hoja1!$K$19+'Todos los Datos (2)'!R29*Hoja1!$K$20+'Todos los Datos (2)'!W29*Hoja1!$K$21+'Todos los Datos (2)'!AB29*Hoja1!$K$22+'Todos los Datos (2)'!AG29*Hoja1!$K$23+'Todos los Datos (2)'!AL29*Hoja1!$K$24</f>
-        <v>136.35431617797826</v>
+        <v>222.29740098497859</v>
       </c>
       <c r="D29">
         <f>'Todos los Datos (2)'!D29*Hoja1!$K$17+'Todos los Datos (2)'!I29*Hoja1!$K$18+'Todos los Datos (2)'!N29*Hoja1!$K$19+'Todos los Datos (2)'!S29*Hoja1!$K$20+'Todos los Datos (2)'!X29*Hoja1!$K$21+'Todos los Datos (2)'!AC29*Hoja1!$K$22+'Todos los Datos (2)'!AH29*Hoja1!$K$23+'Todos los Datos (2)'!AM29*Hoja1!$K$24</f>
-        <v>125.07689153167929</v>
+        <v>235.42017621478388</v>
       </c>
       <c r="E29">
         <f>'Todos los Datos (2)'!E29*Hoja1!$K$17+'Todos los Datos (2)'!J29*Hoja1!$K$18+'Todos los Datos (2)'!O29*Hoja1!$K$19+'Todos los Datos (2)'!T29*Hoja1!$K$20+'Todos los Datos (2)'!Y29*Hoja1!$K$21+'Todos los Datos (2)'!AD29*Hoja1!$K$22+'Todos los Datos (2)'!AI29*Hoja1!$K$23+'Todos los Datos (2)'!AN29*Hoja1!$K$24</f>
-        <v>135.63666188230468</v>
+        <v>240.37863027513251</v>
       </c>
       <c r="F29">
         <f>'Todos los Datos (2)'!F29*Hoja1!$K$17+'Todos los Datos (2)'!K29*Hoja1!$K$18+'Todos los Datos (2)'!P29*Hoja1!$K$19+'Todos los Datos (2)'!U29*Hoja1!$K$20+'Todos los Datos (2)'!Z29*Hoja1!$K$21+'Todos los Datos (2)'!AE29*Hoja1!$K$22+'Todos los Datos (2)'!AJ29*Hoja1!$K$23+'Todos los Datos (2)'!AO29*Hoja1!$K$24</f>
-        <v>181.25897067869593</v>
+        <v>306.46178541835059</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -15444,23 +15675,23 @@
       </c>
       <c r="B30">
         <f>'Todos los Datos (2)'!B30*Hoja1!$K$17+'Todos los Datos (2)'!G30*Hoja1!$K$18+'Todos los Datos (2)'!L30*Hoja1!$K$19+'Todos los Datos (2)'!Q30*Hoja1!$K$20+'Todos los Datos (2)'!V30*Hoja1!$K$21+'Todos los Datos (2)'!AA30*Hoja1!$K$22+'Todos los Datos (2)'!AF30*Hoja1!$K$23+'Todos los Datos (2)'!AK30*Hoja1!$K$24</f>
-        <v>93.895198760970572</v>
+        <v>160.91710234394446</v>
       </c>
       <c r="C30">
         <f>'Todos los Datos (2)'!C30*Hoja1!$K$17+'Todos los Datos (2)'!H30*Hoja1!$K$18+'Todos los Datos (2)'!M30*Hoja1!$K$19+'Todos los Datos (2)'!R30*Hoja1!$K$20+'Todos los Datos (2)'!W30*Hoja1!$K$21+'Todos los Datos (2)'!AB30*Hoja1!$K$22+'Todos los Datos (2)'!AG30*Hoja1!$K$23+'Todos los Datos (2)'!AL30*Hoja1!$K$24</f>
-        <v>150.03871966959215</v>
+        <v>238.00770069904462</v>
       </c>
       <c r="D30">
         <f>'Todos los Datos (2)'!D30*Hoja1!$K$17+'Todos los Datos (2)'!I30*Hoja1!$K$18+'Todos los Datos (2)'!N30*Hoja1!$K$19+'Todos los Datos (2)'!S30*Hoja1!$K$20+'Todos los Datos (2)'!X30*Hoja1!$K$21+'Todos los Datos (2)'!AC30*Hoja1!$K$22+'Todos los Datos (2)'!AH30*Hoja1!$K$23+'Todos los Datos (2)'!AM30*Hoja1!$K$24</f>
-        <v>164.88125967991741</v>
+        <v>237.22299105368683</v>
       </c>
       <c r="E30">
         <f>'Todos los Datos (2)'!E30*Hoja1!$K$17+'Todos los Datos (2)'!J30*Hoja1!$K$18+'Todos los Datos (2)'!O30*Hoja1!$K$19+'Todos los Datos (2)'!T30*Hoja1!$K$20+'Todos los Datos (2)'!Y30*Hoja1!$K$21+'Todos los Datos (2)'!AD30*Hoja1!$K$22+'Todos los Datos (2)'!AI30*Hoja1!$K$23+'Todos los Datos (2)'!AN30*Hoja1!$K$24</f>
-        <v>172.30252968508</v>
+        <v>248.25861080600322</v>
       </c>
       <c r="F30">
         <f>'Todos los Datos (2)'!F30*Hoja1!$K$17+'Todos los Datos (2)'!K30*Hoja1!$K$18+'Todos los Datos (2)'!P30*Hoja1!$K$19+'Todos los Datos (2)'!U30*Hoja1!$K$20+'Todos los Datos (2)'!Z30*Hoja1!$K$21+'Todos los Datos (2)'!AE30*Hoja1!$K$22+'Todos los Datos (2)'!AJ30*Hoja1!$K$23+'Todos los Datos (2)'!AO30*Hoja1!$K$24</f>
-        <v>211.66752710376869</v>
+        <v>296.47277741444009</v>
       </c>
       <c r="P30" cm="1">
         <f t="array" ref="P30:BJ30">IF(IFERROR(VALUE(RIGHT(TRIM('Todos los Datos'!C1:AW1),4)),"")=B$1,1,0)*'Todos los Datos'!C2:AW2</f>
@@ -15611,23 +15842,23 @@
       </c>
       <c r="B31">
         <f>'Todos los Datos (2)'!B31*Hoja1!$K$17+'Todos los Datos (2)'!G31*Hoja1!$K$18+'Todos los Datos (2)'!L31*Hoja1!$K$19+'Todos los Datos (2)'!Q31*Hoja1!$K$20+'Todos los Datos (2)'!V31*Hoja1!$K$21+'Todos los Datos (2)'!AA31*Hoja1!$K$22+'Todos los Datos (2)'!AF31*Hoja1!$K$23+'Todos los Datos (2)'!AK31*Hoja1!$K$24</f>
-        <v>120.71278022609698</v>
+        <v>173.18228835298521</v>
       </c>
       <c r="C31">
         <f>'Todos los Datos (2)'!C31*Hoja1!$K$17+'Todos los Datos (2)'!H31*Hoja1!$K$18+'Todos los Datos (2)'!M31*Hoja1!$K$19+'Todos los Datos (2)'!R31*Hoja1!$K$20+'Todos los Datos (2)'!W31*Hoja1!$K$21+'Todos los Datos (2)'!AB31*Hoja1!$K$22+'Todos los Datos (2)'!AG31*Hoja1!$K$23+'Todos los Datos (2)'!AL31*Hoja1!$K$24</f>
-        <v>116.88062847288754</v>
+        <v>160.99143339662703</v>
       </c>
       <c r="D31">
         <f>'Todos los Datos (2)'!D31*Hoja1!$K$17+'Todos los Datos (2)'!I31*Hoja1!$K$18+'Todos los Datos (2)'!N31*Hoja1!$K$19+'Todos los Datos (2)'!S31*Hoja1!$K$20+'Todos los Datos (2)'!X31*Hoja1!$K$21+'Todos los Datos (2)'!AC31*Hoja1!$K$22+'Todos los Datos (2)'!AH31*Hoja1!$K$23+'Todos los Datos (2)'!AM31*Hoja1!$K$24</f>
-        <v>142.10896084818293</v>
+        <v>192.04502637579364</v>
       </c>
       <c r="E31">
         <f>'Todos los Datos (2)'!E31*Hoja1!$K$17+'Todos los Datos (2)'!J31*Hoja1!$K$18+'Todos los Datos (2)'!O31*Hoja1!$K$19+'Todos los Datos (2)'!T31*Hoja1!$K$20+'Todos los Datos (2)'!Y31*Hoja1!$K$21+'Todos los Datos (2)'!AD31*Hoja1!$K$22+'Todos los Datos (2)'!AI31*Hoja1!$K$23+'Todos los Datos (2)'!AN31*Hoja1!$K$24</f>
-        <v>145.62176662195824</v>
+        <v>205.46592021191117</v>
       </c>
       <c r="F31">
         <f>'Todos los Datos (2)'!F31*Hoja1!$K$17+'Todos los Datos (2)'!K31*Hoja1!$K$18+'Todos los Datos (2)'!P31*Hoja1!$K$19+'Todos los Datos (2)'!U31*Hoja1!$K$20+'Todos los Datos (2)'!Z31*Hoja1!$K$21+'Todos los Datos (2)'!AE31*Hoja1!$K$22+'Todos los Datos (2)'!AJ31*Hoja1!$K$23+'Todos los Datos (2)'!AO31*Hoja1!$K$24</f>
-        <v>121.99016414383344</v>
+        <v>170.22447160643534</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -15636,23 +15867,23 @@
       </c>
       <c r="B32">
         <f>'Todos los Datos (2)'!B32*Hoja1!$K$17+'Todos los Datos (2)'!G32*Hoja1!$K$18+'Todos los Datos (2)'!L32*Hoja1!$K$19+'Todos los Datos (2)'!Q32*Hoja1!$K$20+'Todos los Datos (2)'!V32*Hoja1!$K$21+'Todos los Datos (2)'!AA32*Hoja1!$K$22+'Todos los Datos (2)'!AF32*Hoja1!$K$23+'Todos los Datos (2)'!AK32*Hoja1!$K$24</f>
-        <v>100.5423109965636</v>
+        <v>129.22506676167978</v>
       </c>
       <c r="C32">
         <f>'Todos los Datos (2)'!C32*Hoja1!$K$17+'Todos los Datos (2)'!H32*Hoja1!$K$18+'Todos los Datos (2)'!M32*Hoja1!$K$19+'Todos los Datos (2)'!R32*Hoja1!$K$20+'Todos los Datos (2)'!W32*Hoja1!$K$21+'Todos los Datos (2)'!AB32*Hoja1!$K$22+'Todos los Datos (2)'!AG32*Hoja1!$K$23+'Todos los Datos (2)'!AL32*Hoja1!$K$24</f>
-        <v>108.32796391752578</v>
+        <v>155.9311490136831</v>
       </c>
       <c r="D32">
         <f>'Todos los Datos (2)'!D32*Hoja1!$K$17+'Todos los Datos (2)'!I32*Hoja1!$K$18+'Todos los Datos (2)'!N32*Hoja1!$K$19+'Todos los Datos (2)'!S32*Hoja1!$K$20+'Todos los Datos (2)'!X32*Hoja1!$K$21+'Todos los Datos (2)'!AC32*Hoja1!$K$22+'Todos los Datos (2)'!AH32*Hoja1!$K$23+'Todos los Datos (2)'!AM32*Hoja1!$K$24</f>
-        <v>117.18750000000001</v>
+        <v>195.74581299542058</v>
       </c>
       <c r="E32">
         <f>'Todos los Datos (2)'!E32*Hoja1!$K$17+'Todos los Datos (2)'!J32*Hoja1!$K$18+'Todos los Datos (2)'!O32*Hoja1!$K$19+'Todos los Datos (2)'!T32*Hoja1!$K$20+'Todos los Datos (2)'!Y32*Hoja1!$K$21+'Todos los Datos (2)'!AD32*Hoja1!$K$22+'Todos los Datos (2)'!AI32*Hoja1!$K$23+'Todos los Datos (2)'!AN32*Hoja1!$K$24</f>
-        <v>125.51009450171823</v>
+        <v>186.47388290722461</v>
       </c>
       <c r="F32">
         <f>'Todos los Datos (2)'!F32*Hoja1!$K$17+'Todos los Datos (2)'!K32*Hoja1!$K$18+'Todos los Datos (2)'!P32*Hoja1!$K$19+'Todos los Datos (2)'!U32*Hoja1!$K$20+'Todos los Datos (2)'!Z32*Hoja1!$K$21+'Todos los Datos (2)'!AE32*Hoja1!$K$22+'Todos los Datos (2)'!AJ32*Hoja1!$K$23+'Todos los Datos (2)'!AO32*Hoja1!$K$24</f>
-        <v>169.94201030927837</v>
+        <v>252.93018292741394</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -15661,23 +15892,23 @@
       </c>
       <c r="B33">
         <f>'Todos los Datos (2)'!B33*Hoja1!$K$17+'Todos los Datos (2)'!G33*Hoja1!$K$18+'Todos los Datos (2)'!L33*Hoja1!$K$19+'Todos los Datos (2)'!Q33*Hoja1!$K$20+'Todos los Datos (2)'!V33*Hoja1!$K$21+'Todos los Datos (2)'!AA33*Hoja1!$K$22+'Todos los Datos (2)'!AF33*Hoja1!$K$23+'Todos los Datos (2)'!AK33*Hoja1!$K$24</f>
-        <v>119.69001148105627</v>
+        <v>184.26676590540018</v>
       </c>
       <c r="C33">
         <f>'Todos los Datos (2)'!C33*Hoja1!$K$17+'Todos los Datos (2)'!H33*Hoja1!$K$18+'Todos los Datos (2)'!M33*Hoja1!$K$19+'Todos los Datos (2)'!R33*Hoja1!$K$20+'Todos los Datos (2)'!W33*Hoja1!$K$21+'Todos los Datos (2)'!AB33*Hoja1!$K$22+'Todos los Datos (2)'!AG33*Hoja1!$K$23+'Todos los Datos (2)'!AL33*Hoja1!$K$24</f>
-        <v>145.52238805970148</v>
+        <v>216.27046763823199</v>
       </c>
       <c r="D33">
         <f>'Todos los Datos (2)'!D33*Hoja1!$K$17+'Todos los Datos (2)'!I33*Hoja1!$K$18+'Todos los Datos (2)'!N33*Hoja1!$K$19+'Todos los Datos (2)'!S33*Hoja1!$K$20+'Todos los Datos (2)'!X33*Hoja1!$K$21+'Todos los Datos (2)'!AC33*Hoja1!$K$22+'Todos los Datos (2)'!AH33*Hoja1!$K$23+'Todos los Datos (2)'!AM33*Hoja1!$K$24</f>
-        <v>127.15269804822046</v>
+        <v>217.24346956374458</v>
       </c>
       <c r="E33">
         <f>'Todos los Datos (2)'!E33*Hoja1!$K$17+'Todos los Datos (2)'!J33*Hoja1!$K$18+'Todos los Datos (2)'!O33*Hoja1!$K$19+'Todos los Datos (2)'!T33*Hoja1!$K$20+'Todos los Datos (2)'!Y33*Hoja1!$K$21+'Todos los Datos (2)'!AD33*Hoja1!$K$22+'Todos los Datos (2)'!AI33*Hoja1!$K$23+'Todos los Datos (2)'!AN33*Hoja1!$K$24</f>
-        <v>194.89092996555684</v>
+        <v>328.07077245603688</v>
       </c>
       <c r="F33">
         <f>'Todos los Datos (2)'!F33*Hoja1!$K$17+'Todos los Datos (2)'!K33*Hoja1!$K$18+'Todos los Datos (2)'!P33*Hoja1!$K$19+'Todos los Datos (2)'!U33*Hoja1!$K$20+'Todos los Datos (2)'!Z33*Hoja1!$K$21+'Todos los Datos (2)'!AE33*Hoja1!$K$22+'Todos los Datos (2)'!AJ33*Hoja1!$K$23+'Todos los Datos (2)'!AO33*Hoja1!$K$24</f>
-        <v>146.09644087256027</v>
+        <v>239.11109421809564</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -15686,23 +15917,23 @@
       </c>
       <c r="B34">
         <f>'Todos los Datos (2)'!B34*Hoja1!$K$17+'Todos los Datos (2)'!G34*Hoja1!$K$18+'Todos los Datos (2)'!L34*Hoja1!$K$19+'Todos los Datos (2)'!Q34*Hoja1!$K$20+'Todos los Datos (2)'!V34*Hoja1!$K$21+'Todos los Datos (2)'!AA34*Hoja1!$K$22+'Todos los Datos (2)'!AF34*Hoja1!$K$23+'Todos los Datos (2)'!AK34*Hoja1!$K$24</f>
-        <v>115.43076553875689</v>
+        <v>163.70013126074969</v>
       </c>
       <c r="C34">
         <f>'Todos los Datos (2)'!C34*Hoja1!$K$17+'Todos los Datos (2)'!H34*Hoja1!$K$18+'Todos los Datos (2)'!M34*Hoja1!$K$19+'Todos los Datos (2)'!R34*Hoja1!$K$20+'Todos los Datos (2)'!W34*Hoja1!$K$21+'Todos los Datos (2)'!AB34*Hoja1!$K$22+'Todos los Datos (2)'!AG34*Hoja1!$K$23+'Todos los Datos (2)'!AL34*Hoja1!$K$24</f>
-        <v>102.95176385889127</v>
+        <v>174.97022090532462</v>
       </c>
       <c r="D34">
         <f>'Todos los Datos (2)'!D34*Hoja1!$K$17+'Todos los Datos (2)'!I34*Hoja1!$K$18+'Todos los Datos (2)'!N34*Hoja1!$K$19+'Todos los Datos (2)'!S34*Hoja1!$K$20+'Todos los Datos (2)'!X34*Hoja1!$K$21+'Todos los Datos (2)'!AC34*Hoja1!$K$22+'Todos los Datos (2)'!AH34*Hoja1!$K$23+'Todos los Datos (2)'!AM34*Hoja1!$K$24</f>
-        <v>135.82913366930646</v>
+        <v>237.99152614458228</v>
       </c>
       <c r="E34">
         <f>'Todos los Datos (2)'!E34*Hoja1!$K$17+'Todos los Datos (2)'!J34*Hoja1!$K$18+'Todos los Datos (2)'!O34*Hoja1!$K$19+'Todos los Datos (2)'!T34*Hoja1!$K$20+'Todos los Datos (2)'!Y34*Hoja1!$K$21+'Todos los Datos (2)'!AD34*Hoja1!$K$22+'Todos los Datos (2)'!AI34*Hoja1!$K$23+'Todos los Datos (2)'!AN34*Hoja1!$K$24</f>
-        <v>134.62922966162708</v>
+        <v>240.18131144721013</v>
       </c>
       <c r="F34">
         <f>'Todos los Datos (2)'!F34*Hoja1!$K$17+'Todos los Datos (2)'!K34*Hoja1!$K$18+'Todos los Datos (2)'!P34*Hoja1!$K$19+'Todos los Datos (2)'!U34*Hoja1!$K$20+'Todos los Datos (2)'!Z34*Hoja1!$K$21+'Todos los Datos (2)'!AE34*Hoja1!$K$22+'Todos los Datos (2)'!AJ34*Hoja1!$K$23+'Todos los Datos (2)'!AO34*Hoja1!$K$24</f>
-        <v>134.26925845932325</v>
+        <v>246.55714155441544</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -15711,23 +15942,23 @@
       </c>
       <c r="B35">
         <f>'Todos los Datos (2)'!B35*Hoja1!$K$17+'Todos los Datos (2)'!G35*Hoja1!$K$18+'Todos los Datos (2)'!L35*Hoja1!$K$19+'Todos los Datos (2)'!Q35*Hoja1!$K$20+'Todos los Datos (2)'!V35*Hoja1!$K$21+'Todos los Datos (2)'!AA35*Hoja1!$K$22+'Todos los Datos (2)'!AF35*Hoja1!$K$23+'Todos los Datos (2)'!AK35*Hoja1!$K$24</f>
-        <v>64.172958133150303</v>
+        <v>54.647894189555451</v>
       </c>
       <c r="C35">
         <f>'Todos los Datos (2)'!C35*Hoja1!$K$17+'Todos los Datos (2)'!H35*Hoja1!$K$18+'Todos los Datos (2)'!M35*Hoja1!$K$19+'Todos los Datos (2)'!R35*Hoja1!$K$20+'Todos los Datos (2)'!W35*Hoja1!$K$21+'Todos los Datos (2)'!AB35*Hoja1!$K$22+'Todos los Datos (2)'!AG35*Hoja1!$K$23+'Todos los Datos (2)'!AL35*Hoja1!$K$24</f>
-        <v>102.60809883321895</v>
+        <v>99.1574024092983</v>
       </c>
       <c r="D35">
         <f>'Todos los Datos (2)'!D35*Hoja1!$K$17+'Todos los Datos (2)'!I35*Hoja1!$K$18+'Todos los Datos (2)'!N35*Hoja1!$K$19+'Todos los Datos (2)'!S35*Hoja1!$K$20+'Todos los Datos (2)'!X35*Hoja1!$K$21+'Todos los Datos (2)'!AC35*Hoja1!$K$22+'Todos los Datos (2)'!AH35*Hoja1!$K$23+'Todos los Datos (2)'!AM35*Hoja1!$K$24</f>
-        <v>80.988332189430352</v>
+        <v>74.732107798348977</v>
       </c>
       <c r="E35">
         <f>'Todos los Datos (2)'!E35*Hoja1!$K$17+'Todos los Datos (2)'!J35*Hoja1!$K$18+'Todos los Datos (2)'!O35*Hoja1!$K$19+'Todos los Datos (2)'!T35*Hoja1!$K$20+'Todos los Datos (2)'!Y35*Hoja1!$K$21+'Todos los Datos (2)'!AD35*Hoja1!$K$22+'Todos los Datos (2)'!AI35*Hoja1!$K$23+'Todos los Datos (2)'!AN35*Hoja1!$K$24</f>
-        <v>88.194921070693212</v>
+        <v>89.829782943621552</v>
       </c>
       <c r="F35">
         <f>'Todos los Datos (2)'!F35*Hoja1!$K$17+'Todos los Datos (2)'!K35*Hoja1!$K$18+'Todos los Datos (2)'!P35*Hoja1!$K$19+'Todos los Datos (2)'!U35*Hoja1!$K$20+'Todos los Datos (2)'!Z35*Hoja1!$K$21+'Todos los Datos (2)'!AE35*Hoja1!$K$22+'Todos los Datos (2)'!AJ35*Hoja1!$K$23+'Todos los Datos (2)'!AO35*Hoja1!$K$24</f>
-        <v>81.674673987645832</v>
+        <v>57.54354463923012</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -15736,23 +15967,23 @@
       </c>
       <c r="B36">
         <f>'Todos los Datos (2)'!B36*Hoja1!$K$17+'Todos los Datos (2)'!G36*Hoja1!$K$18+'Todos los Datos (2)'!L36*Hoja1!$K$19+'Todos los Datos (2)'!Q36*Hoja1!$K$20+'Todos los Datos (2)'!V36*Hoja1!$K$21+'Todos los Datos (2)'!AA36*Hoja1!$K$22+'Todos los Datos (2)'!AF36*Hoja1!$K$23+'Todos los Datos (2)'!AK36*Hoja1!$K$24</f>
-        <v>91.831425598335059</v>
+        <v>117.34553762951518</v>
       </c>
       <c r="C36">
         <f>'Todos los Datos (2)'!C36*Hoja1!$K$17+'Todos los Datos (2)'!H36*Hoja1!$K$18+'Todos los Datos (2)'!M36*Hoja1!$K$19+'Todos los Datos (2)'!R36*Hoja1!$K$20+'Todos los Datos (2)'!W36*Hoja1!$K$21+'Todos los Datos (2)'!AB36*Hoja1!$K$22+'Todos los Datos (2)'!AG36*Hoja1!$K$23+'Todos los Datos (2)'!AL36*Hoja1!$K$24</f>
-        <v>88.969823100936537</v>
+        <v>95.000064913468165</v>
       </c>
       <c r="D36">
         <f>'Todos los Datos (2)'!D36*Hoja1!$K$17+'Todos los Datos (2)'!I36*Hoja1!$K$18+'Todos los Datos (2)'!N36*Hoja1!$K$19+'Todos los Datos (2)'!S36*Hoja1!$K$20+'Todos los Datos (2)'!X36*Hoja1!$K$21+'Todos los Datos (2)'!AC36*Hoja1!$K$22+'Todos los Datos (2)'!AH36*Hoja1!$K$23+'Todos los Datos (2)'!AM36*Hoja1!$K$24</f>
-        <v>105.6191467221644</v>
+        <v>130.82397086115856</v>
       </c>
       <c r="E36">
         <f>'Todos los Datos (2)'!E36*Hoja1!$K$17+'Todos los Datos (2)'!J36*Hoja1!$K$18+'Todos los Datos (2)'!O36*Hoja1!$K$19+'Todos los Datos (2)'!T36*Hoja1!$K$20+'Todos los Datos (2)'!Y36*Hoja1!$K$21+'Todos los Datos (2)'!AD36*Hoja1!$K$22+'Todos los Datos (2)'!AI36*Hoja1!$K$23+'Todos los Datos (2)'!AN36*Hoja1!$K$24</f>
-        <v>81.165452653485943</v>
+        <v>94.107432844908487</v>
       </c>
       <c r="F36">
         <f>'Todos los Datos (2)'!F36*Hoja1!$K$17+'Todos los Datos (2)'!K36*Hoja1!$K$18+'Todos los Datos (2)'!P36*Hoja1!$K$19+'Todos los Datos (2)'!U36*Hoja1!$K$20+'Todos los Datos (2)'!Z36*Hoja1!$K$21+'Todos los Datos (2)'!AE36*Hoja1!$K$22+'Todos los Datos (2)'!AJ36*Hoja1!$K$23+'Todos los Datos (2)'!AO36*Hoja1!$K$24</f>
-        <v>119.66701352757542</v>
+        <v>133.69742780220631</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -15761,23 +15992,23 @@
       </c>
       <c r="B37">
         <f>'Todos los Datos (2)'!B37*Hoja1!$K$17+'Todos los Datos (2)'!G37*Hoja1!$K$18+'Todos los Datos (2)'!L37*Hoja1!$K$19+'Todos los Datos (2)'!Q37*Hoja1!$K$20+'Todos los Datos (2)'!V37*Hoja1!$K$21+'Todos los Datos (2)'!AA37*Hoja1!$K$22+'Todos los Datos (2)'!AF37*Hoja1!$K$23+'Todos los Datos (2)'!AK37*Hoja1!$K$24</f>
-        <v>106.74446309633402</v>
+        <v>194.0816698056887</v>
       </c>
       <c r="C37">
         <f>'Todos los Datos (2)'!C37*Hoja1!$K$17+'Todos los Datos (2)'!H37*Hoja1!$K$18+'Todos los Datos (2)'!M37*Hoja1!$K$19+'Todos los Datos (2)'!R37*Hoja1!$K$20+'Todos los Datos (2)'!W37*Hoja1!$K$21+'Todos los Datos (2)'!AB37*Hoja1!$K$22+'Todos los Datos (2)'!AG37*Hoja1!$K$23+'Todos los Datos (2)'!AL37*Hoja1!$K$24</f>
-        <v>124.27573509503439</v>
+        <v>252.71156229471939</v>
       </c>
       <c r="D37">
         <f>'Todos los Datos (2)'!D37*Hoja1!$K$17+'Todos los Datos (2)'!I37*Hoja1!$K$18+'Todos los Datos (2)'!N37*Hoja1!$K$19+'Todos los Datos (2)'!S37*Hoja1!$K$20+'Todos los Datos (2)'!X37*Hoja1!$K$21+'Todos los Datos (2)'!AC37*Hoja1!$K$22+'Todos los Datos (2)'!AH37*Hoja1!$K$23+'Todos los Datos (2)'!AM37*Hoja1!$K$24</f>
-        <v>129.98411581018394</v>
+        <v>292.22211365918838</v>
       </c>
       <c r="E37">
         <f>'Todos los Datos (2)'!E37*Hoja1!$K$17+'Todos los Datos (2)'!J37*Hoja1!$K$18+'Todos los Datos (2)'!O37*Hoja1!$K$19+'Todos los Datos (2)'!T37*Hoja1!$K$20+'Todos los Datos (2)'!Y37*Hoja1!$K$21+'Todos los Datos (2)'!AD37*Hoja1!$K$22+'Todos los Datos (2)'!AI37*Hoja1!$K$23+'Todos los Datos (2)'!AN37*Hoja1!$K$24</f>
-        <v>161.25611451056838</v>
+        <v>315.70361537971871</v>
       </c>
       <c r="F37">
         <f>'Todos los Datos (2)'!F37*Hoja1!$K$17+'Todos los Datos (2)'!K37*Hoja1!$K$18+'Todos los Datos (2)'!P37*Hoja1!$K$19+'Todos los Datos (2)'!U37*Hoja1!$K$20+'Todos los Datos (2)'!Z37*Hoja1!$K$21+'Todos los Datos (2)'!AE37*Hoja1!$K$22+'Todos los Datos (2)'!AJ37*Hoja1!$K$23+'Todos los Datos (2)'!AO37*Hoja1!$K$24</f>
-        <v>167.21268569159403</v>
+        <v>290.40090339430333</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -15786,23 +16017,23 @@
       </c>
       <c r="B38">
         <f>'Todos los Datos (2)'!B38*Hoja1!$K$17+'Todos los Datos (2)'!G38*Hoja1!$K$18+'Todos los Datos (2)'!L38*Hoja1!$K$19+'Todos los Datos (2)'!Q38*Hoja1!$K$20+'Todos los Datos (2)'!V38*Hoja1!$K$21+'Todos los Datos (2)'!AA38*Hoja1!$K$22+'Todos los Datos (2)'!AF38*Hoja1!$K$23+'Todos los Datos (2)'!AK38*Hoja1!$K$24</f>
-        <v>77.078363002385771</v>
+        <v>103.64224576985632</v>
       </c>
       <c r="C38">
         <f>'Todos los Datos (2)'!C38*Hoja1!$K$17+'Todos los Datos (2)'!H38*Hoja1!$K$18+'Todos los Datos (2)'!M38*Hoja1!$K$19+'Todos los Datos (2)'!R38*Hoja1!$K$20+'Todos los Datos (2)'!W38*Hoja1!$K$21+'Todos los Datos (2)'!AB38*Hoja1!$K$22+'Todos los Datos (2)'!AG38*Hoja1!$K$23+'Todos los Datos (2)'!AL38*Hoja1!$K$24</f>
-        <v>101.85355111029547</v>
+        <v>127.95155955608895</v>
       </c>
       <c r="D38">
         <f>'Todos los Datos (2)'!D38*Hoja1!$K$17+'Todos los Datos (2)'!I38*Hoja1!$K$18+'Todos los Datos (2)'!N38*Hoja1!$K$19+'Todos los Datos (2)'!S38*Hoja1!$K$20+'Todos los Datos (2)'!X38*Hoja1!$K$21+'Todos los Datos (2)'!AC38*Hoja1!$K$22+'Todos los Datos (2)'!AH38*Hoja1!$K$23+'Todos los Datos (2)'!AM38*Hoja1!$K$24</f>
-        <v>86.254358597907881</v>
+        <v>128.31372113553974</v>
       </c>
       <c r="E38">
         <f>'Todos los Datos (2)'!E38*Hoja1!$K$17+'Todos los Datos (2)'!J38*Hoja1!$K$18+'Todos los Datos (2)'!O38*Hoja1!$K$19+'Todos los Datos (2)'!T38*Hoja1!$K$20+'Todos los Datos (2)'!Y38*Hoja1!$K$21+'Todos los Datos (2)'!AD38*Hoja1!$K$22+'Todos los Datos (2)'!AI38*Hoja1!$K$23+'Todos los Datos (2)'!AN38*Hoja1!$K$24</f>
-        <v>63.314369609102584</v>
+        <v>99.835723789980847</v>
       </c>
       <c r="F38">
         <f>'Todos los Datos (2)'!F38*Hoja1!$K$17+'Todos los Datos (2)'!K38*Hoja1!$K$18+'Todos los Datos (2)'!P38*Hoja1!$K$19+'Todos los Datos (2)'!U38*Hoja1!$K$20+'Todos los Datos (2)'!Z38*Hoja1!$K$21+'Todos los Datos (2)'!AE38*Hoja1!$K$22+'Todos los Datos (2)'!AJ38*Hoja1!$K$23+'Todos los Datos (2)'!AO38*Hoja1!$K$24</f>
-        <v>94.512754633877762</v>
+        <v>108.91319539876106</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -15811,23 +16042,23 @@
       </c>
       <c r="B39">
         <f>'Todos los Datos (2)'!B39*Hoja1!$K$17+'Todos los Datos (2)'!G39*Hoja1!$K$18+'Todos los Datos (2)'!L39*Hoja1!$K$19+'Todos los Datos (2)'!Q39*Hoja1!$K$20+'Todos los Datos (2)'!V39*Hoja1!$K$21+'Todos los Datos (2)'!AA39*Hoja1!$K$22+'Todos los Datos (2)'!AF39*Hoja1!$K$23+'Todos los Datos (2)'!AK39*Hoja1!$K$24</f>
-        <v>70.342475486713084</v>
+        <v>97.288158327412745</v>
       </c>
       <c r="C39">
         <f>'Todos los Datos (2)'!C39*Hoja1!$K$17+'Todos los Datos (2)'!H39*Hoja1!$K$18+'Todos los Datos (2)'!M39*Hoja1!$K$19+'Todos los Datos (2)'!R39*Hoja1!$K$20+'Todos los Datos (2)'!W39*Hoja1!$K$21+'Todos los Datos (2)'!AB39*Hoja1!$K$22+'Todos los Datos (2)'!AG39*Hoja1!$K$23+'Todos los Datos (2)'!AL39*Hoja1!$K$24</f>
-        <v>72.474065652977117</v>
+        <v>105.60458915135936</v>
       </c>
       <c r="D39">
         <f>'Todos los Datos (2)'!D39*Hoja1!$K$17+'Todos los Datos (2)'!I39*Hoja1!$K$18+'Todos los Datos (2)'!N39*Hoja1!$K$19+'Todos los Datos (2)'!S39*Hoja1!$K$20+'Todos los Datos (2)'!X39*Hoja1!$K$21+'Todos los Datos (2)'!AC39*Hoja1!$K$22+'Todos los Datos (2)'!AH39*Hoja1!$K$23+'Todos los Datos (2)'!AM39*Hoja1!$K$24</f>
-        <v>83.132016484297282</v>
+        <v>117.5394414060633</v>
       </c>
       <c r="E39">
         <f>'Todos los Datos (2)'!E39*Hoja1!$K$17+'Todos los Datos (2)'!J39*Hoja1!$K$18+'Todos los Datos (2)'!O39*Hoja1!$K$19+'Todos los Datos (2)'!T39*Hoja1!$K$20+'Todos los Datos (2)'!Y39*Hoja1!$K$21+'Todos los Datos (2)'!AD39*Hoja1!$K$22+'Todos los Datos (2)'!AI39*Hoja1!$K$23+'Todos los Datos (2)'!AN39*Hoja1!$K$24</f>
-        <v>103.02685803609492</v>
+        <v>152.92718030908765</v>
       </c>
       <c r="F39">
         <f>'Todos los Datos (2)'!F39*Hoja1!$K$17+'Todos los Datos (2)'!K39*Hoja1!$K$18+'Todos los Datos (2)'!P39*Hoja1!$K$19+'Todos los Datos (2)'!U39*Hoja1!$K$20+'Todos los Datos (2)'!Z39*Hoja1!$K$21+'Todos los Datos (2)'!AE39*Hoja1!$K$22+'Todos los Datos (2)'!AJ39*Hoja1!$K$23+'Todos los Datos (2)'!AO39*Hoja1!$K$24</f>
-        <v>112.2637487565724</v>
+        <v>130.83316339011273</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -15836,23 +16067,23 @@
       </c>
       <c r="B40">
         <f>'Todos los Datos (2)'!B40*Hoja1!$K$17+'Todos los Datos (2)'!G40*Hoja1!$K$18+'Todos los Datos (2)'!L40*Hoja1!$K$19+'Todos los Datos (2)'!Q40*Hoja1!$K$20+'Todos los Datos (2)'!V40*Hoja1!$K$21+'Todos los Datos (2)'!AA40*Hoja1!$K$22+'Todos los Datos (2)'!AF40*Hoja1!$K$23+'Todos los Datos (2)'!AK40*Hoja1!$K$24</f>
-        <v>77.035106546067766</v>
+        <v>133.92784059794457</v>
       </c>
       <c r="C40">
         <f>'Todos los Datos (2)'!C40*Hoja1!$K$17+'Todos los Datos (2)'!H40*Hoja1!$K$18+'Todos los Datos (2)'!M40*Hoja1!$K$19+'Todos los Datos (2)'!R40*Hoja1!$K$20+'Todos los Datos (2)'!W40*Hoja1!$K$21+'Todos los Datos (2)'!AB40*Hoja1!$K$22+'Todos los Datos (2)'!AG40*Hoja1!$K$23+'Todos los Datos (2)'!AL40*Hoja1!$K$24</f>
-        <v>128.77510347999387</v>
+        <v>199.80223708680217</v>
       </c>
       <c r="D40">
         <f>'Todos los Datos (2)'!D40*Hoja1!$K$17+'Todos los Datos (2)'!I40*Hoja1!$K$18+'Todos los Datos (2)'!N40*Hoja1!$K$19+'Todos los Datos (2)'!S40*Hoja1!$K$20+'Todos los Datos (2)'!X40*Hoja1!$K$21+'Todos los Datos (2)'!AC40*Hoja1!$K$22+'Todos los Datos (2)'!AH40*Hoja1!$K$23+'Todos los Datos (2)'!AM40*Hoja1!$K$24</f>
-        <v>105.01303081404262</v>
+        <v>188.35492445296035</v>
       </c>
       <c r="E40">
         <f>'Todos los Datos (2)'!E40*Hoja1!$K$17+'Todos los Datos (2)'!J40*Hoja1!$K$18+'Todos los Datos (2)'!O40*Hoja1!$K$19+'Todos los Datos (2)'!T40*Hoja1!$K$20+'Todos los Datos (2)'!Y40*Hoja1!$K$21+'Todos los Datos (2)'!AD40*Hoja1!$K$22+'Todos los Datos (2)'!AI40*Hoja1!$K$23+'Todos los Datos (2)'!AN40*Hoja1!$K$24</f>
-        <v>77.035106546067766</v>
+        <v>132.88182259653601</v>
       </c>
       <c r="F40">
         <f>'Todos los Datos (2)'!F40*Hoja1!$K$17+'Todos los Datos (2)'!K40*Hoja1!$K$18+'Todos los Datos (2)'!P40*Hoja1!$K$19+'Todos los Datos (2)'!U40*Hoja1!$K$20+'Todos los Datos (2)'!Z40*Hoja1!$K$21+'Todos los Datos (2)'!AE40*Hoja1!$K$22+'Todos los Datos (2)'!AJ40*Hoja1!$K$23+'Todos los Datos (2)'!AO40*Hoja1!$K$24</f>
-        <v>128.77510347999387</v>
+        <v>225.77606735261327</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -15861,23 +16092,23 @@
       </c>
       <c r="B41">
         <f>'Todos los Datos (2)'!B41*Hoja1!$K$17+'Todos los Datos (2)'!G41*Hoja1!$K$18+'Todos los Datos (2)'!L41*Hoja1!$K$19+'Todos los Datos (2)'!Q41*Hoja1!$K$20+'Todos los Datos (2)'!V41*Hoja1!$K$21+'Todos los Datos (2)'!AA41*Hoja1!$K$22+'Todos los Datos (2)'!AF41*Hoja1!$K$23+'Todos los Datos (2)'!AK41*Hoja1!$K$24</f>
-        <v>105.79268292682927</v>
+        <v>174.51857164501985</v>
       </c>
       <c r="C41">
         <f>'Todos los Datos (2)'!C41*Hoja1!$K$17+'Todos los Datos (2)'!H41*Hoja1!$K$18+'Todos los Datos (2)'!M41*Hoja1!$K$19+'Todos los Datos (2)'!R41*Hoja1!$K$20+'Todos los Datos (2)'!W41*Hoja1!$K$21+'Todos los Datos (2)'!AB41*Hoja1!$K$22+'Todos los Datos (2)'!AG41*Hoja1!$K$23+'Todos los Datos (2)'!AL41*Hoja1!$K$24</f>
-        <v>123.78048780487804</v>
+        <v>204.31397897566927</v>
       </c>
       <c r="D41">
         <f>'Todos los Datos (2)'!D41*Hoja1!$K$17+'Todos los Datos (2)'!I41*Hoja1!$K$18+'Todos los Datos (2)'!N41*Hoja1!$K$19+'Todos los Datos (2)'!S41*Hoja1!$K$20+'Todos los Datos (2)'!X41*Hoja1!$K$21+'Todos los Datos (2)'!AC41*Hoja1!$K$22+'Todos los Datos (2)'!AH41*Hoja1!$K$23+'Todos los Datos (2)'!AM41*Hoja1!$K$24</f>
-        <v>155.48780487804879</v>
+        <v>303.08178124401667</v>
       </c>
       <c r="E41">
         <f>'Todos los Datos (2)'!E41*Hoja1!$K$17+'Todos los Datos (2)'!J41*Hoja1!$K$18+'Todos los Datos (2)'!O41*Hoja1!$K$19+'Todos los Datos (2)'!T41*Hoja1!$K$20+'Todos los Datos (2)'!Y41*Hoja1!$K$21+'Todos los Datos (2)'!AD41*Hoja1!$K$22+'Todos los Datos (2)'!AI41*Hoja1!$K$23+'Todos los Datos (2)'!AN41*Hoja1!$K$24</f>
-        <v>146.64634146341461</v>
+        <v>268.4346697232844</v>
       </c>
       <c r="F41">
         <f>'Todos los Datos (2)'!F41*Hoja1!$K$17+'Todos los Datos (2)'!K41*Hoja1!$K$18+'Todos los Datos (2)'!P41*Hoja1!$K$19+'Todos los Datos (2)'!U41*Hoja1!$K$20+'Todos los Datos (2)'!Z41*Hoja1!$K$21+'Todos los Datos (2)'!AE41*Hoja1!$K$22+'Todos los Datos (2)'!AJ41*Hoja1!$K$23+'Todos los Datos (2)'!AO41*Hoja1!$K$24</f>
-        <v>188.71951219512192</v>
+        <v>282.13688695381438</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -15886,23 +16117,23 @@
       </c>
       <c r="B42">
         <f>'Todos los Datos (2)'!B42*Hoja1!$K$17+'Todos los Datos (2)'!G42*Hoja1!$K$18+'Todos los Datos (2)'!L42*Hoja1!$K$19+'Todos los Datos (2)'!Q42*Hoja1!$K$20+'Todos los Datos (2)'!V42*Hoja1!$K$21+'Todos los Datos (2)'!AA42*Hoja1!$K$22+'Todos los Datos (2)'!AF42*Hoja1!$K$23+'Todos los Datos (2)'!AK42*Hoja1!$K$24</f>
-        <v>181.83612322155838</v>
+        <v>379.21232942146986</v>
       </c>
       <c r="C42">
         <f>'Todos los Datos (2)'!C42*Hoja1!$K$17+'Todos los Datos (2)'!H42*Hoja1!$K$18+'Todos los Datos (2)'!M42*Hoja1!$K$19+'Todos los Datos (2)'!R42*Hoja1!$K$20+'Todos los Datos (2)'!W42*Hoja1!$K$21+'Todos los Datos (2)'!AB42*Hoja1!$K$22+'Todos los Datos (2)'!AG42*Hoja1!$K$23+'Todos los Datos (2)'!AL42*Hoja1!$K$24</f>
-        <v>256.47236126809838</v>
+        <v>506.11794721101853</v>
       </c>
       <c r="D42">
         <f>'Todos los Datos (2)'!D42*Hoja1!$K$17+'Todos los Datos (2)'!I42*Hoja1!$K$18+'Todos los Datos (2)'!N42*Hoja1!$K$19+'Todos los Datos (2)'!S42*Hoja1!$K$20+'Todos los Datos (2)'!X42*Hoja1!$K$21+'Todos los Datos (2)'!AC42*Hoja1!$K$22+'Todos los Datos (2)'!AH42*Hoja1!$K$23+'Todos los Datos (2)'!AM42*Hoja1!$K$24</f>
-        <v>235.12209124997756</v>
+        <v>543.11668810882713</v>
       </c>
       <c r="E42">
         <f>'Todos los Datos (2)'!E42*Hoja1!$K$17+'Todos los Datos (2)'!J42*Hoja1!$K$18+'Todos los Datos (2)'!O42*Hoja1!$K$19+'Todos los Datos (2)'!T42*Hoja1!$K$20+'Todos los Datos (2)'!Y42*Hoja1!$K$21+'Todos los Datos (2)'!AD42*Hoja1!$K$22+'Todos los Datos (2)'!AI42*Hoja1!$K$23+'Todos los Datos (2)'!AN42*Hoja1!$K$24</f>
-        <v>221.62118520910707</v>
+        <v>494.29807356057415</v>
       </c>
       <c r="F42">
         <f>'Todos los Datos (2)'!F42*Hoja1!$K$17+'Todos los Datos (2)'!K42*Hoja1!$K$18+'Todos los Datos (2)'!P42*Hoja1!$K$19+'Todos los Datos (2)'!U42*Hoja1!$K$20+'Todos los Datos (2)'!Z42*Hoja1!$K$21+'Todos los Datos (2)'!AE42*Hoja1!$K$22+'Todos los Datos (2)'!AJ42*Hoja1!$K$23+'Todos los Datos (2)'!AO42*Hoja1!$K$24</f>
-        <v>283.96756194269517</v>
+        <v>577.75132754166998</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -15911,26 +16142,29 @@
       </c>
       <c r="B43">
         <f>'Todos los Datos (2)'!B43*Hoja1!$K$17+'Todos los Datos (2)'!G43*Hoja1!$K$18+'Todos los Datos (2)'!L43*Hoja1!$K$19+'Todos los Datos (2)'!Q43*Hoja1!$K$20+'Todos los Datos (2)'!V43*Hoja1!$K$21+'Todos los Datos (2)'!AA43*Hoja1!$K$22+'Todos los Datos (2)'!AF43*Hoja1!$K$23+'Todos los Datos (2)'!AK43*Hoja1!$K$24</f>
-        <v>117.60596180717278</v>
+        <v>162.6465936178914</v>
       </c>
       <c r="C43">
         <f>'Todos los Datos (2)'!C43*Hoja1!$K$17+'Todos los Datos (2)'!H43*Hoja1!$K$18+'Todos los Datos (2)'!M43*Hoja1!$K$19+'Todos los Datos (2)'!R43*Hoja1!$K$20+'Todos los Datos (2)'!W43*Hoja1!$K$21+'Todos los Datos (2)'!AB43*Hoja1!$K$22+'Todos los Datos (2)'!AG43*Hoja1!$K$23+'Todos los Datos (2)'!AL43*Hoja1!$K$24</f>
-        <v>158.70982766651142</v>
+        <v>236.15169761161394</v>
       </c>
       <c r="D43">
         <f>'Todos los Datos (2)'!D43*Hoja1!$K$17+'Todos los Datos (2)'!I43*Hoja1!$K$18+'Todos los Datos (2)'!N43*Hoja1!$K$19+'Todos los Datos (2)'!S43*Hoja1!$K$20+'Todos los Datos (2)'!X43*Hoja1!$K$21+'Todos los Datos (2)'!AC43*Hoja1!$K$22+'Todos los Datos (2)'!AH43*Hoja1!$K$23+'Todos los Datos (2)'!AM43*Hoja1!$K$24</f>
-        <v>141.01071262226361</v>
+        <v>233.24642324154709</v>
       </c>
       <c r="E43">
         <f>'Todos los Datos (2)'!E43*Hoja1!$K$17+'Todos los Datos (2)'!J43*Hoja1!$K$18+'Todos los Datos (2)'!O43*Hoja1!$K$19+'Todos los Datos (2)'!T43*Hoja1!$K$20+'Todos los Datos (2)'!Y43*Hoja1!$K$21+'Todos los Datos (2)'!AD43*Hoja1!$K$22+'Todos los Datos (2)'!AI43*Hoja1!$K$23+'Todos los Datos (2)'!AN43*Hoja1!$K$24</f>
-        <v>120.16767582673498</v>
+        <v>201.8797324160945</v>
       </c>
       <c r="F43">
         <f>'Todos los Datos (2)'!F43*Hoja1!$K$17+'Todos los Datos (2)'!K43*Hoja1!$K$18+'Todos los Datos (2)'!P43*Hoja1!$K$19+'Todos los Datos (2)'!U43*Hoja1!$K$20+'Todos los Datos (2)'!Z43*Hoja1!$K$21+'Todos los Datos (2)'!AE43*Hoja1!$K$22+'Todos los Datos (2)'!AJ43*Hoja1!$K$23+'Todos los Datos (2)'!AO43*Hoja1!$K$24</f>
-        <v>147.76432231020027</v>
+        <v>214.50257306588048</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J16:K16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15941,11 +16175,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -15967,25 +16202,25 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="11">
         <f>'Todos los Datos (2)'!B2*Hoja1!$K$17+'Todos los Datos (2)'!G2*Hoja1!$K$18+'Todos los Datos (2)'!L2*Hoja1!$K$19+'Todos los Datos (2)'!Q2*Hoja1!$K$20+'Todos los Datos (2)'!V2*Hoja1!$K$21+'Todos los Datos (2)'!AA2*Hoja1!$K$22+'Todos los Datos (2)'!AF2*Hoja1!$K$23+'Todos los Datos (2)'!AK2*Hoja1!$K$24</f>
-        <v>206.51872259587967</v>
+        <v>489.366037019202</v>
       </c>
       <c r="C2">
         <f>'Todos los Datos (2)'!C2*Hoja1!$K$17+'Todos los Datos (2)'!H2*Hoja1!$K$18+'Todos los Datos (2)'!M2*Hoja1!$K$19+'Todos los Datos (2)'!R2*Hoja1!$K$20+'Todos los Datos (2)'!W2*Hoja1!$K$21+'Todos los Datos (2)'!AB2*Hoja1!$K$22+'Todos los Datos (2)'!AG2*Hoja1!$K$23+'Todos los Datos (2)'!AL2*Hoja1!$K$24</f>
-        <v>247.25032629563597</v>
+        <v>599.9971193790866</v>
       </c>
       <c r="D2">
         <f>'Todos los Datos (2)'!D2*Hoja1!$K$17+'Todos los Datos (2)'!I2*Hoja1!$K$18+'Todos los Datos (2)'!N2*Hoja1!$K$19+'Todos los Datos (2)'!S2*Hoja1!$K$20+'Todos los Datos (2)'!X2*Hoja1!$K$21+'Todos los Datos (2)'!AC2*Hoja1!$K$22+'Todos los Datos (2)'!AH2*Hoja1!$K$23+'Todos los Datos (2)'!AM2*Hoja1!$K$24</f>
-        <v>253.76308635117525</v>
+        <v>658.36706114535104</v>
       </c>
       <c r="E2">
         <f>'Todos los Datos (2)'!E2*Hoja1!$K$17+'Todos los Datos (2)'!J2*Hoja1!$K$18+'Todos los Datos (2)'!O2*Hoja1!$K$19+'Todos los Datos (2)'!T2*Hoja1!$K$20+'Todos los Datos (2)'!Y2*Hoja1!$K$21+'Todos los Datos (2)'!AD2*Hoja1!$K$22+'Todos los Datos (2)'!AI2*Hoja1!$K$23+'Todos los Datos (2)'!AN2*Hoja1!$K$24</f>
-        <v>243.79994449576424</v>
+        <v>627.77554524057075</v>
       </c>
       <c r="F2">
         <f>'Todos los Datos (2)'!F2*Hoja1!$K$17+'Todos los Datos (2)'!K2*Hoja1!$K$18+'Todos los Datos (2)'!P2*Hoja1!$K$19+'Todos los Datos (2)'!U2*Hoja1!$K$20+'Todos los Datos (2)'!Z2*Hoja1!$K$21+'Todos los Datos (2)'!AE2*Hoja1!$K$22+'Todos los Datos (2)'!AJ2*Hoja1!$K$23+'Todos los Datos (2)'!AO2*Hoja1!$K$24</f>
-        <v>249.71425840685308</v>
+        <v>621.9009438841299</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -15994,23 +16229,23 @@
       </c>
       <c r="B3">
         <f>'Todos los Datos (2)'!B3*Hoja1!$K$17+'Todos los Datos (2)'!G3*Hoja1!$K$18+'Todos los Datos (2)'!L3*Hoja1!$K$19+'Todos los Datos (2)'!Q3*Hoja1!$K$20+'Todos los Datos (2)'!V3*Hoja1!$K$21+'Todos los Datos (2)'!AA3*Hoja1!$K$22+'Todos los Datos (2)'!AF3*Hoja1!$K$23+'Todos los Datos (2)'!AK3*Hoja1!$K$24</f>
-        <v>149.18530013401988</v>
+        <v>229.03479981817298</v>
       </c>
       <c r="C3">
         <f>'Todos los Datos (2)'!C3*Hoja1!$K$17+'Todos los Datos (2)'!H3*Hoja1!$K$18+'Todos los Datos (2)'!M3*Hoja1!$K$19+'Todos los Datos (2)'!R3*Hoja1!$K$20+'Todos los Datos (2)'!W3*Hoja1!$K$21+'Todos los Datos (2)'!AB3*Hoja1!$K$22+'Todos los Datos (2)'!AG3*Hoja1!$K$23+'Todos los Datos (2)'!AL3*Hoja1!$K$24</f>
-        <v>150.24335190802003</v>
+        <v>260.95522307330214</v>
       </c>
       <c r="D3">
         <f>'Todos los Datos (2)'!D3*Hoja1!$K$17+'Todos los Datos (2)'!I3*Hoja1!$K$18+'Todos los Datos (2)'!N3*Hoja1!$K$19+'Todos los Datos (2)'!S3*Hoja1!$K$20+'Todos los Datos (2)'!X3*Hoja1!$K$21+'Todos los Datos (2)'!AC3*Hoja1!$K$22+'Todos los Datos (2)'!AH3*Hoja1!$K$23+'Todos los Datos (2)'!AM3*Hoja1!$K$24</f>
-        <v>131.19841997601748</v>
+        <v>231.84047368966679</v>
       </c>
       <c r="E3">
         <f>'Todos los Datos (2)'!E3*Hoja1!$K$17+'Todos los Datos (2)'!J3*Hoja1!$K$18+'Todos los Datos (2)'!O3*Hoja1!$K$19+'Todos los Datos (2)'!T3*Hoja1!$K$20+'Todos los Datos (2)'!Y3*Hoja1!$K$21+'Todos los Datos (2)'!AD3*Hoja1!$K$22+'Todos los Datos (2)'!AI3*Hoja1!$K$23+'Todos los Datos (2)'!AN3*Hoja1!$K$24</f>
-        <v>130.49305212668406</v>
+        <v>187.39011369267519</v>
       </c>
       <c r="F3">
         <f>'Todos los Datos (2)'!F3*Hoja1!$K$17+'Todos los Datos (2)'!K3*Hoja1!$K$18+'Todos los Datos (2)'!P3*Hoja1!$K$19+'Todos los Datos (2)'!U3*Hoja1!$K$20+'Todos los Datos (2)'!Z3*Hoja1!$K$21+'Todos los Datos (2)'!AE3*Hoja1!$K$22+'Todos los Datos (2)'!AJ3*Hoja1!$K$23+'Todos los Datos (2)'!AO3*Hoja1!$K$24</f>
-        <v>195.03421034069265</v>
+        <v>293.24003292779446</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -16019,23 +16254,23 @@
       </c>
       <c r="B4">
         <f>'Todos los Datos (2)'!B4*Hoja1!$K$17+'Todos los Datos (2)'!G4*Hoja1!$K$18+'Todos los Datos (2)'!L4*Hoja1!$K$19+'Todos los Datos (2)'!Q4*Hoja1!$K$20+'Todos los Datos (2)'!V4*Hoja1!$K$21+'Todos los Datos (2)'!AA4*Hoja1!$K$22+'Todos los Datos (2)'!AF4*Hoja1!$K$23+'Todos los Datos (2)'!AK4*Hoja1!$K$24</f>
-        <v>87.201678468397574</v>
+        <v>132.8841652027308</v>
       </c>
       <c r="C4">
         <f>'Todos los Datos (2)'!C4*Hoja1!$K$17+'Todos los Datos (2)'!H4*Hoja1!$K$18+'Todos los Datos (2)'!M4*Hoja1!$K$19+'Todos los Datos (2)'!R4*Hoja1!$K$20+'Todos los Datos (2)'!W4*Hoja1!$K$21+'Todos los Datos (2)'!AB4*Hoja1!$K$22+'Todos los Datos (2)'!AG4*Hoja1!$K$23+'Todos los Datos (2)'!AL4*Hoja1!$K$24</f>
-        <v>127.19643325465512</v>
+        <v>196.3792939315428</v>
       </c>
       <c r="D4">
         <f>'Todos los Datos (2)'!D4*Hoja1!$K$17+'Todos los Datos (2)'!I4*Hoja1!$K$18+'Todos los Datos (2)'!N4*Hoja1!$K$19+'Todos los Datos (2)'!S4*Hoja1!$K$20+'Todos los Datos (2)'!X4*Hoja1!$K$21+'Todos los Datos (2)'!AC4*Hoja1!$K$22+'Todos los Datos (2)'!AH4*Hoja1!$K$23+'Todos los Datos (2)'!AM4*Hoja1!$K$24</f>
-        <v>111.24224145467261</v>
+        <v>183.43467002793011</v>
       </c>
       <c r="E4">
         <f>'Todos los Datos (2)'!E4*Hoja1!$K$17+'Todos los Datos (2)'!J4*Hoja1!$K$18+'Todos los Datos (2)'!O4*Hoja1!$K$19+'Todos los Datos (2)'!T4*Hoja1!$K$20+'Todos los Datos (2)'!Y4*Hoja1!$K$21+'Todos los Datos (2)'!AD4*Hoja1!$K$22+'Todos los Datos (2)'!AI4*Hoja1!$K$23+'Todos los Datos (2)'!AN4*Hoja1!$K$24</f>
-        <v>157.79351341900519</v>
+        <v>241.20209003401277</v>
       </c>
       <c r="F4">
         <f>'Todos los Datos (2)'!F4*Hoja1!$K$17+'Todos los Datos (2)'!K4*Hoja1!$K$18+'Todos los Datos (2)'!P4*Hoja1!$K$19+'Todos los Datos (2)'!U4*Hoja1!$K$20+'Todos los Datos (2)'!Z4*Hoja1!$K$21+'Todos los Datos (2)'!AE4*Hoja1!$K$22+'Todos los Datos (2)'!AJ4*Hoja1!$K$23+'Todos los Datos (2)'!AO4*Hoja1!$K$24</f>
-        <v>126.32223096424514</v>
+        <v>185.35654317540389</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -16044,23 +16279,23 @@
       </c>
       <c r="B5">
         <f>'Todos los Datos (2)'!B5*Hoja1!$K$17+'Todos los Datos (2)'!G5*Hoja1!$K$18+'Todos los Datos (2)'!L5*Hoja1!$K$19+'Todos los Datos (2)'!Q5*Hoja1!$K$20+'Todos los Datos (2)'!V5*Hoja1!$K$21+'Todos los Datos (2)'!AA5*Hoja1!$K$22+'Todos los Datos (2)'!AF5*Hoja1!$K$23+'Todos los Datos (2)'!AK5*Hoja1!$K$24</f>
-        <v>56.17977528089888</v>
+        <v>68.447361065615041</v>
       </c>
       <c r="C5">
         <f>'Todos los Datos (2)'!C5*Hoja1!$K$17+'Todos los Datos (2)'!H5*Hoja1!$K$18+'Todos los Datos (2)'!M5*Hoja1!$K$19+'Todos los Datos (2)'!R5*Hoja1!$K$20+'Todos los Datos (2)'!W5*Hoja1!$K$21+'Todos los Datos (2)'!AB5*Hoja1!$K$22+'Todos los Datos (2)'!AG5*Hoja1!$K$23+'Todos los Datos (2)'!AL5*Hoja1!$K$24</f>
-        <v>68.442365824445332</v>
+        <v>101.04396232257588</v>
       </c>
       <c r="D5">
         <f>'Todos los Datos (2)'!D5*Hoja1!$K$17+'Todos los Datos (2)'!I5*Hoja1!$K$18+'Todos los Datos (2)'!N5*Hoja1!$K$19+'Todos los Datos (2)'!S5*Hoja1!$K$20+'Todos los Datos (2)'!X5*Hoja1!$K$21+'Todos los Datos (2)'!AC5*Hoja1!$K$22+'Todos los Datos (2)'!AH5*Hoja1!$K$23+'Todos los Datos (2)'!AM5*Hoja1!$K$24</f>
-        <v>120.05931671704784</v>
+        <v>134.97895205722611</v>
       </c>
       <c r="E5">
         <f>'Todos los Datos (2)'!E5*Hoja1!$K$17+'Todos los Datos (2)'!J5*Hoja1!$K$18+'Todos los Datos (2)'!O5*Hoja1!$K$19+'Todos los Datos (2)'!T5*Hoja1!$K$20+'Todos los Datos (2)'!Y5*Hoja1!$K$21+'Todos los Datos (2)'!AD5*Hoja1!$K$22+'Todos los Datos (2)'!AI5*Hoja1!$K$23+'Todos los Datos (2)'!AN5*Hoja1!$K$24</f>
-        <v>126.90355329949239</v>
+        <v>129.73198594611603</v>
       </c>
       <c r="F5">
         <f>'Todos los Datos (2)'!F5*Hoja1!$K$17+'Todos los Datos (2)'!K5*Hoja1!$K$18+'Todos los Datos (2)'!P5*Hoja1!$K$19+'Todos los Datos (2)'!U5*Hoja1!$K$20+'Todos los Datos (2)'!Z5*Hoja1!$K$21+'Todos los Datos (2)'!AE5*Hoja1!$K$22+'Todos los Datos (2)'!AJ5*Hoja1!$K$23+'Todos los Datos (2)'!AO5*Hoja1!$K$24</f>
-        <v>116.63719842582557</v>
+        <v>104.2573413488456</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -16069,23 +16304,23 @@
       </c>
       <c r="B6">
         <f>'Todos los Datos (2)'!B6*Hoja1!$K$17+'Todos los Datos (2)'!G6*Hoja1!$K$18+'Todos los Datos (2)'!L6*Hoja1!$K$19+'Todos los Datos (2)'!Q6*Hoja1!$K$20+'Todos los Datos (2)'!V6*Hoja1!$K$21+'Todos los Datos (2)'!AA6*Hoja1!$K$22+'Todos los Datos (2)'!AF6*Hoja1!$K$23+'Todos los Datos (2)'!AK6*Hoja1!$K$24</f>
-        <v>86.798931705455914</v>
+        <v>123.60570967360098</v>
       </c>
       <c r="C6">
         <f>'Todos los Datos (2)'!C6*Hoja1!$K$17+'Todos los Datos (2)'!H6*Hoja1!$K$18+'Todos los Datos (2)'!M6*Hoja1!$K$19+'Todos los Datos (2)'!R6*Hoja1!$K$20+'Todos los Datos (2)'!W6*Hoja1!$K$21+'Todos los Datos (2)'!AB6*Hoja1!$K$22+'Todos los Datos (2)'!AG6*Hoja1!$K$23+'Todos los Datos (2)'!AL6*Hoja1!$K$24</f>
-        <v>131.62914917970241</v>
+        <v>194.56313689377745</v>
       </c>
       <c r="D6">
         <f>'Todos los Datos (2)'!D6*Hoja1!$K$17+'Todos los Datos (2)'!I6*Hoja1!$K$18+'Todos los Datos (2)'!N6*Hoja1!$K$19+'Todos los Datos (2)'!S6*Hoja1!$K$20+'Todos los Datos (2)'!X6*Hoja1!$K$21+'Todos los Datos (2)'!AC6*Hoja1!$K$22+'Todos los Datos (2)'!AH6*Hoja1!$K$23+'Todos los Datos (2)'!AM6*Hoja1!$K$24</f>
-        <v>50.55322396032048</v>
+        <v>68.3637647180568</v>
       </c>
       <c r="E6">
         <f>'Todos los Datos (2)'!E6*Hoja1!$K$17+'Todos los Datos (2)'!J6*Hoja1!$K$18+'Todos los Datos (2)'!O6*Hoja1!$K$19+'Todos los Datos (2)'!T6*Hoja1!$K$20+'Todos los Datos (2)'!Y6*Hoja1!$K$21+'Todos los Datos (2)'!AD6*Hoja1!$K$22+'Todos los Datos (2)'!AI6*Hoja1!$K$23+'Todos los Datos (2)'!AN6*Hoja1!$K$24</f>
-        <v>53.414727203357501</v>
+        <v>61.536606210833298</v>
       </c>
       <c r="F6">
         <f>'Todos los Datos (2)'!F6*Hoja1!$K$17+'Todos los Datos (2)'!K6*Hoja1!$K$18+'Todos los Datos (2)'!P6*Hoja1!$K$19+'Todos los Datos (2)'!U6*Hoja1!$K$20+'Todos los Datos (2)'!Z6*Hoja1!$K$21+'Todos los Datos (2)'!AE6*Hoja1!$K$22+'Todos los Datos (2)'!AJ6*Hoja1!$K$23+'Todos los Datos (2)'!AO6*Hoja1!$K$24</f>
-        <v>69.629912247233889</v>
+        <v>69.452140972632364</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -16094,23 +16329,23 @@
       </c>
       <c r="B7">
         <f>'Todos los Datos (2)'!B7*Hoja1!$K$17+'Todos los Datos (2)'!G7*Hoja1!$K$18+'Todos los Datos (2)'!L7*Hoja1!$K$19+'Todos los Datos (2)'!Q7*Hoja1!$K$20+'Todos los Datos (2)'!V7*Hoja1!$K$21+'Todos los Datos (2)'!AA7*Hoja1!$K$22+'Todos los Datos (2)'!AF7*Hoja1!$K$23+'Todos los Datos (2)'!AK7*Hoja1!$K$24</f>
-        <v>70.391553013638358</v>
+        <v>78.162230802237971</v>
       </c>
       <c r="C7">
         <f>'Todos los Datos (2)'!C7*Hoja1!$K$17+'Todos los Datos (2)'!H7*Hoja1!$K$18+'Todos los Datos (2)'!M7*Hoja1!$K$19+'Todos los Datos (2)'!R7*Hoja1!$K$20+'Todos los Datos (2)'!W7*Hoja1!$K$21+'Todos los Datos (2)'!AB7*Hoja1!$K$22+'Todos los Datos (2)'!AG7*Hoja1!$K$23+'Todos los Datos (2)'!AL7*Hoja1!$K$24</f>
-        <v>73.534033058890088</v>
+        <v>94.807833641398162</v>
       </c>
       <c r="D7">
         <f>'Todos los Datos (2)'!D7*Hoja1!$K$17+'Todos los Datos (2)'!I7*Hoja1!$K$18+'Todos los Datos (2)'!N7*Hoja1!$K$19+'Todos los Datos (2)'!S7*Hoja1!$K$20+'Todos los Datos (2)'!X7*Hoja1!$K$21+'Todos los Datos (2)'!AC7*Hoja1!$K$22+'Todos los Datos (2)'!AH7*Hoja1!$K$23+'Todos los Datos (2)'!AM7*Hoja1!$K$24</f>
-        <v>104.0160894978317</v>
+        <v>158.1501948587989</v>
       </c>
       <c r="E7">
         <f>'Todos los Datos (2)'!E7*Hoja1!$K$17+'Todos los Datos (2)'!J7*Hoja1!$K$18+'Todos los Datos (2)'!O7*Hoja1!$K$19+'Todos los Datos (2)'!T7*Hoja1!$K$20+'Todos los Datos (2)'!Y7*Hoja1!$K$21+'Todos los Datos (2)'!AD7*Hoja1!$K$22+'Todos los Datos (2)'!AI7*Hoja1!$K$23+'Todos los Datos (2)'!AN7*Hoja1!$K$24</f>
-        <v>133.24115391867261</v>
+        <v>180.05673315048932</v>
       </c>
       <c r="F7">
         <f>'Todos los Datos (2)'!F7*Hoja1!$K$17+'Todos los Datos (2)'!K7*Hoja1!$K$18+'Todos los Datos (2)'!P7*Hoja1!$K$19+'Todos los Datos (2)'!U7*Hoja1!$K$20+'Todos los Datos (2)'!Z7*Hoja1!$K$21+'Todos los Datos (2)'!AE7*Hoja1!$K$22+'Todos los Datos (2)'!AJ7*Hoja1!$K$23+'Todos los Datos (2)'!AO7*Hoja1!$K$24</f>
-        <v>129.47017786437056</v>
+        <v>135.63503243219526</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -16119,23 +16354,23 @@
       </c>
       <c r="B8">
         <f>'Todos los Datos (2)'!B8*Hoja1!$K$17+'Todos los Datos (2)'!G8*Hoja1!$K$18+'Todos los Datos (2)'!L8*Hoja1!$K$19+'Todos los Datos (2)'!Q8*Hoja1!$K$20+'Todos los Datos (2)'!V8*Hoja1!$K$21+'Todos los Datos (2)'!AA8*Hoja1!$K$22+'Todos los Datos (2)'!AF8*Hoja1!$K$23+'Todos los Datos (2)'!AK8*Hoja1!$K$24</f>
-        <v>85.750119559261805</v>
+        <v>171.95079727766449</v>
       </c>
       <c r="C8">
         <f>'Todos los Datos (2)'!C8*Hoja1!$K$17+'Todos los Datos (2)'!H8*Hoja1!$K$18+'Todos los Datos (2)'!M8*Hoja1!$K$19+'Todos los Datos (2)'!R8*Hoja1!$K$20+'Todos los Datos (2)'!W8*Hoja1!$K$21+'Todos los Datos (2)'!AB8*Hoja1!$K$22+'Todos los Datos (2)'!AG8*Hoja1!$K$23+'Todos los Datos (2)'!AL8*Hoja1!$K$24</f>
-        <v>101.34824841722542</v>
+        <v>195.63441740435553</v>
       </c>
       <c r="D8">
         <f>'Todos los Datos (2)'!D8*Hoja1!$K$17+'Todos los Datos (2)'!I8*Hoja1!$K$18+'Todos los Datos (2)'!N8*Hoja1!$K$19+'Todos los Datos (2)'!S8*Hoja1!$K$20+'Todos los Datos (2)'!X8*Hoja1!$K$21+'Todos los Datos (2)'!AC8*Hoja1!$K$22+'Todos los Datos (2)'!AH8*Hoja1!$K$23+'Todos los Datos (2)'!AM8*Hoja1!$K$24</f>
-        <v>90.659175341971164</v>
+        <v>176.54359905541239</v>
       </c>
       <c r="E8">
         <f>'Todos los Datos (2)'!E8*Hoja1!$K$17+'Todos los Datos (2)'!J8*Hoja1!$K$18+'Todos los Datos (2)'!O8*Hoja1!$K$19+'Todos los Datos (2)'!T8*Hoja1!$K$20+'Todos los Datos (2)'!Y8*Hoja1!$K$21+'Todos los Datos (2)'!AD8*Hoja1!$K$22+'Todos los Datos (2)'!AI8*Hoja1!$K$23+'Todos los Datos (2)'!AN8*Hoja1!$K$24</f>
-        <v>92.670304646500469</v>
+        <v>184.37683184898941</v>
       </c>
       <c r="F8">
         <f>'Todos los Datos (2)'!F8*Hoja1!$K$17+'Todos los Datos (2)'!K8*Hoja1!$K$18+'Todos los Datos (2)'!P8*Hoja1!$K$19+'Todos los Datos (2)'!U8*Hoja1!$K$20+'Todos los Datos (2)'!Z8*Hoja1!$K$21+'Todos los Datos (2)'!AE8*Hoja1!$K$22+'Todos los Datos (2)'!AJ8*Hoja1!$K$23+'Todos los Datos (2)'!AO8*Hoja1!$K$24</f>
-        <v>79.305004386478871</v>
+        <v>157.63120407946221</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -16144,23 +16379,23 @@
       </c>
       <c r="B9">
         <f>'Todos los Datos (2)'!B9*Hoja1!$K$17+'Todos los Datos (2)'!G9*Hoja1!$K$18+'Todos los Datos (2)'!L9*Hoja1!$K$19+'Todos los Datos (2)'!Q9*Hoja1!$K$20+'Todos los Datos (2)'!V9*Hoja1!$K$21+'Todos los Datos (2)'!AA9*Hoja1!$K$22+'Todos los Datos (2)'!AF9*Hoja1!$K$23+'Todos los Datos (2)'!AK9*Hoja1!$K$24</f>
-        <v>145.52250237431451</v>
+        <v>242.79617839341779</v>
       </c>
       <c r="C9">
         <f>'Todos los Datos (2)'!C9*Hoja1!$K$17+'Todos los Datos (2)'!H9*Hoja1!$K$18+'Todos los Datos (2)'!M9*Hoja1!$K$19+'Todos los Datos (2)'!R9*Hoja1!$K$20+'Todos los Datos (2)'!W9*Hoja1!$K$21+'Todos los Datos (2)'!AB9*Hoja1!$K$22+'Todos los Datos (2)'!AG9*Hoja1!$K$23+'Todos los Datos (2)'!AL9*Hoja1!$K$24</f>
-        <v>172.59734689500937</v>
+        <v>300.26413663836126</v>
       </c>
       <c r="D9">
         <f>'Todos los Datos (2)'!D9*Hoja1!$K$17+'Todos los Datos (2)'!I9*Hoja1!$K$18+'Todos los Datos (2)'!N9*Hoja1!$K$19+'Todos los Datos (2)'!S9*Hoja1!$K$20+'Todos los Datos (2)'!X9*Hoja1!$K$21+'Todos los Datos (2)'!AC9*Hoja1!$K$22+'Todos los Datos (2)'!AH9*Hoja1!$K$23+'Todos los Datos (2)'!AM9*Hoja1!$K$24</f>
-        <v>185.46459973652767</v>
+        <v>361.88580215129372</v>
       </c>
       <c r="E9">
         <f>'Todos los Datos (2)'!E9*Hoja1!$K$17+'Todos los Datos (2)'!J9*Hoja1!$K$18+'Todos los Datos (2)'!O9*Hoja1!$K$19+'Todos los Datos (2)'!T9*Hoja1!$K$20+'Todos los Datos (2)'!Y9*Hoja1!$K$21+'Todos los Datos (2)'!AD9*Hoja1!$K$22+'Todos los Datos (2)'!AI9*Hoja1!$K$23+'Todos los Datos (2)'!AN9*Hoja1!$K$24</f>
-        <v>197.10639992647285</v>
+        <v>372.4616776274367</v>
       </c>
       <c r="F9">
         <f>'Todos los Datos (2)'!F9*Hoja1!$K$17+'Todos los Datos (2)'!K9*Hoja1!$K$18+'Todos los Datos (2)'!P9*Hoja1!$K$19+'Todos los Datos (2)'!U9*Hoja1!$K$20+'Todos los Datos (2)'!Z9*Hoja1!$K$21+'Todos los Datos (2)'!AE9*Hoja1!$K$22+'Todos los Datos (2)'!AJ9*Hoja1!$K$23+'Todos los Datos (2)'!AO9*Hoja1!$K$24</f>
-        <v>202.31457369565882</v>
+        <v>362.68046413426953</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -16169,23 +16404,23 @@
       </c>
       <c r="B10">
         <f>'Todos los Datos (2)'!B10*Hoja1!$K$17+'Todos los Datos (2)'!G10*Hoja1!$K$18+'Todos los Datos (2)'!L10*Hoja1!$K$19+'Todos los Datos (2)'!Q10*Hoja1!$K$20+'Todos los Datos (2)'!V10*Hoja1!$K$21+'Todos los Datos (2)'!AA10*Hoja1!$K$22+'Todos los Datos (2)'!AF10*Hoja1!$K$23+'Todos los Datos (2)'!AK10*Hoja1!$K$24</f>
-        <v>89.011787502018421</v>
+        <v>119.71600125248605</v>
       </c>
       <c r="C10">
         <f>'Todos los Datos (2)'!C10*Hoja1!$K$17+'Todos los Datos (2)'!H10*Hoja1!$K$18+'Todos los Datos (2)'!M10*Hoja1!$K$19+'Todos los Datos (2)'!R10*Hoja1!$K$20+'Todos los Datos (2)'!W10*Hoja1!$K$21+'Todos los Datos (2)'!AB10*Hoja1!$K$22+'Todos los Datos (2)'!AG10*Hoja1!$K$23+'Todos los Datos (2)'!AL10*Hoja1!$K$24</f>
-        <v>111.01243339253996</v>
+        <v>199.08430976779448</v>
       </c>
       <c r="D10">
         <f>'Todos los Datos (2)'!D10*Hoja1!$K$17+'Todos los Datos (2)'!I10*Hoja1!$K$18+'Todos los Datos (2)'!N10*Hoja1!$K$19+'Todos los Datos (2)'!S10*Hoja1!$K$20+'Todos los Datos (2)'!X10*Hoja1!$K$21+'Todos los Datos (2)'!AC10*Hoja1!$K$22+'Todos los Datos (2)'!AH10*Hoja1!$K$23+'Todos los Datos (2)'!AM10*Hoja1!$K$24</f>
-        <v>123.12288067172616</v>
+        <v>212.36509719254843</v>
       </c>
       <c r="E10">
         <f>'Todos los Datos (2)'!E10*Hoja1!$K$17+'Todos los Datos (2)'!J10*Hoja1!$K$18+'Todos los Datos (2)'!O10*Hoja1!$K$19+'Todos los Datos (2)'!T10*Hoja1!$K$20+'Todos los Datos (2)'!Y10*Hoja1!$K$21+'Todos los Datos (2)'!AD10*Hoja1!$K$22+'Todos los Datos (2)'!AI10*Hoja1!$K$23+'Todos los Datos (2)'!AN10*Hoja1!$K$24</f>
-        <v>130.38914903923785</v>
+        <v>199.44166856096382</v>
       </c>
       <c r="F10">
         <f>'Todos los Datos (2)'!F10*Hoja1!$K$17+'Todos los Datos (2)'!K10*Hoja1!$K$18+'Todos los Datos (2)'!P10*Hoja1!$K$19+'Todos los Datos (2)'!U10*Hoja1!$K$20+'Todos los Datos (2)'!Z10*Hoja1!$K$21+'Todos los Datos (2)'!AE10*Hoja1!$K$22+'Todos los Datos (2)'!AJ10*Hoja1!$K$23+'Todos los Datos (2)'!AO10*Hoja1!$K$24</f>
-        <v>135.03148716292591</v>
+        <v>221.85775580242341</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -16194,48 +16429,48 @@
       </c>
       <c r="B11">
         <f>'Todos los Datos (2)'!B11*Hoja1!$K$17+'Todos los Datos (2)'!G11*Hoja1!$K$18+'Todos los Datos (2)'!L11*Hoja1!$K$19+'Todos los Datos (2)'!Q11*Hoja1!$K$20+'Todos los Datos (2)'!V11*Hoja1!$K$21+'Todos los Datos (2)'!AA11*Hoja1!$K$22+'Todos los Datos (2)'!AF11*Hoja1!$K$23+'Todos los Datos (2)'!AK11*Hoja1!$K$24</f>
-        <v>117.90574465874859</v>
+        <v>176.03415173272174</v>
       </c>
       <c r="C11">
         <f>'Todos los Datos (2)'!C11*Hoja1!$K$17+'Todos los Datos (2)'!H11*Hoja1!$K$18+'Todos los Datos (2)'!M11*Hoja1!$K$19+'Todos los Datos (2)'!R11*Hoja1!$K$20+'Todos los Datos (2)'!W11*Hoja1!$K$21+'Todos los Datos (2)'!AB11*Hoja1!$K$22+'Todos los Datos (2)'!AG11*Hoja1!$K$23+'Todos los Datos (2)'!AL11*Hoja1!$K$24</f>
-        <v>105.78621143391391</v>
+        <v>175.7466452960316</v>
       </c>
       <c r="D11">
         <f>'Todos los Datos (2)'!D11*Hoja1!$K$17+'Todos los Datos (2)'!I11*Hoja1!$K$18+'Todos los Datos (2)'!N11*Hoja1!$K$19+'Todos los Datos (2)'!S11*Hoja1!$K$20+'Todos los Datos (2)'!X11*Hoja1!$K$21+'Todos los Datos (2)'!AC11*Hoja1!$K$22+'Todos los Datos (2)'!AH11*Hoja1!$K$23+'Todos los Datos (2)'!AM11*Hoja1!$K$24</f>
-        <v>121.02219605942034</v>
+        <v>215.52725979091309</v>
       </c>
       <c r="E11">
         <f>'Todos los Datos (2)'!E11*Hoja1!$K$17+'Todos los Datos (2)'!J11*Hoja1!$K$18+'Todos los Datos (2)'!O11*Hoja1!$K$19+'Todos los Datos (2)'!T11*Hoja1!$K$20+'Todos los Datos (2)'!Y11*Hoja1!$K$21+'Todos los Datos (2)'!AD11*Hoja1!$K$22+'Todos los Datos (2)'!AI11*Hoja1!$K$23+'Todos los Datos (2)'!AN11*Hoja1!$K$24</f>
-        <v>115.82811039163408</v>
+        <v>200.27979462891523</v>
       </c>
       <c r="F11">
         <f>'Todos los Datos (2)'!F11*Hoja1!$K$17+'Todos los Datos (2)'!K11*Hoja1!$K$18+'Todos los Datos (2)'!P11*Hoja1!$K$19+'Todos los Datos (2)'!U11*Hoja1!$K$20+'Todos los Datos (2)'!Z11*Hoja1!$K$21+'Todos los Datos (2)'!AE11*Hoja1!$K$22+'Todos los Datos (2)'!AJ11*Hoja1!$K$23+'Todos los Datos (2)'!AO11*Hoja1!$K$24</f>
-        <v>111.49970566847882</v>
+        <v>185.83455285400947</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <f>'Todos los Datos (2)'!B12*Hoja1!$K$17+'Todos los Datos (2)'!G12*Hoja1!$K$18+'Todos los Datos (2)'!L12*Hoja1!$K$19+'Todos los Datos (2)'!Q12*Hoja1!$K$20+'Todos los Datos (2)'!V12*Hoja1!$K$21+'Todos los Datos (2)'!AA12*Hoja1!$K$22+'Todos los Datos (2)'!AF12*Hoja1!$K$23+'Todos los Datos (2)'!AK12*Hoja1!$K$24</f>
-        <v>98.404974317383079</v>
+        <v>170.61349374281775</v>
       </c>
       <c r="C12">
         <f>'Todos los Datos (2)'!C12*Hoja1!$K$17+'Todos los Datos (2)'!H12*Hoja1!$K$18+'Todos los Datos (2)'!M12*Hoja1!$K$19+'Todos los Datos (2)'!R12*Hoja1!$K$20+'Todos los Datos (2)'!W12*Hoja1!$K$21+'Todos los Datos (2)'!AB12*Hoja1!$K$22+'Todos los Datos (2)'!AG12*Hoja1!$K$23+'Todos los Datos (2)'!AL12*Hoja1!$K$24</f>
-        <v>136.52338469856718</v>
+        <v>266.64971884138856</v>
       </c>
       <c r="D12">
         <f>'Todos los Datos (2)'!D12*Hoja1!$K$17+'Todos los Datos (2)'!I12*Hoja1!$K$18+'Todos los Datos (2)'!N12*Hoja1!$K$19+'Todos los Datos (2)'!S12*Hoja1!$K$20+'Todos los Datos (2)'!X12*Hoja1!$K$21+'Todos los Datos (2)'!AC12*Hoja1!$K$22+'Todos los Datos (2)'!AH12*Hoja1!$K$23+'Todos los Datos (2)'!AM12*Hoja1!$K$24</f>
-        <v>144.09299810759663</v>
+        <v>315.57819015484063</v>
       </c>
       <c r="E12">
         <f>'Todos los Datos (2)'!E12*Hoja1!$K$17+'Todos los Datos (2)'!J12*Hoja1!$K$18+'Todos los Datos (2)'!O12*Hoja1!$K$19+'Todos los Datos (2)'!T12*Hoja1!$K$20+'Todos los Datos (2)'!Y12*Hoja1!$K$21+'Todos los Datos (2)'!AD12*Hoja1!$K$22+'Todos los Datos (2)'!AI12*Hoja1!$K$23+'Todos los Datos (2)'!AN12*Hoja1!$K$24</f>
-        <v>148.68883482022167</v>
+        <v>302.46081656813823</v>
       </c>
       <c r="F12">
         <f>'Todos los Datos (2)'!F12*Hoja1!$K$17+'Todos los Datos (2)'!K12*Hoja1!$K$18+'Todos los Datos (2)'!P12*Hoja1!$K$19+'Todos los Datos (2)'!U12*Hoja1!$K$20+'Todos los Datos (2)'!Z12*Hoja1!$K$21+'Todos los Datos (2)'!AE12*Hoja1!$K$22+'Todos los Datos (2)'!AJ12*Hoja1!$K$23+'Todos los Datos (2)'!AO12*Hoja1!$K$24</f>
-        <v>149.77020816436874</v>
+        <v>274.70612550281589</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -16244,23 +16479,23 @@
       </c>
       <c r="B13">
         <f>'Todos los Datos (2)'!B13*Hoja1!$K$17+'Todos los Datos (2)'!G13*Hoja1!$K$18+'Todos los Datos (2)'!L13*Hoja1!$K$19+'Todos los Datos (2)'!Q13*Hoja1!$K$20+'Todos los Datos (2)'!V13*Hoja1!$K$21+'Todos los Datos (2)'!AA13*Hoja1!$K$22+'Todos los Datos (2)'!AF13*Hoja1!$K$23+'Todos los Datos (2)'!AK13*Hoja1!$K$24</f>
-        <v>169.99779904205928</v>
+        <v>314.23195215284989</v>
       </c>
       <c r="C13">
         <f>'Todos los Datos (2)'!C13*Hoja1!$K$17+'Todos los Datos (2)'!H13*Hoja1!$K$18+'Todos los Datos (2)'!M13*Hoja1!$K$19+'Todos los Datos (2)'!R13*Hoja1!$K$20+'Todos los Datos (2)'!W13*Hoja1!$K$21+'Todos los Datos (2)'!AB13*Hoja1!$K$22+'Todos los Datos (2)'!AG13*Hoja1!$K$23+'Todos los Datos (2)'!AL13*Hoja1!$K$24</f>
-        <v>206.41841258528711</v>
+        <v>392.3482294176971</v>
       </c>
       <c r="D13">
         <f>'Todos los Datos (2)'!D13*Hoja1!$K$17+'Todos los Datos (2)'!I13*Hoja1!$K$18+'Todos los Datos (2)'!N13*Hoja1!$K$19+'Todos los Datos (2)'!S13*Hoja1!$K$20+'Todos los Datos (2)'!X13*Hoja1!$K$21+'Todos los Datos (2)'!AC13*Hoja1!$K$22+'Todos los Datos (2)'!AH13*Hoja1!$K$23+'Todos los Datos (2)'!AM13*Hoja1!$K$24</f>
-        <v>212.91647888652489</v>
+        <v>434.71182764492733</v>
       </c>
       <c r="E13">
         <f>'Todos los Datos (2)'!E13*Hoja1!$K$17+'Todos los Datos (2)'!J13*Hoja1!$K$18+'Todos los Datos (2)'!O13*Hoja1!$K$19+'Todos los Datos (2)'!T13*Hoja1!$K$20+'Todos los Datos (2)'!Y13*Hoja1!$K$21+'Todos los Datos (2)'!AD13*Hoja1!$K$22+'Todos los Datos (2)'!AI13*Hoja1!$K$23+'Todos los Datos (2)'!AN13*Hoja1!$K$24</f>
-        <v>207.25687275318879</v>
+        <v>421.29054162159235</v>
       </c>
       <c r="F13">
         <f>'Todos los Datos (2)'!F13*Hoja1!$K$17+'Todos los Datos (2)'!K13*Hoja1!$K$18+'Todos los Datos (2)'!P13*Hoja1!$K$19+'Todos los Datos (2)'!U13*Hoja1!$K$20+'Todos los Datos (2)'!Z13*Hoja1!$K$21+'Todos los Datos (2)'!AE13*Hoja1!$K$22+'Todos los Datos (2)'!AJ13*Hoja1!$K$23+'Todos los Datos (2)'!AO13*Hoja1!$K$24</f>
-        <v>220.41021663714588</v>
+        <v>464.33515236040625</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -16269,23 +16504,23 @@
       </c>
       <c r="B14">
         <f>'Todos los Datos (2)'!B14*Hoja1!$K$17+'Todos los Datos (2)'!G14*Hoja1!$K$18+'Todos los Datos (2)'!L14*Hoja1!$K$19+'Todos los Datos (2)'!Q14*Hoja1!$K$20+'Todos los Datos (2)'!V14*Hoja1!$K$21+'Todos los Datos (2)'!AA14*Hoja1!$K$22+'Todos los Datos (2)'!AF14*Hoja1!$K$23+'Todos los Datos (2)'!AK14*Hoja1!$K$24</f>
-        <v>110.44696675442003</v>
+        <v>198.26550811340488</v>
       </c>
       <c r="C14">
         <f>'Todos los Datos (2)'!C14*Hoja1!$K$17+'Todos los Datos (2)'!H14*Hoja1!$K$18+'Todos los Datos (2)'!M14*Hoja1!$K$19+'Todos los Datos (2)'!R14*Hoja1!$K$20+'Todos los Datos (2)'!W14*Hoja1!$K$21+'Todos los Datos (2)'!AB14*Hoja1!$K$22+'Todos los Datos (2)'!AG14*Hoja1!$K$23+'Todos los Datos (2)'!AL14*Hoja1!$K$24</f>
-        <v>132.88881216463108</v>
+        <v>230.66625938013681</v>
       </c>
       <c r="D14">
         <f>'Todos los Datos (2)'!D14*Hoja1!$K$17+'Todos los Datos (2)'!I14*Hoja1!$K$18+'Todos los Datos (2)'!N14*Hoja1!$K$19+'Todos los Datos (2)'!S14*Hoja1!$K$20+'Todos los Datos (2)'!X14*Hoja1!$K$21+'Todos los Datos (2)'!AC14*Hoja1!$K$22+'Todos los Datos (2)'!AH14*Hoja1!$K$23+'Todos los Datos (2)'!AM14*Hoja1!$K$24</f>
-        <v>124.50908463165163</v>
+        <v>227.71930594983829</v>
       </c>
       <c r="E14">
         <f>'Todos los Datos (2)'!E14*Hoja1!$K$17+'Todos los Datos (2)'!J14*Hoja1!$K$18+'Todos los Datos (2)'!O14*Hoja1!$K$19+'Todos los Datos (2)'!T14*Hoja1!$K$20+'Todos los Datos (2)'!Y14*Hoja1!$K$21+'Todos los Datos (2)'!AD14*Hoja1!$K$22+'Todos los Datos (2)'!AI14*Hoja1!$K$23+'Todos los Datos (2)'!AN14*Hoja1!$K$24</f>
-        <v>132.13355775178744</v>
+        <v>252.50014120192085</v>
       </c>
       <c r="F14">
         <f>'Todos los Datos (2)'!F14*Hoja1!$K$17+'Todos los Datos (2)'!K14*Hoja1!$K$18+'Todos los Datos (2)'!P14*Hoja1!$K$19+'Todos los Datos (2)'!U14*Hoja1!$K$20+'Todos los Datos (2)'!Z14*Hoja1!$K$21+'Todos los Datos (2)'!AE14*Hoja1!$K$22+'Todos los Datos (2)'!AJ14*Hoja1!$K$23+'Todos los Datos (2)'!AO14*Hoja1!$K$24</f>
-        <v>136.55719074130019</v>
+        <v>250.30237288757877</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -16294,23 +16529,23 @@
       </c>
       <c r="B15">
         <f>'Todos los Datos (2)'!B15*Hoja1!$K$17+'Todos los Datos (2)'!G15*Hoja1!$K$18+'Todos los Datos (2)'!L15*Hoja1!$K$19+'Todos los Datos (2)'!Q15*Hoja1!$K$20+'Todos los Datos (2)'!V15*Hoja1!$K$21+'Todos los Datos (2)'!AA15*Hoja1!$K$22+'Todos los Datos (2)'!AF15*Hoja1!$K$23+'Todos los Datos (2)'!AK15*Hoja1!$K$24</f>
-        <v>95.303338639156976</v>
+        <v>145.77624556420346</v>
       </c>
       <c r="C15">
         <f>'Todos los Datos (2)'!C15*Hoja1!$K$17+'Todos los Datos (2)'!H15*Hoja1!$K$18+'Todos los Datos (2)'!M15*Hoja1!$K$19+'Todos los Datos (2)'!R15*Hoja1!$K$20+'Todos los Datos (2)'!W15*Hoja1!$K$21+'Todos los Datos (2)'!AB15*Hoja1!$K$22+'Todos los Datos (2)'!AG15*Hoja1!$K$23+'Todos los Datos (2)'!AL15*Hoja1!$K$24</f>
-        <v>118.474340633878</v>
+        <v>183.07148040890073</v>
       </c>
       <c r="D15">
         <f>'Todos los Datos (2)'!D15*Hoja1!$K$17+'Todos los Datos (2)'!I15*Hoja1!$K$18+'Todos los Datos (2)'!N15*Hoja1!$K$19+'Todos los Datos (2)'!S15*Hoja1!$K$20+'Todos los Datos (2)'!X15*Hoja1!$K$21+'Todos los Datos (2)'!AC15*Hoja1!$K$22+'Todos los Datos (2)'!AH15*Hoja1!$K$23+'Todos los Datos (2)'!AM15*Hoja1!$K$24</f>
-        <v>109.5081702967903</v>
+        <v>173.42277829688612</v>
       </c>
       <c r="E15">
         <f>'Todos los Datos (2)'!E15*Hoja1!$K$17+'Todos los Datos (2)'!J15*Hoja1!$K$18+'Todos los Datos (2)'!O15*Hoja1!$K$19+'Todos los Datos (2)'!T15*Hoja1!$K$20+'Todos los Datos (2)'!Y15*Hoja1!$K$21+'Todos los Datos (2)'!AD15*Hoja1!$K$22+'Todos los Datos (2)'!AI15*Hoja1!$K$23+'Todos los Datos (2)'!AN15*Hoja1!$K$24</f>
-        <v>102.35538272450685</v>
+        <v>174.50029403919939</v>
       </c>
       <c r="F15">
         <f>'Todos los Datos (2)'!F15*Hoja1!$K$17+'Todos los Datos (2)'!K15*Hoja1!$K$18+'Todos los Datos (2)'!P15*Hoja1!$K$19+'Todos los Datos (2)'!U15*Hoja1!$K$20+'Todos los Datos (2)'!Z15*Hoja1!$K$21+'Todos los Datos (2)'!AE15*Hoja1!$K$22+'Todos los Datos (2)'!AJ15*Hoja1!$K$23+'Todos los Datos (2)'!AO15*Hoja1!$K$24</f>
-        <v>95.706312586891258</v>
+        <v>149.29121343278842</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -16319,23 +16554,23 @@
       </c>
       <c r="B16">
         <f>'Todos los Datos (2)'!B16*Hoja1!$K$17+'Todos los Datos (2)'!G16*Hoja1!$K$18+'Todos los Datos (2)'!L16*Hoja1!$K$19+'Todos los Datos (2)'!Q16*Hoja1!$K$20+'Todos los Datos (2)'!V16*Hoja1!$K$21+'Todos los Datos (2)'!AA16*Hoja1!$K$22+'Todos los Datos (2)'!AF16*Hoja1!$K$23+'Todos los Datos (2)'!AK16*Hoja1!$K$24</f>
-        <v>34.602076124567475</v>
+        <v>21.979661933396123</v>
       </c>
       <c r="C16">
         <f>'Todos los Datos (2)'!C16*Hoja1!$K$17+'Todos los Datos (2)'!H16*Hoja1!$K$18+'Todos los Datos (2)'!M16*Hoja1!$K$19+'Todos los Datos (2)'!R16*Hoja1!$K$20+'Todos los Datos (2)'!W16*Hoja1!$K$21+'Todos los Datos (2)'!AB16*Hoja1!$K$22+'Todos los Datos (2)'!AG16*Hoja1!$K$23+'Todos los Datos (2)'!AL16*Hoja1!$K$24</f>
-        <v>49.019607843137251</v>
+        <v>45.501434335526447</v>
       </c>
       <c r="D16">
         <f>'Todos los Datos (2)'!D16*Hoja1!$K$17+'Todos los Datos (2)'!I16*Hoja1!$K$18+'Todos los Datos (2)'!N16*Hoja1!$K$19+'Todos los Datos (2)'!S16*Hoja1!$K$20+'Todos los Datos (2)'!X16*Hoja1!$K$21+'Todos los Datos (2)'!AC16*Hoja1!$K$22+'Todos los Datos (2)'!AH16*Hoja1!$K$23+'Todos los Datos (2)'!AM16*Hoja1!$K$24</f>
-        <v>108.99653979238754</v>
+        <v>52.130748282087318</v>
       </c>
       <c r="E16">
         <f>'Todos los Datos (2)'!E16*Hoja1!$K$17+'Todos los Datos (2)'!J16*Hoja1!$K$18+'Todos los Datos (2)'!O16*Hoja1!$K$19+'Todos los Datos (2)'!T16*Hoja1!$K$20+'Todos los Datos (2)'!Y16*Hoja1!$K$21+'Todos los Datos (2)'!AD16*Hoja1!$K$22+'Todos los Datos (2)'!AI16*Hoja1!$K$23+'Todos los Datos (2)'!AN16*Hoja1!$K$24</f>
-        <v>77.277970011534009</v>
+        <v>73.038101777740266</v>
       </c>
       <c r="F16">
         <f>'Todos los Datos (2)'!F16*Hoja1!$K$17+'Todos los Datos (2)'!K16*Hoja1!$K$18+'Todos los Datos (2)'!P16*Hoja1!$K$19+'Todos los Datos (2)'!U16*Hoja1!$K$20+'Todos los Datos (2)'!Z16*Hoja1!$K$21+'Todos los Datos (2)'!AE16*Hoja1!$K$22+'Todos los Datos (2)'!AJ16*Hoja1!$K$23+'Todos los Datos (2)'!AO16*Hoja1!$K$24</f>
-        <v>90.542099192618224</v>
+        <v>71.531472530610557</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -16344,23 +16579,23 @@
       </c>
       <c r="B17">
         <f>'Todos los Datos (2)'!B17*Hoja1!$K$17+'Todos los Datos (2)'!G17*Hoja1!$K$18+'Todos los Datos (2)'!L17*Hoja1!$K$19+'Todos los Datos (2)'!Q17*Hoja1!$K$20+'Todos los Datos (2)'!V17*Hoja1!$K$21+'Todos los Datos (2)'!AA17*Hoja1!$K$22+'Todos los Datos (2)'!AF17*Hoja1!$K$23+'Todos los Datos (2)'!AK17*Hoja1!$K$24</f>
-        <v>132.81724347298118</v>
+        <v>150.34436365175426</v>
       </c>
       <c r="C17">
         <f>'Todos los Datos (2)'!C17*Hoja1!$K$17+'Todos los Datos (2)'!H17*Hoja1!$K$18+'Todos los Datos (2)'!M17*Hoja1!$K$19+'Todos los Datos (2)'!R17*Hoja1!$K$20+'Todos los Datos (2)'!W17*Hoja1!$K$21+'Todos los Datos (2)'!AB17*Hoja1!$K$22+'Todos los Datos (2)'!AG17*Hoja1!$K$23+'Todos los Datos (2)'!AL17*Hoja1!$K$24</f>
-        <v>103.21797207043109</v>
+        <v>117.02752901720447</v>
       </c>
       <c r="D17">
         <f>'Todos los Datos (2)'!D17*Hoja1!$K$17+'Todos los Datos (2)'!I17*Hoja1!$K$18+'Todos los Datos (2)'!N17*Hoja1!$K$19+'Todos los Datos (2)'!S17*Hoja1!$K$20+'Todos los Datos (2)'!X17*Hoja1!$K$21+'Todos los Datos (2)'!AC17*Hoja1!$K$22+'Todos los Datos (2)'!AH17*Hoja1!$K$23+'Todos los Datos (2)'!AM17*Hoja1!$K$24</f>
-        <v>70.582877959927146</v>
+        <v>65.902728282524691</v>
       </c>
       <c r="E17">
         <f>'Todos los Datos (2)'!E17*Hoja1!$K$17+'Todos los Datos (2)'!J17*Hoja1!$K$18+'Todos los Datos (2)'!O17*Hoja1!$K$19+'Todos los Datos (2)'!T17*Hoja1!$K$20+'Todos los Datos (2)'!Y17*Hoja1!$K$21+'Todos los Datos (2)'!AD17*Hoja1!$K$22+'Todos los Datos (2)'!AI17*Hoja1!$K$23+'Todos los Datos (2)'!AN17*Hoja1!$K$24</f>
-        <v>85.761991499696421</v>
+        <v>82.570410223227356</v>
       </c>
       <c r="F17">
         <f>'Todos los Datos (2)'!F17*Hoja1!$K$17+'Todos los Datos (2)'!K17*Hoja1!$K$18+'Todos los Datos (2)'!P17*Hoja1!$K$19+'Todos los Datos (2)'!U17*Hoja1!$K$20+'Todos los Datos (2)'!Z17*Hoja1!$K$21+'Todos los Datos (2)'!AE17*Hoja1!$K$22+'Todos los Datos (2)'!AJ17*Hoja1!$K$23+'Todos los Datos (2)'!AO17*Hoja1!$K$24</f>
-        <v>81.967213114754102</v>
+        <v>94.940954048694636</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -16369,23 +16604,23 @@
       </c>
       <c r="B18">
         <f>'Todos los Datos (2)'!B18*Hoja1!$K$17+'Todos los Datos (2)'!G18*Hoja1!$K$18+'Todos los Datos (2)'!L18*Hoja1!$K$19+'Todos los Datos (2)'!Q18*Hoja1!$K$20+'Todos los Datos (2)'!V18*Hoja1!$K$21+'Todos los Datos (2)'!AA18*Hoja1!$K$22+'Todos los Datos (2)'!AF18*Hoja1!$K$23+'Todos los Datos (2)'!AK18*Hoja1!$K$24</f>
-        <v>93.170385991599119</v>
+        <v>161.87453104515487</v>
       </c>
       <c r="C18">
         <f>'Todos los Datos (2)'!C18*Hoja1!$K$17+'Todos los Datos (2)'!H18*Hoja1!$K$18+'Todos los Datos (2)'!M18*Hoja1!$K$19+'Todos los Datos (2)'!R18*Hoja1!$K$20+'Todos los Datos (2)'!W18*Hoja1!$K$21+'Todos los Datos (2)'!AB18*Hoja1!$K$22+'Todos los Datos (2)'!AG18*Hoja1!$K$23+'Todos los Datos (2)'!AL18*Hoja1!$K$24</f>
-        <v>137.59485575011669</v>
+        <v>267.28700779264017</v>
       </c>
       <c r="D18">
         <f>'Todos los Datos (2)'!D18*Hoja1!$K$17+'Todos los Datos (2)'!I18*Hoja1!$K$18+'Todos los Datos (2)'!N18*Hoja1!$K$19+'Todos los Datos (2)'!S18*Hoja1!$K$20+'Todos los Datos (2)'!X18*Hoja1!$K$21+'Todos los Datos (2)'!AC18*Hoja1!$K$22+'Todos los Datos (2)'!AH18*Hoja1!$K$23+'Todos los Datos (2)'!AM18*Hoja1!$K$24</f>
-        <v>119.87692520440442</v>
+        <v>246.00314419005574</v>
       </c>
       <c r="E18">
         <f>'Todos los Datos (2)'!E18*Hoja1!$K$17+'Todos los Datos (2)'!J18*Hoja1!$K$18+'Todos los Datos (2)'!O18*Hoja1!$K$19+'Todos los Datos (2)'!T18*Hoja1!$K$20+'Todos los Datos (2)'!Y18*Hoja1!$K$21+'Todos los Datos (2)'!AD18*Hoja1!$K$22+'Todos los Datos (2)'!AI18*Hoja1!$K$23+'Todos los Datos (2)'!AN18*Hoja1!$K$24</f>
-        <v>132.58197783962248</v>
+        <v>282.05227484512125</v>
       </c>
       <c r="F18">
         <f>'Todos los Datos (2)'!F18*Hoja1!$K$17+'Todos los Datos (2)'!K18*Hoja1!$K$18+'Todos los Datos (2)'!P18*Hoja1!$K$19+'Todos los Datos (2)'!U18*Hoja1!$K$20+'Todos los Datos (2)'!Z18*Hoja1!$K$21+'Todos los Datos (2)'!AE18*Hoja1!$K$22+'Todos los Datos (2)'!AJ18*Hoja1!$K$23+'Todos los Datos (2)'!AO18*Hoja1!$K$24</f>
-        <v>147.01560906466614</v>
+        <v>305.23796885345729</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -16394,23 +16629,23 @@
       </c>
       <c r="B19">
         <f>'Todos los Datos (2)'!B19*Hoja1!$K$17+'Todos los Datos (2)'!G19*Hoja1!$K$18+'Todos los Datos (2)'!L19*Hoja1!$K$19+'Todos los Datos (2)'!Q19*Hoja1!$K$20+'Todos los Datos (2)'!V19*Hoja1!$K$21+'Todos los Datos (2)'!AA19*Hoja1!$K$22+'Todos los Datos (2)'!AF19*Hoja1!$K$23+'Todos los Datos (2)'!AK19*Hoja1!$K$24</f>
-        <v>100.87116001834019</v>
+        <v>80.413041480567429</v>
       </c>
       <c r="C19">
         <f>'Todos los Datos (2)'!C19*Hoja1!$K$17+'Todos los Datos (2)'!H19*Hoja1!$K$18+'Todos los Datos (2)'!M19*Hoja1!$K$19+'Todos los Datos (2)'!R19*Hoja1!$K$20+'Todos los Datos (2)'!W19*Hoja1!$K$21+'Todos los Datos (2)'!AB19*Hoja1!$K$22+'Todos los Datos (2)'!AG19*Hoja1!$K$23+'Todos los Datos (2)'!AL19*Hoja1!$K$24</f>
-        <v>88.262265016047692</v>
+        <v>111.52343689314559</v>
       </c>
       <c r="D19">
         <f>'Todos los Datos (2)'!D19*Hoja1!$K$17+'Todos los Datos (2)'!I19*Hoja1!$K$18+'Todos los Datos (2)'!N19*Hoja1!$K$19+'Todos los Datos (2)'!S19*Hoja1!$K$20+'Todos los Datos (2)'!X19*Hoja1!$K$21+'Todos los Datos (2)'!AC19*Hoja1!$K$22+'Todos los Datos (2)'!AH19*Hoja1!$K$23+'Todos los Datos (2)'!AM19*Hoja1!$K$24</f>
-        <v>73.93397524071527</v>
+        <v>107.09400022530397</v>
       </c>
       <c r="E19">
         <f>'Todos los Datos (2)'!E19*Hoja1!$K$17+'Todos los Datos (2)'!J19*Hoja1!$K$18+'Todos los Datos (2)'!O19*Hoja1!$K$19+'Todos los Datos (2)'!T19*Hoja1!$K$20+'Todos los Datos (2)'!Y19*Hoja1!$K$21+'Todos los Datos (2)'!AD19*Hoja1!$K$22+'Todos los Datos (2)'!AI19*Hoja1!$K$23+'Todos los Datos (2)'!AN19*Hoja1!$K$24</f>
-        <v>141.56350298028428</v>
+        <v>187.16049759988755</v>
       </c>
       <c r="F19">
         <f>'Todos los Datos (2)'!F19*Hoja1!$K$17+'Todos los Datos (2)'!K19*Hoja1!$K$18+'Todos los Datos (2)'!P19*Hoja1!$K$19+'Todos los Datos (2)'!U19*Hoja1!$K$20+'Todos los Datos (2)'!Z19*Hoja1!$K$21+'Todos los Datos (2)'!AE19*Hoja1!$K$22+'Todos los Datos (2)'!AJ19*Hoja1!$K$23+'Todos los Datos (2)'!AO19*Hoja1!$K$24</f>
-        <v>138.69784502521779</v>
+        <v>175.79167486981308</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -16419,23 +16654,23 @@
       </c>
       <c r="B20">
         <f>'Todos los Datos (2)'!B20*Hoja1!$K$17+'Todos los Datos (2)'!G20*Hoja1!$K$18+'Todos los Datos (2)'!L20*Hoja1!$K$19+'Todos los Datos (2)'!Q20*Hoja1!$K$20+'Todos los Datos (2)'!V20*Hoja1!$K$21+'Todos los Datos (2)'!AA20*Hoja1!$K$22+'Todos los Datos (2)'!AF20*Hoja1!$K$23+'Todos los Datos (2)'!AK20*Hoja1!$K$24</f>
-        <v>83.064969585441901</v>
+        <v>156.33078517111227</v>
       </c>
       <c r="C20">
         <f>'Todos los Datos (2)'!C20*Hoja1!$K$17+'Todos los Datos (2)'!H20*Hoja1!$K$18+'Todos los Datos (2)'!M20*Hoja1!$K$19+'Todos los Datos (2)'!R20*Hoja1!$K$20+'Todos los Datos (2)'!W20*Hoja1!$K$21+'Todos los Datos (2)'!AB20*Hoja1!$K$22+'Todos los Datos (2)'!AG20*Hoja1!$K$23+'Todos los Datos (2)'!AL20*Hoja1!$K$24</f>
-        <v>115.35381417301367</v>
+        <v>215.20136463209923</v>
       </c>
       <c r="D20">
         <f>'Todos los Datos (2)'!D20*Hoja1!$K$17+'Todos los Datos (2)'!I20*Hoja1!$K$18+'Todos los Datos (2)'!N20*Hoja1!$K$19+'Todos los Datos (2)'!S20*Hoja1!$K$20+'Todos los Datos (2)'!X20*Hoja1!$K$21+'Todos los Datos (2)'!AC20*Hoja1!$K$22+'Todos los Datos (2)'!AH20*Hoja1!$K$23+'Todos los Datos (2)'!AM20*Hoja1!$K$24</f>
-        <v>125.15122084206581</v>
+        <v>242.68929036732672</v>
       </c>
       <c r="E20">
         <f>'Todos los Datos (2)'!E20*Hoja1!$K$17+'Todos los Datos (2)'!J20*Hoja1!$K$18+'Todos los Datos (2)'!O20*Hoja1!$K$19+'Todos los Datos (2)'!T20*Hoja1!$K$20+'Todos los Datos (2)'!Y20*Hoja1!$K$21+'Todos los Datos (2)'!AD20*Hoja1!$K$22+'Todos los Datos (2)'!AI20*Hoja1!$K$23+'Todos los Datos (2)'!AN20*Hoja1!$K$24</f>
-        <v>121.06186849324405</v>
+        <v>250.75504752289376</v>
       </c>
       <c r="F20">
         <f>'Todos los Datos (2)'!F20*Hoja1!$K$17+'Todos los Datos (2)'!K20*Hoja1!$K$18+'Todos los Datos (2)'!P20*Hoja1!$K$19+'Todos los Datos (2)'!U20*Hoja1!$K$20+'Todos los Datos (2)'!Z20*Hoja1!$K$21+'Todos los Datos (2)'!AE20*Hoja1!$K$22+'Todos los Datos (2)'!AJ20*Hoja1!$K$23+'Todos los Datos (2)'!AO20*Hoja1!$K$24</f>
-        <v>136.90810884492834</v>
+        <v>275.52224902924581</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -16444,23 +16679,23 @@
       </c>
       <c r="B21">
         <f>'Todos los Datos (2)'!B21*Hoja1!$K$17+'Todos los Datos (2)'!G21*Hoja1!$K$18+'Todos los Datos (2)'!L21*Hoja1!$K$19+'Todos los Datos (2)'!Q21*Hoja1!$K$20+'Todos los Datos (2)'!V21*Hoja1!$K$21+'Todos los Datos (2)'!AA21*Hoja1!$K$22+'Todos los Datos (2)'!AF21*Hoja1!$K$23+'Todos los Datos (2)'!AK21*Hoja1!$K$24</f>
-        <v>79.263067694944311</v>
+        <v>141.60919187892932</v>
       </c>
       <c r="C21">
         <f>'Todos los Datos (2)'!C21*Hoja1!$K$17+'Todos los Datos (2)'!H21*Hoja1!$K$18+'Todos los Datos (2)'!M21*Hoja1!$K$19+'Todos los Datos (2)'!R21*Hoja1!$K$20+'Todos los Datos (2)'!W21*Hoja1!$K$21+'Todos los Datos (2)'!AB21*Hoja1!$K$22+'Todos los Datos (2)'!AG21*Hoja1!$K$23+'Todos los Datos (2)'!AL21*Hoja1!$K$24</f>
-        <v>135.38988860325625</v>
+        <v>225.5777373946928</v>
       </c>
       <c r="D21">
         <f>'Todos los Datos (2)'!D21*Hoja1!$K$17+'Todos los Datos (2)'!I21*Hoja1!$K$18+'Todos los Datos (2)'!N21*Hoja1!$K$19+'Todos los Datos (2)'!S21*Hoja1!$K$20+'Todos los Datos (2)'!X21*Hoja1!$K$21+'Todos los Datos (2)'!AC21*Hoja1!$K$22+'Todos los Datos (2)'!AH21*Hoja1!$K$23+'Todos los Datos (2)'!AM21*Hoja1!$K$24</f>
-        <v>122.10796915167094</v>
+        <v>254.52021096511967</v>
       </c>
       <c r="E21">
         <f>'Todos los Datos (2)'!E21*Hoja1!$K$17+'Todos los Datos (2)'!J21*Hoja1!$K$18+'Todos los Datos (2)'!O21*Hoja1!$K$19+'Todos los Datos (2)'!T21*Hoja1!$K$20+'Todos los Datos (2)'!Y21*Hoja1!$K$21+'Todos los Datos (2)'!AD21*Hoja1!$K$22+'Todos los Datos (2)'!AI21*Hoja1!$K$23+'Todos los Datos (2)'!AN21*Hoja1!$K$24</f>
-        <v>116.10968294772921</v>
+        <v>219.81964212534015</v>
       </c>
       <c r="F21">
         <f>'Todos los Datos (2)'!F21*Hoja1!$K$17+'Todos los Datos (2)'!K21*Hoja1!$K$18+'Todos los Datos (2)'!P21*Hoja1!$K$19+'Todos los Datos (2)'!U21*Hoja1!$K$20+'Todos los Datos (2)'!Z21*Hoja1!$K$21+'Todos los Datos (2)'!AE21*Hoja1!$K$22+'Todos los Datos (2)'!AJ21*Hoja1!$K$23+'Todos los Datos (2)'!AO21*Hoja1!$K$24</f>
-        <v>104.54155955441303</v>
+        <v>182.03852507222371</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -16469,23 +16704,23 @@
       </c>
       <c r="B22">
         <f>'Todos los Datos (2)'!B22*Hoja1!$K$17+'Todos los Datos (2)'!G22*Hoja1!$K$18+'Todos los Datos (2)'!L22*Hoja1!$K$19+'Todos los Datos (2)'!Q22*Hoja1!$K$20+'Todos los Datos (2)'!V22*Hoja1!$K$21+'Todos los Datos (2)'!AA22*Hoja1!$K$22+'Todos los Datos (2)'!AF22*Hoja1!$K$23+'Todos los Datos (2)'!AK22*Hoja1!$K$24</f>
-        <v>96.470588235294116</v>
+        <v>143.61970079806289</v>
       </c>
       <c r="C22">
         <f>'Todos los Datos (2)'!C22*Hoja1!$K$17+'Todos los Datos (2)'!H22*Hoja1!$K$18+'Todos los Datos (2)'!M22*Hoja1!$K$19+'Todos los Datos (2)'!R22*Hoja1!$K$20+'Todos los Datos (2)'!W22*Hoja1!$K$21+'Todos los Datos (2)'!AB22*Hoja1!$K$22+'Todos los Datos (2)'!AG22*Hoja1!$K$23+'Todos los Datos (2)'!AL22*Hoja1!$K$24</f>
-        <v>142.05882352941174</v>
+        <v>211.20019270710537</v>
       </c>
       <c r="D22">
         <f>'Todos los Datos (2)'!D22*Hoja1!$K$17+'Todos los Datos (2)'!I22*Hoja1!$K$18+'Todos los Datos (2)'!N22*Hoja1!$K$19+'Todos los Datos (2)'!S22*Hoja1!$K$20+'Todos los Datos (2)'!X22*Hoja1!$K$21+'Todos los Datos (2)'!AC22*Hoja1!$K$22+'Todos los Datos (2)'!AH22*Hoja1!$K$23+'Todos los Datos (2)'!AM22*Hoja1!$K$24</f>
-        <v>166.61764705882354</v>
+        <v>301.75077471745101</v>
       </c>
       <c r="E22">
         <f>'Todos los Datos (2)'!E22*Hoja1!$K$17+'Todos los Datos (2)'!J22*Hoja1!$K$18+'Todos los Datos (2)'!O22*Hoja1!$K$19+'Todos los Datos (2)'!T22*Hoja1!$K$20+'Todos los Datos (2)'!Y22*Hoja1!$K$21+'Todos los Datos (2)'!AD22*Hoja1!$K$22+'Todos los Datos (2)'!AI22*Hoja1!$K$23+'Todos los Datos (2)'!AN22*Hoja1!$K$24</f>
-        <v>170.4411764705882</v>
+        <v>291.17355452912449</v>
       </c>
       <c r="F22">
         <f>'Todos los Datos (2)'!F22*Hoja1!$K$17+'Todos los Datos (2)'!K22*Hoja1!$K$18+'Todos los Datos (2)'!P22*Hoja1!$K$19+'Todos los Datos (2)'!U22*Hoja1!$K$20+'Todos los Datos (2)'!Z22*Hoja1!$K$21+'Todos los Datos (2)'!AE22*Hoja1!$K$22+'Todos los Datos (2)'!AJ22*Hoja1!$K$23+'Todos los Datos (2)'!AO22*Hoja1!$K$24</f>
-        <v>186.47058823529409</v>
+        <v>271.36796646054177</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -16494,23 +16729,23 @@
       </c>
       <c r="B23">
         <f>'Todos los Datos (2)'!B23*Hoja1!$K$17+'Todos los Datos (2)'!G23*Hoja1!$K$18+'Todos los Datos (2)'!L23*Hoja1!$K$19+'Todos los Datos (2)'!Q23*Hoja1!$K$20+'Todos los Datos (2)'!V23*Hoja1!$K$21+'Todos los Datos (2)'!AA23*Hoja1!$K$22+'Todos los Datos (2)'!AF23*Hoja1!$K$23+'Todos los Datos (2)'!AK23*Hoja1!$K$24</f>
-        <v>132.08884688090734</v>
+        <v>261.96568538589872</v>
       </c>
       <c r="C23">
         <f>'Todos los Datos (2)'!C23*Hoja1!$K$17+'Todos los Datos (2)'!H23*Hoja1!$K$18+'Todos los Datos (2)'!M23*Hoja1!$K$19+'Todos los Datos (2)'!R23*Hoja1!$K$20+'Todos los Datos (2)'!W23*Hoja1!$K$21+'Todos los Datos (2)'!AB23*Hoja1!$K$22+'Todos los Datos (2)'!AG23*Hoja1!$K$23+'Todos los Datos (2)'!AL23*Hoja1!$K$24</f>
-        <v>157.72684310018906</v>
+        <v>322.2228289004737</v>
       </c>
       <c r="D23">
         <f>'Todos los Datos (2)'!D23*Hoja1!$K$17+'Todos los Datos (2)'!I23*Hoja1!$K$18+'Todos los Datos (2)'!N23*Hoja1!$K$19+'Todos los Datos (2)'!S23*Hoja1!$K$20+'Todos los Datos (2)'!X23*Hoja1!$K$21+'Todos los Datos (2)'!AC23*Hoja1!$K$22+'Todos los Datos (2)'!AH23*Hoja1!$K$23+'Todos los Datos (2)'!AM23*Hoja1!$K$24</f>
-        <v>167.09002835538752</v>
+        <v>363.90708262681915</v>
       </c>
       <c r="E23">
         <f>'Todos los Datos (2)'!E23*Hoja1!$K$17+'Todos los Datos (2)'!J23*Hoja1!$K$18+'Todos los Datos (2)'!O23*Hoja1!$K$19+'Todos los Datos (2)'!T23*Hoja1!$K$20+'Todos los Datos (2)'!Y23*Hoja1!$K$21+'Todos los Datos (2)'!AD23*Hoja1!$K$22+'Todos los Datos (2)'!AI23*Hoja1!$K$23+'Todos los Datos (2)'!AN23*Hoja1!$K$24</f>
-        <v>156.78166351606808</v>
+        <v>324.92003853055422</v>
       </c>
       <c r="F23">
         <f>'Todos los Datos (2)'!F23*Hoja1!$K$17+'Todos los Datos (2)'!K23*Hoja1!$K$18+'Todos los Datos (2)'!P23*Hoja1!$K$19+'Todos los Datos (2)'!U23*Hoja1!$K$20+'Todos los Datos (2)'!Z23*Hoja1!$K$21+'Todos los Datos (2)'!AE23*Hoja1!$K$22+'Todos los Datos (2)'!AJ23*Hoja1!$K$23+'Todos los Datos (2)'!AO23*Hoja1!$K$24</f>
-        <v>163.81143667296789</v>
+        <v>333.81401230519839</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -16519,23 +16754,23 @@
       </c>
       <c r="B24">
         <f>'Todos los Datos (2)'!B24*Hoja1!$K$17+'Todos los Datos (2)'!G24*Hoja1!$K$18+'Todos los Datos (2)'!L24*Hoja1!$K$19+'Todos los Datos (2)'!Q24*Hoja1!$K$20+'Todos los Datos (2)'!V24*Hoja1!$K$21+'Todos los Datos (2)'!AA24*Hoja1!$K$22+'Todos los Datos (2)'!AF24*Hoja1!$K$23+'Todos los Datos (2)'!AK24*Hoja1!$K$24</f>
-        <v>82.854749940177072</v>
+        <v>152.04424290176726</v>
       </c>
       <c r="C24">
         <f>'Todos los Datos (2)'!C24*Hoja1!$K$17+'Todos los Datos (2)'!H24*Hoja1!$K$18+'Todos los Datos (2)'!M24*Hoja1!$K$19+'Todos los Datos (2)'!R24*Hoja1!$K$20+'Todos los Datos (2)'!W24*Hoja1!$K$21+'Todos los Datos (2)'!AB24*Hoja1!$K$22+'Todos los Datos (2)'!AG24*Hoja1!$K$23+'Todos los Datos (2)'!AL24*Hoja1!$K$24</f>
-        <v>149.85642498205311</v>
+        <v>236.57624495392758</v>
       </c>
       <c r="D24">
         <f>'Todos los Datos (2)'!D24*Hoja1!$K$17+'Todos los Datos (2)'!I24*Hoja1!$K$18+'Todos los Datos (2)'!N24*Hoja1!$K$19+'Todos los Datos (2)'!S24*Hoja1!$K$20+'Todos los Datos (2)'!X24*Hoja1!$K$21+'Todos los Datos (2)'!AC24*Hoja1!$K$22+'Todos los Datos (2)'!AH24*Hoja1!$K$23+'Todos los Datos (2)'!AM24*Hoja1!$K$24</f>
-        <v>117.85116056472839</v>
+        <v>217.64119464355474</v>
       </c>
       <c r="E24">
         <f>'Todos los Datos (2)'!E24*Hoja1!$K$17+'Todos los Datos (2)'!J24*Hoja1!$K$18+'Todos los Datos (2)'!O24*Hoja1!$K$19+'Todos los Datos (2)'!T24*Hoja1!$K$20+'Todos los Datos (2)'!Y24*Hoja1!$K$21+'Todos los Datos (2)'!AD24*Hoja1!$K$22+'Todos los Datos (2)'!AI24*Hoja1!$K$23+'Todos los Datos (2)'!AN24*Hoja1!$K$24</f>
-        <v>106.18569035654463</v>
+        <v>186.94631657001187</v>
       </c>
       <c r="F24">
         <f>'Todos los Datos (2)'!F24*Hoja1!$K$17+'Todos los Datos (2)'!K24*Hoja1!$K$18+'Todos los Datos (2)'!P24*Hoja1!$K$19+'Todos los Datos (2)'!U24*Hoja1!$K$20+'Todos los Datos (2)'!Z24*Hoja1!$K$21+'Todos los Datos (2)'!AE24*Hoja1!$K$22+'Todos los Datos (2)'!AJ24*Hoja1!$K$23+'Todos los Datos (2)'!AO24*Hoja1!$K$24</f>
-        <v>119.04761904761907</v>
+        <v>216.15768581889324</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -16544,23 +16779,23 @@
       </c>
       <c r="B25">
         <f>'Todos los Datos (2)'!B25*Hoja1!$K$17+'Todos los Datos (2)'!G25*Hoja1!$K$18+'Todos los Datos (2)'!L25*Hoja1!$K$19+'Todos los Datos (2)'!Q25*Hoja1!$K$20+'Todos los Datos (2)'!V25*Hoja1!$K$21+'Todos los Datos (2)'!AA25*Hoja1!$K$22+'Todos los Datos (2)'!AF25*Hoja1!$K$23+'Todos los Datos (2)'!AK25*Hoja1!$K$24</f>
-        <v>86.594337732230287</v>
+        <v>93.56356818620506</v>
       </c>
       <c r="C25">
         <f>'Todos los Datos (2)'!C25*Hoja1!$K$17+'Todos los Datos (2)'!H25*Hoja1!$K$18+'Todos los Datos (2)'!M25*Hoja1!$K$19+'Todos los Datos (2)'!R25*Hoja1!$K$20+'Todos los Datos (2)'!W25*Hoja1!$K$21+'Todos los Datos (2)'!AB25*Hoja1!$K$22+'Todos los Datos (2)'!AG25*Hoja1!$K$23+'Todos los Datos (2)'!AL25*Hoja1!$K$24</f>
-        <v>87.882517962957664</v>
+        <v>120.64307002864987</v>
       </c>
       <c r="D25">
         <f>'Todos los Datos (2)'!D25*Hoja1!$K$17+'Todos los Datos (2)'!I25*Hoja1!$K$18+'Todos los Datos (2)'!N25*Hoja1!$K$19+'Todos los Datos (2)'!S25*Hoja1!$K$20+'Todos los Datos (2)'!X25*Hoja1!$K$21+'Todos los Datos (2)'!AC25*Hoja1!$K$22+'Todos los Datos (2)'!AH25*Hoja1!$K$23+'Todos los Datos (2)'!AM25*Hoja1!$K$24</f>
-        <v>92.748976612372275</v>
+        <v>137.31514771876812</v>
       </c>
       <c r="E25">
         <f>'Todos los Datos (2)'!E25*Hoja1!$K$17+'Todos los Datos (2)'!J25*Hoja1!$K$18+'Todos los Datos (2)'!O25*Hoja1!$K$19+'Todos los Datos (2)'!T25*Hoja1!$K$20+'Todos los Datos (2)'!Y25*Hoja1!$K$21+'Todos los Datos (2)'!AD25*Hoja1!$K$22+'Todos los Datos (2)'!AI25*Hoja1!$K$23+'Todos los Datos (2)'!AN25*Hoja1!$K$24</f>
-        <v>110.64036870580827</v>
+        <v>150.57445726089801</v>
       </c>
       <c r="F25">
         <f>'Todos los Datos (2)'!F25*Hoja1!$K$17+'Todos los Datos (2)'!K25*Hoja1!$K$18+'Todos los Datos (2)'!P25*Hoja1!$K$19+'Todos los Datos (2)'!U25*Hoja1!$K$20+'Todos los Datos (2)'!Z25*Hoja1!$K$21+'Todos los Datos (2)'!AE25*Hoja1!$K$22+'Todos los Datos (2)'!AJ25*Hoja1!$K$23+'Todos los Datos (2)'!AO25*Hoja1!$K$24</f>
-        <v>145.4212349354479</v>
+        <v>179.1453659726688</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -16569,23 +16804,23 @@
       </c>
       <c r="B26">
         <f>'Todos los Datos (2)'!B26*Hoja1!$K$17+'Todos los Datos (2)'!G26*Hoja1!$K$18+'Todos los Datos (2)'!L26*Hoja1!$K$19+'Todos los Datos (2)'!Q26*Hoja1!$K$20+'Todos los Datos (2)'!V26*Hoja1!$K$21+'Todos los Datos (2)'!AA26*Hoja1!$K$22+'Todos los Datos (2)'!AF26*Hoja1!$K$23+'Todos los Datos (2)'!AK26*Hoja1!$K$24</f>
-        <v>123.16910785619174</v>
+        <v>172.43756951754841</v>
       </c>
       <c r="C26">
         <f>'Todos los Datos (2)'!C26*Hoja1!$K$17+'Todos los Datos (2)'!H26*Hoja1!$K$18+'Todos los Datos (2)'!M26*Hoja1!$K$19+'Todos los Datos (2)'!R26*Hoja1!$K$20+'Todos los Datos (2)'!W26*Hoja1!$K$21+'Todos los Datos (2)'!AB26*Hoja1!$K$22+'Todos los Datos (2)'!AG26*Hoja1!$K$23+'Todos los Datos (2)'!AL26*Hoja1!$K$24</f>
-        <v>95.705725699067898</v>
+        <v>125.42859943791828</v>
       </c>
       <c r="D26">
         <f>'Todos los Datos (2)'!D26*Hoja1!$K$17+'Todos los Datos (2)'!I26*Hoja1!$K$18+'Todos los Datos (2)'!N26*Hoja1!$K$19+'Todos los Datos (2)'!S26*Hoja1!$K$20+'Todos los Datos (2)'!X26*Hoja1!$K$21+'Todos los Datos (2)'!AC26*Hoja1!$K$22+'Todos los Datos (2)'!AH26*Hoja1!$K$23+'Todos los Datos (2)'!AM26*Hoja1!$K$24</f>
-        <v>70.322902796271649</v>
+        <v>116.03234880106839</v>
       </c>
       <c r="E26">
         <f>'Todos los Datos (2)'!E26*Hoja1!$K$17+'Todos los Datos (2)'!J26*Hoja1!$K$18+'Todos los Datos (2)'!O26*Hoja1!$K$19+'Todos los Datos (2)'!T26*Hoja1!$K$20+'Todos los Datos (2)'!Y26*Hoja1!$K$21+'Todos los Datos (2)'!AD26*Hoja1!$K$22+'Todos los Datos (2)'!AI26*Hoja1!$K$23+'Todos los Datos (2)'!AN26*Hoja1!$K$24</f>
-        <v>64.913448735019969</v>
+        <v>125.06743357138109</v>
       </c>
       <c r="F26">
         <f>'Todos los Datos (2)'!F26*Hoja1!$K$17+'Todos los Datos (2)'!K26*Hoja1!$K$18+'Todos los Datos (2)'!P26*Hoja1!$K$19+'Todos los Datos (2)'!U26*Hoja1!$K$20+'Todos los Datos (2)'!Z26*Hoja1!$K$21+'Todos los Datos (2)'!AE26*Hoja1!$K$22+'Todos los Datos (2)'!AJ26*Hoja1!$K$23+'Todos los Datos (2)'!AO26*Hoja1!$K$24</f>
-        <v>120.25632490013315</v>
+        <v>144.30767270348812</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -16594,23 +16829,23 @@
       </c>
       <c r="B27">
         <f>'Todos los Datos (2)'!B27*Hoja1!$K$17+'Todos los Datos (2)'!G27*Hoja1!$K$18+'Todos los Datos (2)'!L27*Hoja1!$K$19+'Todos los Datos (2)'!Q27*Hoja1!$K$20+'Todos los Datos (2)'!V27*Hoja1!$K$21+'Todos los Datos (2)'!AA27*Hoja1!$K$22+'Todos los Datos (2)'!AF27*Hoja1!$K$23+'Todos los Datos (2)'!AK27*Hoja1!$K$24</f>
-        <v>91.445911588616426</v>
+        <v>111.17778687003972</v>
       </c>
       <c r="C27">
         <f>'Todos los Datos (2)'!C27*Hoja1!$K$17+'Todos los Datos (2)'!H27*Hoja1!$K$18+'Todos los Datos (2)'!M27*Hoja1!$K$19+'Todos los Datos (2)'!R27*Hoja1!$K$20+'Todos los Datos (2)'!W27*Hoja1!$K$21+'Todos los Datos (2)'!AB27*Hoja1!$K$22+'Todos los Datos (2)'!AG27*Hoja1!$K$23+'Todos los Datos (2)'!AL27*Hoja1!$K$24</f>
-        <v>84.064627245140656</v>
+        <v>102.77629756912111</v>
       </c>
       <c r="D27">
         <f>'Todos los Datos (2)'!D27*Hoja1!$K$17+'Todos los Datos (2)'!I27*Hoja1!$K$18+'Todos los Datos (2)'!N27*Hoja1!$K$19+'Todos los Datos (2)'!S27*Hoja1!$K$20+'Todos los Datos (2)'!X27*Hoja1!$K$21+'Todos los Datos (2)'!AC27*Hoja1!$K$22+'Todos los Datos (2)'!AH27*Hoja1!$K$23+'Todos los Datos (2)'!AM27*Hoja1!$K$24</f>
-        <v>96.776839170015577</v>
+        <v>97.524159333706933</v>
       </c>
       <c r="E27">
         <f>'Todos los Datos (2)'!E27*Hoja1!$K$17+'Todos los Datos (2)'!J27*Hoja1!$K$18+'Todos los Datos (2)'!O27*Hoja1!$K$19+'Todos los Datos (2)'!T27*Hoja1!$K$20+'Todos los Datos (2)'!Y27*Hoja1!$K$21+'Todos los Datos (2)'!AD27*Hoja1!$K$22+'Todos los Datos (2)'!AI27*Hoja1!$K$23+'Todos los Datos (2)'!AN27*Hoja1!$K$24</f>
-        <v>131.22283277290248</v>
+        <v>152.33491006751265</v>
       </c>
       <c r="F27">
         <f>'Todos los Datos (2)'!F27*Hoja1!$K$17+'Todos los Datos (2)'!K27*Hoja1!$K$18+'Todos los Datos (2)'!P27*Hoja1!$K$19+'Todos los Datos (2)'!U27*Hoja1!$K$20+'Todos los Datos (2)'!Z27*Hoja1!$K$21+'Todos los Datos (2)'!AE27*Hoja1!$K$22+'Todos los Datos (2)'!AJ27*Hoja1!$K$23+'Todos los Datos (2)'!AO27*Hoja1!$K$24</f>
-        <v>163.20839826129748</v>
+        <v>199.26009024175696</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -16619,23 +16854,23 @@
       </c>
       <c r="B28">
         <f>'Todos los Datos (2)'!B28*Hoja1!$K$17+'Todos los Datos (2)'!G28*Hoja1!$K$18+'Todos los Datos (2)'!L28*Hoja1!$K$19+'Todos los Datos (2)'!Q28*Hoja1!$K$20+'Todos los Datos (2)'!V28*Hoja1!$K$21+'Todos los Datos (2)'!AA28*Hoja1!$K$22+'Todos los Datos (2)'!AF28*Hoja1!$K$23+'Todos los Datos (2)'!AK28*Hoja1!$K$24</f>
-        <v>118.23938284198147</v>
+        <v>263.49087003520219</v>
       </c>
       <c r="C28">
         <f>'Todos los Datos (2)'!C28*Hoja1!$K$17+'Todos los Datos (2)'!H28*Hoja1!$K$18+'Todos los Datos (2)'!M28*Hoja1!$K$19+'Todos los Datos (2)'!R28*Hoja1!$K$20+'Todos los Datos (2)'!W28*Hoja1!$K$21+'Todos los Datos (2)'!AB28*Hoja1!$K$22+'Todos los Datos (2)'!AG28*Hoja1!$K$23+'Todos los Datos (2)'!AL28*Hoja1!$K$24</f>
-        <v>154.1501535648791</v>
+        <v>336.31230503252112</v>
       </c>
       <c r="D28">
         <f>'Todos los Datos (2)'!D28*Hoja1!$K$17+'Todos los Datos (2)'!I28*Hoja1!$K$18+'Todos los Datos (2)'!N28*Hoja1!$K$19+'Todos los Datos (2)'!S28*Hoja1!$K$20+'Todos los Datos (2)'!X28*Hoja1!$K$21+'Todos los Datos (2)'!AC28*Hoja1!$K$22+'Todos los Datos (2)'!AH28*Hoja1!$K$23+'Todos los Datos (2)'!AM28*Hoja1!$K$24</f>
-        <v>186.40992625541378</v>
+        <v>425.97890035843784</v>
       </c>
       <c r="E28">
         <f>'Todos los Datos (2)'!E28*Hoja1!$K$17+'Todos los Datos (2)'!J28*Hoja1!$K$18+'Todos los Datos (2)'!O28*Hoja1!$K$19+'Todos los Datos (2)'!T28*Hoja1!$K$20+'Todos los Datos (2)'!Y28*Hoja1!$K$21+'Todos los Datos (2)'!AD28*Hoja1!$K$22+'Todos los Datos (2)'!AI28*Hoja1!$K$23+'Todos los Datos (2)'!AN28*Hoja1!$K$24</f>
-        <v>191.0363817773393</v>
+        <v>457.16003817331864</v>
       </c>
       <c r="F28">
         <f>'Todos los Datos (2)'!F28*Hoja1!$K$17+'Todos los Datos (2)'!K28*Hoja1!$K$18+'Todos los Datos (2)'!P28*Hoja1!$K$19+'Todos los Datos (2)'!U28*Hoja1!$K$20+'Todos los Datos (2)'!Z28*Hoja1!$K$21+'Todos los Datos (2)'!AE28*Hoja1!$K$22+'Todos los Datos (2)'!AJ28*Hoja1!$K$23+'Todos los Datos (2)'!AO28*Hoja1!$K$24</f>
-        <v>214.94902537861685</v>
+        <v>492.43855722328988</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -16644,23 +16879,23 @@
       </c>
       <c r="B29">
         <f>'Todos los Datos (2)'!B29*Hoja1!$K$17+'Todos los Datos (2)'!G29*Hoja1!$K$18+'Todos los Datos (2)'!L29*Hoja1!$K$19+'Todos los Datos (2)'!Q29*Hoja1!$K$20+'Todos los Datos (2)'!V29*Hoja1!$K$21+'Todos los Datos (2)'!AA29*Hoja1!$K$22+'Todos los Datos (2)'!AF29*Hoja1!$K$23+'Todos los Datos (2)'!AK29*Hoja1!$K$24</f>
-        <v>98.728726676235397</v>
+        <v>161.10124692374274</v>
       </c>
       <c r="C29">
         <f>'Todos los Datos (2)'!C29*Hoja1!$K$17+'Todos los Datos (2)'!H29*Hoja1!$K$18+'Todos los Datos (2)'!M29*Hoja1!$K$19+'Todos los Datos (2)'!R29*Hoja1!$K$20+'Todos los Datos (2)'!W29*Hoja1!$K$21+'Todos los Datos (2)'!AB29*Hoja1!$K$22+'Todos los Datos (2)'!AG29*Hoja1!$K$23+'Todos los Datos (2)'!AL29*Hoja1!$K$24</f>
-        <v>136.35431617797826</v>
+        <v>222.29740098497859</v>
       </c>
       <c r="D29">
         <f>'Todos los Datos (2)'!D29*Hoja1!$K$17+'Todos los Datos (2)'!I29*Hoja1!$K$18+'Todos los Datos (2)'!N29*Hoja1!$K$19+'Todos los Datos (2)'!S29*Hoja1!$K$20+'Todos los Datos (2)'!X29*Hoja1!$K$21+'Todos los Datos (2)'!AC29*Hoja1!$K$22+'Todos los Datos (2)'!AH29*Hoja1!$K$23+'Todos los Datos (2)'!AM29*Hoja1!$K$24</f>
-        <v>125.07689153167929</v>
+        <v>235.42017621478388</v>
       </c>
       <c r="E29">
         <f>'Todos los Datos (2)'!E29*Hoja1!$K$17+'Todos los Datos (2)'!J29*Hoja1!$K$18+'Todos los Datos (2)'!O29*Hoja1!$K$19+'Todos los Datos (2)'!T29*Hoja1!$K$20+'Todos los Datos (2)'!Y29*Hoja1!$K$21+'Todos los Datos (2)'!AD29*Hoja1!$K$22+'Todos los Datos (2)'!AI29*Hoja1!$K$23+'Todos los Datos (2)'!AN29*Hoja1!$K$24</f>
-        <v>135.63666188230468</v>
+        <v>240.37863027513251</v>
       </c>
       <c r="F29">
         <f>'Todos los Datos (2)'!F29*Hoja1!$K$17+'Todos los Datos (2)'!K29*Hoja1!$K$18+'Todos los Datos (2)'!P29*Hoja1!$K$19+'Todos los Datos (2)'!U29*Hoja1!$K$20+'Todos los Datos (2)'!Z29*Hoja1!$K$21+'Todos los Datos (2)'!AE29*Hoja1!$K$22+'Todos los Datos (2)'!AJ29*Hoja1!$K$23+'Todos los Datos (2)'!AO29*Hoja1!$K$24</f>
-        <v>181.25897067869593</v>
+        <v>306.46178541835059</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -16669,23 +16904,23 @@
       </c>
       <c r="B30">
         <f>'Todos los Datos (2)'!B30*Hoja1!$K$17+'Todos los Datos (2)'!G30*Hoja1!$K$18+'Todos los Datos (2)'!L30*Hoja1!$K$19+'Todos los Datos (2)'!Q30*Hoja1!$K$20+'Todos los Datos (2)'!V30*Hoja1!$K$21+'Todos los Datos (2)'!AA30*Hoja1!$K$22+'Todos los Datos (2)'!AF30*Hoja1!$K$23+'Todos los Datos (2)'!AK30*Hoja1!$K$24</f>
-        <v>93.895198760970572</v>
+        <v>160.91710234394446</v>
       </c>
       <c r="C30">
         <f>'Todos los Datos (2)'!C30*Hoja1!$K$17+'Todos los Datos (2)'!H30*Hoja1!$K$18+'Todos los Datos (2)'!M30*Hoja1!$K$19+'Todos los Datos (2)'!R30*Hoja1!$K$20+'Todos los Datos (2)'!W30*Hoja1!$K$21+'Todos los Datos (2)'!AB30*Hoja1!$K$22+'Todos los Datos (2)'!AG30*Hoja1!$K$23+'Todos los Datos (2)'!AL30*Hoja1!$K$24</f>
-        <v>150.03871966959215</v>
+        <v>238.00770069904462</v>
       </c>
       <c r="D30">
         <f>'Todos los Datos (2)'!D30*Hoja1!$K$17+'Todos los Datos (2)'!I30*Hoja1!$K$18+'Todos los Datos (2)'!N30*Hoja1!$K$19+'Todos los Datos (2)'!S30*Hoja1!$K$20+'Todos los Datos (2)'!X30*Hoja1!$K$21+'Todos los Datos (2)'!AC30*Hoja1!$K$22+'Todos los Datos (2)'!AH30*Hoja1!$K$23+'Todos los Datos (2)'!AM30*Hoja1!$K$24</f>
-        <v>164.88125967991741</v>
+        <v>237.22299105368683</v>
       </c>
       <c r="E30">
         <f>'Todos los Datos (2)'!E30*Hoja1!$K$17+'Todos los Datos (2)'!J30*Hoja1!$K$18+'Todos los Datos (2)'!O30*Hoja1!$K$19+'Todos los Datos (2)'!T30*Hoja1!$K$20+'Todos los Datos (2)'!Y30*Hoja1!$K$21+'Todos los Datos (2)'!AD30*Hoja1!$K$22+'Todos los Datos (2)'!AI30*Hoja1!$K$23+'Todos los Datos (2)'!AN30*Hoja1!$K$24</f>
-        <v>172.30252968508</v>
+        <v>248.25861080600322</v>
       </c>
       <c r="F30">
         <f>'Todos los Datos (2)'!F30*Hoja1!$K$17+'Todos los Datos (2)'!K30*Hoja1!$K$18+'Todos los Datos (2)'!P30*Hoja1!$K$19+'Todos los Datos (2)'!U30*Hoja1!$K$20+'Todos los Datos (2)'!Z30*Hoja1!$K$21+'Todos los Datos (2)'!AE30*Hoja1!$K$22+'Todos los Datos (2)'!AJ30*Hoja1!$K$23+'Todos los Datos (2)'!AO30*Hoja1!$K$24</f>
-        <v>211.66752710376869</v>
+        <v>296.47277741444009</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -16694,23 +16929,23 @@
       </c>
       <c r="B31">
         <f>'Todos los Datos (2)'!B31*Hoja1!$K$17+'Todos los Datos (2)'!G31*Hoja1!$K$18+'Todos los Datos (2)'!L31*Hoja1!$K$19+'Todos los Datos (2)'!Q31*Hoja1!$K$20+'Todos los Datos (2)'!V31*Hoja1!$K$21+'Todos los Datos (2)'!AA31*Hoja1!$K$22+'Todos los Datos (2)'!AF31*Hoja1!$K$23+'Todos los Datos (2)'!AK31*Hoja1!$K$24</f>
-        <v>120.71278022609698</v>
+        <v>173.18228835298521</v>
       </c>
       <c r="C31">
         <f>'Todos los Datos (2)'!C31*Hoja1!$K$17+'Todos los Datos (2)'!H31*Hoja1!$K$18+'Todos los Datos (2)'!M31*Hoja1!$K$19+'Todos los Datos (2)'!R31*Hoja1!$K$20+'Todos los Datos (2)'!W31*Hoja1!$K$21+'Todos los Datos (2)'!AB31*Hoja1!$K$22+'Todos los Datos (2)'!AG31*Hoja1!$K$23+'Todos los Datos (2)'!AL31*Hoja1!$K$24</f>
-        <v>116.88062847288754</v>
+        <v>160.99143339662703</v>
       </c>
       <c r="D31">
         <f>'Todos los Datos (2)'!D31*Hoja1!$K$17+'Todos los Datos (2)'!I31*Hoja1!$K$18+'Todos los Datos (2)'!N31*Hoja1!$K$19+'Todos los Datos (2)'!S31*Hoja1!$K$20+'Todos los Datos (2)'!X31*Hoja1!$K$21+'Todos los Datos (2)'!AC31*Hoja1!$K$22+'Todos los Datos (2)'!AH31*Hoja1!$K$23+'Todos los Datos (2)'!AM31*Hoja1!$K$24</f>
-        <v>142.10896084818293</v>
+        <v>192.04502637579364</v>
       </c>
       <c r="E31">
         <f>'Todos los Datos (2)'!E31*Hoja1!$K$17+'Todos los Datos (2)'!J31*Hoja1!$K$18+'Todos los Datos (2)'!O31*Hoja1!$K$19+'Todos los Datos (2)'!T31*Hoja1!$K$20+'Todos los Datos (2)'!Y31*Hoja1!$K$21+'Todos los Datos (2)'!AD31*Hoja1!$K$22+'Todos los Datos (2)'!AI31*Hoja1!$K$23+'Todos los Datos (2)'!AN31*Hoja1!$K$24</f>
-        <v>145.62176662195824</v>
+        <v>205.46592021191117</v>
       </c>
       <c r="F31">
         <f>'Todos los Datos (2)'!F31*Hoja1!$K$17+'Todos los Datos (2)'!K31*Hoja1!$K$18+'Todos los Datos (2)'!P31*Hoja1!$K$19+'Todos los Datos (2)'!U31*Hoja1!$K$20+'Todos los Datos (2)'!Z31*Hoja1!$K$21+'Todos los Datos (2)'!AE31*Hoja1!$K$22+'Todos los Datos (2)'!AJ31*Hoja1!$K$23+'Todos los Datos (2)'!AO31*Hoja1!$K$24</f>
-        <v>121.99016414383344</v>
+        <v>170.22447160643534</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -16719,23 +16954,23 @@
       </c>
       <c r="B32">
         <f>'Todos los Datos (2)'!B32*Hoja1!$K$17+'Todos los Datos (2)'!G32*Hoja1!$K$18+'Todos los Datos (2)'!L32*Hoja1!$K$19+'Todos los Datos (2)'!Q32*Hoja1!$K$20+'Todos los Datos (2)'!V32*Hoja1!$K$21+'Todos los Datos (2)'!AA32*Hoja1!$K$22+'Todos los Datos (2)'!AF32*Hoja1!$K$23+'Todos los Datos (2)'!AK32*Hoja1!$K$24</f>
-        <v>100.5423109965636</v>
+        <v>129.22506676167978</v>
       </c>
       <c r="C32">
         <f>'Todos los Datos (2)'!C32*Hoja1!$K$17+'Todos los Datos (2)'!H32*Hoja1!$K$18+'Todos los Datos (2)'!M32*Hoja1!$K$19+'Todos los Datos (2)'!R32*Hoja1!$K$20+'Todos los Datos (2)'!W32*Hoja1!$K$21+'Todos los Datos (2)'!AB32*Hoja1!$K$22+'Todos los Datos (2)'!AG32*Hoja1!$K$23+'Todos los Datos (2)'!AL32*Hoja1!$K$24</f>
-        <v>108.32796391752578</v>
+        <v>155.9311490136831</v>
       </c>
       <c r="D32">
         <f>'Todos los Datos (2)'!D32*Hoja1!$K$17+'Todos los Datos (2)'!I32*Hoja1!$K$18+'Todos los Datos (2)'!N32*Hoja1!$K$19+'Todos los Datos (2)'!S32*Hoja1!$K$20+'Todos los Datos (2)'!X32*Hoja1!$K$21+'Todos los Datos (2)'!AC32*Hoja1!$K$22+'Todos los Datos (2)'!AH32*Hoja1!$K$23+'Todos los Datos (2)'!AM32*Hoja1!$K$24</f>
-        <v>117.18750000000001</v>
+        <v>195.74581299542058</v>
       </c>
       <c r="E32">
         <f>'Todos los Datos (2)'!E32*Hoja1!$K$17+'Todos los Datos (2)'!J32*Hoja1!$K$18+'Todos los Datos (2)'!O32*Hoja1!$K$19+'Todos los Datos (2)'!T32*Hoja1!$K$20+'Todos los Datos (2)'!Y32*Hoja1!$K$21+'Todos los Datos (2)'!AD32*Hoja1!$K$22+'Todos los Datos (2)'!AI32*Hoja1!$K$23+'Todos los Datos (2)'!AN32*Hoja1!$K$24</f>
-        <v>125.51009450171823</v>
+        <v>186.47388290722461</v>
       </c>
       <c r="F32">
         <f>'Todos los Datos (2)'!F32*Hoja1!$K$17+'Todos los Datos (2)'!K32*Hoja1!$K$18+'Todos los Datos (2)'!P32*Hoja1!$K$19+'Todos los Datos (2)'!U32*Hoja1!$K$20+'Todos los Datos (2)'!Z32*Hoja1!$K$21+'Todos los Datos (2)'!AE32*Hoja1!$K$22+'Todos los Datos (2)'!AJ32*Hoja1!$K$23+'Todos los Datos (2)'!AO32*Hoja1!$K$24</f>
-        <v>169.94201030927837</v>
+        <v>252.93018292741394</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -16744,23 +16979,23 @@
       </c>
       <c r="B33">
         <f>'Todos los Datos (2)'!B33*Hoja1!$K$17+'Todos los Datos (2)'!G33*Hoja1!$K$18+'Todos los Datos (2)'!L33*Hoja1!$K$19+'Todos los Datos (2)'!Q33*Hoja1!$K$20+'Todos los Datos (2)'!V33*Hoja1!$K$21+'Todos los Datos (2)'!AA33*Hoja1!$K$22+'Todos los Datos (2)'!AF33*Hoja1!$K$23+'Todos los Datos (2)'!AK33*Hoja1!$K$24</f>
-        <v>119.69001148105627</v>
+        <v>184.26676590540018</v>
       </c>
       <c r="C33">
         <f>'Todos los Datos (2)'!C33*Hoja1!$K$17+'Todos los Datos (2)'!H33*Hoja1!$K$18+'Todos los Datos (2)'!M33*Hoja1!$K$19+'Todos los Datos (2)'!R33*Hoja1!$K$20+'Todos los Datos (2)'!W33*Hoja1!$K$21+'Todos los Datos (2)'!AB33*Hoja1!$K$22+'Todos los Datos (2)'!AG33*Hoja1!$K$23+'Todos los Datos (2)'!AL33*Hoja1!$K$24</f>
-        <v>145.52238805970148</v>
+        <v>216.27046763823199</v>
       </c>
       <c r="D33">
         <f>'Todos los Datos (2)'!D33*Hoja1!$K$17+'Todos los Datos (2)'!I33*Hoja1!$K$18+'Todos los Datos (2)'!N33*Hoja1!$K$19+'Todos los Datos (2)'!S33*Hoja1!$K$20+'Todos los Datos (2)'!X33*Hoja1!$K$21+'Todos los Datos (2)'!AC33*Hoja1!$K$22+'Todos los Datos (2)'!AH33*Hoja1!$K$23+'Todos los Datos (2)'!AM33*Hoja1!$K$24</f>
-        <v>127.15269804822046</v>
+        <v>217.24346956374458</v>
       </c>
       <c r="E33">
         <f>'Todos los Datos (2)'!E33*Hoja1!$K$17+'Todos los Datos (2)'!J33*Hoja1!$K$18+'Todos los Datos (2)'!O33*Hoja1!$K$19+'Todos los Datos (2)'!T33*Hoja1!$K$20+'Todos los Datos (2)'!Y33*Hoja1!$K$21+'Todos los Datos (2)'!AD33*Hoja1!$K$22+'Todos los Datos (2)'!AI33*Hoja1!$K$23+'Todos los Datos (2)'!AN33*Hoja1!$K$24</f>
-        <v>194.89092996555684</v>
+        <v>328.07077245603688</v>
       </c>
       <c r="F33">
         <f>'Todos los Datos (2)'!F33*Hoja1!$K$17+'Todos los Datos (2)'!K33*Hoja1!$K$18+'Todos los Datos (2)'!P33*Hoja1!$K$19+'Todos los Datos (2)'!U33*Hoja1!$K$20+'Todos los Datos (2)'!Z33*Hoja1!$K$21+'Todos los Datos (2)'!AE33*Hoja1!$K$22+'Todos los Datos (2)'!AJ33*Hoja1!$K$23+'Todos los Datos (2)'!AO33*Hoja1!$K$24</f>
-        <v>146.09644087256027</v>
+        <v>239.11109421809564</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -16769,23 +17004,23 @@
       </c>
       <c r="B34">
         <f>'Todos los Datos (2)'!B34*Hoja1!$K$17+'Todos los Datos (2)'!G34*Hoja1!$K$18+'Todos los Datos (2)'!L34*Hoja1!$K$19+'Todos los Datos (2)'!Q34*Hoja1!$K$20+'Todos los Datos (2)'!V34*Hoja1!$K$21+'Todos los Datos (2)'!AA34*Hoja1!$K$22+'Todos los Datos (2)'!AF34*Hoja1!$K$23+'Todos los Datos (2)'!AK34*Hoja1!$K$24</f>
-        <v>115.43076553875689</v>
+        <v>163.70013126074969</v>
       </c>
       <c r="C34">
         <f>'Todos los Datos (2)'!C34*Hoja1!$K$17+'Todos los Datos (2)'!H34*Hoja1!$K$18+'Todos los Datos (2)'!M34*Hoja1!$K$19+'Todos los Datos (2)'!R34*Hoja1!$K$20+'Todos los Datos (2)'!W34*Hoja1!$K$21+'Todos los Datos (2)'!AB34*Hoja1!$K$22+'Todos los Datos (2)'!AG34*Hoja1!$K$23+'Todos los Datos (2)'!AL34*Hoja1!$K$24</f>
-        <v>102.95176385889127</v>
+        <v>174.97022090532462</v>
       </c>
       <c r="D34">
         <f>'Todos los Datos (2)'!D34*Hoja1!$K$17+'Todos los Datos (2)'!I34*Hoja1!$K$18+'Todos los Datos (2)'!N34*Hoja1!$K$19+'Todos los Datos (2)'!S34*Hoja1!$K$20+'Todos los Datos (2)'!X34*Hoja1!$K$21+'Todos los Datos (2)'!AC34*Hoja1!$K$22+'Todos los Datos (2)'!AH34*Hoja1!$K$23+'Todos los Datos (2)'!AM34*Hoja1!$K$24</f>
-        <v>135.82913366930646</v>
+        <v>237.99152614458228</v>
       </c>
       <c r="E34">
         <f>'Todos los Datos (2)'!E34*Hoja1!$K$17+'Todos los Datos (2)'!J34*Hoja1!$K$18+'Todos los Datos (2)'!O34*Hoja1!$K$19+'Todos los Datos (2)'!T34*Hoja1!$K$20+'Todos los Datos (2)'!Y34*Hoja1!$K$21+'Todos los Datos (2)'!AD34*Hoja1!$K$22+'Todos los Datos (2)'!AI34*Hoja1!$K$23+'Todos los Datos (2)'!AN34*Hoja1!$K$24</f>
-        <v>134.62922966162708</v>
+        <v>240.18131144721013</v>
       </c>
       <c r="F34">
         <f>'Todos los Datos (2)'!F34*Hoja1!$K$17+'Todos los Datos (2)'!K34*Hoja1!$K$18+'Todos los Datos (2)'!P34*Hoja1!$K$19+'Todos los Datos (2)'!U34*Hoja1!$K$20+'Todos los Datos (2)'!Z34*Hoja1!$K$21+'Todos los Datos (2)'!AE34*Hoja1!$K$22+'Todos los Datos (2)'!AJ34*Hoja1!$K$23+'Todos los Datos (2)'!AO34*Hoja1!$K$24</f>
-        <v>134.26925845932325</v>
+        <v>246.55714155441544</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -16794,23 +17029,23 @@
       </c>
       <c r="B35">
         <f>'Todos los Datos (2)'!B35*Hoja1!$K$17+'Todos los Datos (2)'!G35*Hoja1!$K$18+'Todos los Datos (2)'!L35*Hoja1!$K$19+'Todos los Datos (2)'!Q35*Hoja1!$K$20+'Todos los Datos (2)'!V35*Hoja1!$K$21+'Todos los Datos (2)'!AA35*Hoja1!$K$22+'Todos los Datos (2)'!AF35*Hoja1!$K$23+'Todos los Datos (2)'!AK35*Hoja1!$K$24</f>
-        <v>64.172958133150303</v>
+        <v>54.647894189555451</v>
       </c>
       <c r="C35">
         <f>'Todos los Datos (2)'!C35*Hoja1!$K$17+'Todos los Datos (2)'!H35*Hoja1!$K$18+'Todos los Datos (2)'!M35*Hoja1!$K$19+'Todos los Datos (2)'!R35*Hoja1!$K$20+'Todos los Datos (2)'!W35*Hoja1!$K$21+'Todos los Datos (2)'!AB35*Hoja1!$K$22+'Todos los Datos (2)'!AG35*Hoja1!$K$23+'Todos los Datos (2)'!AL35*Hoja1!$K$24</f>
-        <v>102.60809883321895</v>
+        <v>99.1574024092983</v>
       </c>
       <c r="D35">
         <f>'Todos los Datos (2)'!D35*Hoja1!$K$17+'Todos los Datos (2)'!I35*Hoja1!$K$18+'Todos los Datos (2)'!N35*Hoja1!$K$19+'Todos los Datos (2)'!S35*Hoja1!$K$20+'Todos los Datos (2)'!X35*Hoja1!$K$21+'Todos los Datos (2)'!AC35*Hoja1!$K$22+'Todos los Datos (2)'!AH35*Hoja1!$K$23+'Todos los Datos (2)'!AM35*Hoja1!$K$24</f>
-        <v>80.988332189430352</v>
+        <v>74.732107798348977</v>
       </c>
       <c r="E35">
         <f>'Todos los Datos (2)'!E35*Hoja1!$K$17+'Todos los Datos (2)'!J35*Hoja1!$K$18+'Todos los Datos (2)'!O35*Hoja1!$K$19+'Todos los Datos (2)'!T35*Hoja1!$K$20+'Todos los Datos (2)'!Y35*Hoja1!$K$21+'Todos los Datos (2)'!AD35*Hoja1!$K$22+'Todos los Datos (2)'!AI35*Hoja1!$K$23+'Todos los Datos (2)'!AN35*Hoja1!$K$24</f>
-        <v>88.194921070693212</v>
+        <v>89.829782943621552</v>
       </c>
       <c r="F35">
         <f>'Todos los Datos (2)'!F35*Hoja1!$K$17+'Todos los Datos (2)'!K35*Hoja1!$K$18+'Todos los Datos (2)'!P35*Hoja1!$K$19+'Todos los Datos (2)'!U35*Hoja1!$K$20+'Todos los Datos (2)'!Z35*Hoja1!$K$21+'Todos los Datos (2)'!AE35*Hoja1!$K$22+'Todos los Datos (2)'!AJ35*Hoja1!$K$23+'Todos los Datos (2)'!AO35*Hoja1!$K$24</f>
-        <v>81.674673987645832</v>
+        <v>57.54354463923012</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -16819,23 +17054,23 @@
       </c>
       <c r="B36">
         <f>'Todos los Datos (2)'!B36*Hoja1!$K$17+'Todos los Datos (2)'!G36*Hoja1!$K$18+'Todos los Datos (2)'!L36*Hoja1!$K$19+'Todos los Datos (2)'!Q36*Hoja1!$K$20+'Todos los Datos (2)'!V36*Hoja1!$K$21+'Todos los Datos (2)'!AA36*Hoja1!$K$22+'Todos los Datos (2)'!AF36*Hoja1!$K$23+'Todos los Datos (2)'!AK36*Hoja1!$K$24</f>
-        <v>91.831425598335059</v>
+        <v>117.34553762951518</v>
       </c>
       <c r="C36">
         <f>'Todos los Datos (2)'!C36*Hoja1!$K$17+'Todos los Datos (2)'!H36*Hoja1!$K$18+'Todos los Datos (2)'!M36*Hoja1!$K$19+'Todos los Datos (2)'!R36*Hoja1!$K$20+'Todos los Datos (2)'!W36*Hoja1!$K$21+'Todos los Datos (2)'!AB36*Hoja1!$K$22+'Todos los Datos (2)'!AG36*Hoja1!$K$23+'Todos los Datos (2)'!AL36*Hoja1!$K$24</f>
-        <v>88.969823100936537</v>
+        <v>95.000064913468165</v>
       </c>
       <c r="D36">
         <f>'Todos los Datos (2)'!D36*Hoja1!$K$17+'Todos los Datos (2)'!I36*Hoja1!$K$18+'Todos los Datos (2)'!N36*Hoja1!$K$19+'Todos los Datos (2)'!S36*Hoja1!$K$20+'Todos los Datos (2)'!X36*Hoja1!$K$21+'Todos los Datos (2)'!AC36*Hoja1!$K$22+'Todos los Datos (2)'!AH36*Hoja1!$K$23+'Todos los Datos (2)'!AM36*Hoja1!$K$24</f>
-        <v>105.6191467221644</v>
+        <v>130.82397086115856</v>
       </c>
       <c r="E36">
         <f>'Todos los Datos (2)'!E36*Hoja1!$K$17+'Todos los Datos (2)'!J36*Hoja1!$K$18+'Todos los Datos (2)'!O36*Hoja1!$K$19+'Todos los Datos (2)'!T36*Hoja1!$K$20+'Todos los Datos (2)'!Y36*Hoja1!$K$21+'Todos los Datos (2)'!AD36*Hoja1!$K$22+'Todos los Datos (2)'!AI36*Hoja1!$K$23+'Todos los Datos (2)'!AN36*Hoja1!$K$24</f>
-        <v>81.165452653485943</v>
+        <v>94.107432844908487</v>
       </c>
       <c r="F36">
         <f>'Todos los Datos (2)'!F36*Hoja1!$K$17+'Todos los Datos (2)'!K36*Hoja1!$K$18+'Todos los Datos (2)'!P36*Hoja1!$K$19+'Todos los Datos (2)'!U36*Hoja1!$K$20+'Todos los Datos (2)'!Z36*Hoja1!$K$21+'Todos los Datos (2)'!AE36*Hoja1!$K$22+'Todos los Datos (2)'!AJ36*Hoja1!$K$23+'Todos los Datos (2)'!AO36*Hoja1!$K$24</f>
-        <v>119.66701352757542</v>
+        <v>133.69742780220631</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -16844,23 +17079,23 @@
       </c>
       <c r="B37">
         <f>'Todos los Datos (2)'!B37*Hoja1!$K$17+'Todos los Datos (2)'!G37*Hoja1!$K$18+'Todos los Datos (2)'!L37*Hoja1!$K$19+'Todos los Datos (2)'!Q37*Hoja1!$K$20+'Todos los Datos (2)'!V37*Hoja1!$K$21+'Todos los Datos (2)'!AA37*Hoja1!$K$22+'Todos los Datos (2)'!AF37*Hoja1!$K$23+'Todos los Datos (2)'!AK37*Hoja1!$K$24</f>
-        <v>106.74446309633402</v>
+        <v>194.0816698056887</v>
       </c>
       <c r="C37">
         <f>'Todos los Datos (2)'!C37*Hoja1!$K$17+'Todos los Datos (2)'!H37*Hoja1!$K$18+'Todos los Datos (2)'!M37*Hoja1!$K$19+'Todos los Datos (2)'!R37*Hoja1!$K$20+'Todos los Datos (2)'!W37*Hoja1!$K$21+'Todos los Datos (2)'!AB37*Hoja1!$K$22+'Todos los Datos (2)'!AG37*Hoja1!$K$23+'Todos los Datos (2)'!AL37*Hoja1!$K$24</f>
-        <v>124.27573509503439</v>
+        <v>252.71156229471939</v>
       </c>
       <c r="D37">
         <f>'Todos los Datos (2)'!D37*Hoja1!$K$17+'Todos los Datos (2)'!I37*Hoja1!$K$18+'Todos los Datos (2)'!N37*Hoja1!$K$19+'Todos los Datos (2)'!S37*Hoja1!$K$20+'Todos los Datos (2)'!X37*Hoja1!$K$21+'Todos los Datos (2)'!AC37*Hoja1!$K$22+'Todos los Datos (2)'!AH37*Hoja1!$K$23+'Todos los Datos (2)'!AM37*Hoja1!$K$24</f>
-        <v>129.98411581018394</v>
+        <v>292.22211365918838</v>
       </c>
       <c r="E37">
         <f>'Todos los Datos (2)'!E37*Hoja1!$K$17+'Todos los Datos (2)'!J37*Hoja1!$K$18+'Todos los Datos (2)'!O37*Hoja1!$K$19+'Todos los Datos (2)'!T37*Hoja1!$K$20+'Todos los Datos (2)'!Y37*Hoja1!$K$21+'Todos los Datos (2)'!AD37*Hoja1!$K$22+'Todos los Datos (2)'!AI37*Hoja1!$K$23+'Todos los Datos (2)'!AN37*Hoja1!$K$24</f>
-        <v>161.25611451056838</v>
+        <v>315.70361537971871</v>
       </c>
       <c r="F37">
         <f>'Todos los Datos (2)'!F37*Hoja1!$K$17+'Todos los Datos (2)'!K37*Hoja1!$K$18+'Todos los Datos (2)'!P37*Hoja1!$K$19+'Todos los Datos (2)'!U37*Hoja1!$K$20+'Todos los Datos (2)'!Z37*Hoja1!$K$21+'Todos los Datos (2)'!AE37*Hoja1!$K$22+'Todos los Datos (2)'!AJ37*Hoja1!$K$23+'Todos los Datos (2)'!AO37*Hoja1!$K$24</f>
-        <v>167.21268569159403</v>
+        <v>290.40090339430333</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -16869,23 +17104,23 @@
       </c>
       <c r="B38">
         <f>'Todos los Datos (2)'!B38*Hoja1!$K$17+'Todos los Datos (2)'!G38*Hoja1!$K$18+'Todos los Datos (2)'!L38*Hoja1!$K$19+'Todos los Datos (2)'!Q38*Hoja1!$K$20+'Todos los Datos (2)'!V38*Hoja1!$K$21+'Todos los Datos (2)'!AA38*Hoja1!$K$22+'Todos los Datos (2)'!AF38*Hoja1!$K$23+'Todos los Datos (2)'!AK38*Hoja1!$K$24</f>
-        <v>77.078363002385771</v>
+        <v>103.64224576985632</v>
       </c>
       <c r="C38">
         <f>'Todos los Datos (2)'!C38*Hoja1!$K$17+'Todos los Datos (2)'!H38*Hoja1!$K$18+'Todos los Datos (2)'!M38*Hoja1!$K$19+'Todos los Datos (2)'!R38*Hoja1!$K$20+'Todos los Datos (2)'!W38*Hoja1!$K$21+'Todos los Datos (2)'!AB38*Hoja1!$K$22+'Todos los Datos (2)'!AG38*Hoja1!$K$23+'Todos los Datos (2)'!AL38*Hoja1!$K$24</f>
-        <v>101.85355111029547</v>
+        <v>127.95155955608895</v>
       </c>
       <c r="D38">
         <f>'Todos los Datos (2)'!D38*Hoja1!$K$17+'Todos los Datos (2)'!I38*Hoja1!$K$18+'Todos los Datos (2)'!N38*Hoja1!$K$19+'Todos los Datos (2)'!S38*Hoja1!$K$20+'Todos los Datos (2)'!X38*Hoja1!$K$21+'Todos los Datos (2)'!AC38*Hoja1!$K$22+'Todos los Datos (2)'!AH38*Hoja1!$K$23+'Todos los Datos (2)'!AM38*Hoja1!$K$24</f>
-        <v>86.254358597907881</v>
+        <v>128.31372113553974</v>
       </c>
       <c r="E38">
         <f>'Todos los Datos (2)'!E38*Hoja1!$K$17+'Todos los Datos (2)'!J38*Hoja1!$K$18+'Todos los Datos (2)'!O38*Hoja1!$K$19+'Todos los Datos (2)'!T38*Hoja1!$K$20+'Todos los Datos (2)'!Y38*Hoja1!$K$21+'Todos los Datos (2)'!AD38*Hoja1!$K$22+'Todos los Datos (2)'!AI38*Hoja1!$K$23+'Todos los Datos (2)'!AN38*Hoja1!$K$24</f>
-        <v>63.314369609102584</v>
+        <v>99.835723789980847</v>
       </c>
       <c r="F38">
         <f>'Todos los Datos (2)'!F38*Hoja1!$K$17+'Todos los Datos (2)'!K38*Hoja1!$K$18+'Todos los Datos (2)'!P38*Hoja1!$K$19+'Todos los Datos (2)'!U38*Hoja1!$K$20+'Todos los Datos (2)'!Z38*Hoja1!$K$21+'Todos los Datos (2)'!AE38*Hoja1!$K$22+'Todos los Datos (2)'!AJ38*Hoja1!$K$23+'Todos los Datos (2)'!AO38*Hoja1!$K$24</f>
-        <v>94.512754633877762</v>
+        <v>108.91319539876106</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -16894,23 +17129,23 @@
       </c>
       <c r="B39">
         <f>'Todos los Datos (2)'!B39*Hoja1!$K$17+'Todos los Datos (2)'!G39*Hoja1!$K$18+'Todos los Datos (2)'!L39*Hoja1!$K$19+'Todos los Datos (2)'!Q39*Hoja1!$K$20+'Todos los Datos (2)'!V39*Hoja1!$K$21+'Todos los Datos (2)'!AA39*Hoja1!$K$22+'Todos los Datos (2)'!AF39*Hoja1!$K$23+'Todos los Datos (2)'!AK39*Hoja1!$K$24</f>
-        <v>70.342475486713084</v>
+        <v>97.288158327412745</v>
       </c>
       <c r="C39">
         <f>'Todos los Datos (2)'!C39*Hoja1!$K$17+'Todos los Datos (2)'!H39*Hoja1!$K$18+'Todos los Datos (2)'!M39*Hoja1!$K$19+'Todos los Datos (2)'!R39*Hoja1!$K$20+'Todos los Datos (2)'!W39*Hoja1!$K$21+'Todos los Datos (2)'!AB39*Hoja1!$K$22+'Todos los Datos (2)'!AG39*Hoja1!$K$23+'Todos los Datos (2)'!AL39*Hoja1!$K$24</f>
-        <v>72.474065652977117</v>
+        <v>105.60458915135936</v>
       </c>
       <c r="D39">
         <f>'Todos los Datos (2)'!D39*Hoja1!$K$17+'Todos los Datos (2)'!I39*Hoja1!$K$18+'Todos los Datos (2)'!N39*Hoja1!$K$19+'Todos los Datos (2)'!S39*Hoja1!$K$20+'Todos los Datos (2)'!X39*Hoja1!$K$21+'Todos los Datos (2)'!AC39*Hoja1!$K$22+'Todos los Datos (2)'!AH39*Hoja1!$K$23+'Todos los Datos (2)'!AM39*Hoja1!$K$24</f>
-        <v>83.132016484297282</v>
+        <v>117.5394414060633</v>
       </c>
       <c r="E39">
         <f>'Todos los Datos (2)'!E39*Hoja1!$K$17+'Todos los Datos (2)'!J39*Hoja1!$K$18+'Todos los Datos (2)'!O39*Hoja1!$K$19+'Todos los Datos (2)'!T39*Hoja1!$K$20+'Todos los Datos (2)'!Y39*Hoja1!$K$21+'Todos los Datos (2)'!AD39*Hoja1!$K$22+'Todos los Datos (2)'!AI39*Hoja1!$K$23+'Todos los Datos (2)'!AN39*Hoja1!$K$24</f>
-        <v>103.02685803609492</v>
+        <v>152.92718030908765</v>
       </c>
       <c r="F39">
         <f>'Todos los Datos (2)'!F39*Hoja1!$K$17+'Todos los Datos (2)'!K39*Hoja1!$K$18+'Todos los Datos (2)'!P39*Hoja1!$K$19+'Todos los Datos (2)'!U39*Hoja1!$K$20+'Todos los Datos (2)'!Z39*Hoja1!$K$21+'Todos los Datos (2)'!AE39*Hoja1!$K$22+'Todos los Datos (2)'!AJ39*Hoja1!$K$23+'Todos los Datos (2)'!AO39*Hoja1!$K$24</f>
-        <v>112.2637487565724</v>
+        <v>130.83316339011273</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -16919,23 +17154,23 @@
       </c>
       <c r="B40">
         <f>'Todos los Datos (2)'!B40*Hoja1!$K$17+'Todos los Datos (2)'!G40*Hoja1!$K$18+'Todos los Datos (2)'!L40*Hoja1!$K$19+'Todos los Datos (2)'!Q40*Hoja1!$K$20+'Todos los Datos (2)'!V40*Hoja1!$K$21+'Todos los Datos (2)'!AA40*Hoja1!$K$22+'Todos los Datos (2)'!AF40*Hoja1!$K$23+'Todos los Datos (2)'!AK40*Hoja1!$K$24</f>
-        <v>77.035106546067766</v>
+        <v>133.92784059794457</v>
       </c>
       <c r="C40">
         <f>'Todos los Datos (2)'!C40*Hoja1!$K$17+'Todos los Datos (2)'!H40*Hoja1!$K$18+'Todos los Datos (2)'!M40*Hoja1!$K$19+'Todos los Datos (2)'!R40*Hoja1!$K$20+'Todos los Datos (2)'!W40*Hoja1!$K$21+'Todos los Datos (2)'!AB40*Hoja1!$K$22+'Todos los Datos (2)'!AG40*Hoja1!$K$23+'Todos los Datos (2)'!AL40*Hoja1!$K$24</f>
-        <v>128.77510347999387</v>
+        <v>199.80223708680217</v>
       </c>
       <c r="D40">
         <f>'Todos los Datos (2)'!D40*Hoja1!$K$17+'Todos los Datos (2)'!I40*Hoja1!$K$18+'Todos los Datos (2)'!N40*Hoja1!$K$19+'Todos los Datos (2)'!S40*Hoja1!$K$20+'Todos los Datos (2)'!X40*Hoja1!$K$21+'Todos los Datos (2)'!AC40*Hoja1!$K$22+'Todos los Datos (2)'!AH40*Hoja1!$K$23+'Todos los Datos (2)'!AM40*Hoja1!$K$24</f>
-        <v>105.01303081404262</v>
+        <v>188.35492445296035</v>
       </c>
       <c r="E40">
         <f>'Todos los Datos (2)'!E40*Hoja1!$K$17+'Todos los Datos (2)'!J40*Hoja1!$K$18+'Todos los Datos (2)'!O40*Hoja1!$K$19+'Todos los Datos (2)'!T40*Hoja1!$K$20+'Todos los Datos (2)'!Y40*Hoja1!$K$21+'Todos los Datos (2)'!AD40*Hoja1!$K$22+'Todos los Datos (2)'!AI40*Hoja1!$K$23+'Todos los Datos (2)'!AN40*Hoja1!$K$24</f>
-        <v>77.035106546067766</v>
+        <v>132.88182259653601</v>
       </c>
       <c r="F40">
         <f>'Todos los Datos (2)'!F40*Hoja1!$K$17+'Todos los Datos (2)'!K40*Hoja1!$K$18+'Todos los Datos (2)'!P40*Hoja1!$K$19+'Todos los Datos (2)'!U40*Hoja1!$K$20+'Todos los Datos (2)'!Z40*Hoja1!$K$21+'Todos los Datos (2)'!AE40*Hoja1!$K$22+'Todos los Datos (2)'!AJ40*Hoja1!$K$23+'Todos los Datos (2)'!AO40*Hoja1!$K$24</f>
-        <v>128.77510347999387</v>
+        <v>225.77606735261327</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -16944,23 +17179,23 @@
       </c>
       <c r="B41">
         <f>'Todos los Datos (2)'!B41*Hoja1!$K$17+'Todos los Datos (2)'!G41*Hoja1!$K$18+'Todos los Datos (2)'!L41*Hoja1!$K$19+'Todos los Datos (2)'!Q41*Hoja1!$K$20+'Todos los Datos (2)'!V41*Hoja1!$K$21+'Todos los Datos (2)'!AA41*Hoja1!$K$22+'Todos los Datos (2)'!AF41*Hoja1!$K$23+'Todos los Datos (2)'!AK41*Hoja1!$K$24</f>
-        <v>105.79268292682927</v>
+        <v>174.51857164501985</v>
       </c>
       <c r="C41">
         <f>'Todos los Datos (2)'!C41*Hoja1!$K$17+'Todos los Datos (2)'!H41*Hoja1!$K$18+'Todos los Datos (2)'!M41*Hoja1!$K$19+'Todos los Datos (2)'!R41*Hoja1!$K$20+'Todos los Datos (2)'!W41*Hoja1!$K$21+'Todos los Datos (2)'!AB41*Hoja1!$K$22+'Todos los Datos (2)'!AG41*Hoja1!$K$23+'Todos los Datos (2)'!AL41*Hoja1!$K$24</f>
-        <v>123.78048780487804</v>
+        <v>204.31397897566927</v>
       </c>
       <c r="D41">
         <f>'Todos los Datos (2)'!D41*Hoja1!$K$17+'Todos los Datos (2)'!I41*Hoja1!$K$18+'Todos los Datos (2)'!N41*Hoja1!$K$19+'Todos los Datos (2)'!S41*Hoja1!$K$20+'Todos los Datos (2)'!X41*Hoja1!$K$21+'Todos los Datos (2)'!AC41*Hoja1!$K$22+'Todos los Datos (2)'!AH41*Hoja1!$K$23+'Todos los Datos (2)'!AM41*Hoja1!$K$24</f>
-        <v>155.48780487804879</v>
+        <v>303.08178124401667</v>
       </c>
       <c r="E41">
         <f>'Todos los Datos (2)'!E41*Hoja1!$K$17+'Todos los Datos (2)'!J41*Hoja1!$K$18+'Todos los Datos (2)'!O41*Hoja1!$K$19+'Todos los Datos (2)'!T41*Hoja1!$K$20+'Todos los Datos (2)'!Y41*Hoja1!$K$21+'Todos los Datos (2)'!AD41*Hoja1!$K$22+'Todos los Datos (2)'!AI41*Hoja1!$K$23+'Todos los Datos (2)'!AN41*Hoja1!$K$24</f>
-        <v>146.64634146341461</v>
+        <v>268.4346697232844</v>
       </c>
       <c r="F41">
         <f>'Todos los Datos (2)'!F41*Hoja1!$K$17+'Todos los Datos (2)'!K41*Hoja1!$K$18+'Todos los Datos (2)'!P41*Hoja1!$K$19+'Todos los Datos (2)'!U41*Hoja1!$K$20+'Todos los Datos (2)'!Z41*Hoja1!$K$21+'Todos los Datos (2)'!AE41*Hoja1!$K$22+'Todos los Datos (2)'!AJ41*Hoja1!$K$23+'Todos los Datos (2)'!AO41*Hoja1!$K$24</f>
-        <v>188.71951219512192</v>
+        <v>282.13688695381438</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -16969,23 +17204,23 @@
       </c>
       <c r="B42">
         <f>'Todos los Datos (2)'!B42*Hoja1!$K$17+'Todos los Datos (2)'!G42*Hoja1!$K$18+'Todos los Datos (2)'!L42*Hoja1!$K$19+'Todos los Datos (2)'!Q42*Hoja1!$K$20+'Todos los Datos (2)'!V42*Hoja1!$K$21+'Todos los Datos (2)'!AA42*Hoja1!$K$22+'Todos los Datos (2)'!AF42*Hoja1!$K$23+'Todos los Datos (2)'!AK42*Hoja1!$K$24</f>
-        <v>181.83612322155838</v>
+        <v>379.21232942146986</v>
       </c>
       <c r="C42">
         <f>'Todos los Datos (2)'!C42*Hoja1!$K$17+'Todos los Datos (2)'!H42*Hoja1!$K$18+'Todos los Datos (2)'!M42*Hoja1!$K$19+'Todos los Datos (2)'!R42*Hoja1!$K$20+'Todos los Datos (2)'!W42*Hoja1!$K$21+'Todos los Datos (2)'!AB42*Hoja1!$K$22+'Todos los Datos (2)'!AG42*Hoja1!$K$23+'Todos los Datos (2)'!AL42*Hoja1!$K$24</f>
-        <v>256.47236126809838</v>
+        <v>506.11794721101853</v>
       </c>
       <c r="D42">
         <f>'Todos los Datos (2)'!D42*Hoja1!$K$17+'Todos los Datos (2)'!I42*Hoja1!$K$18+'Todos los Datos (2)'!N42*Hoja1!$K$19+'Todos los Datos (2)'!S42*Hoja1!$K$20+'Todos los Datos (2)'!X42*Hoja1!$K$21+'Todos los Datos (2)'!AC42*Hoja1!$K$22+'Todos los Datos (2)'!AH42*Hoja1!$K$23+'Todos los Datos (2)'!AM42*Hoja1!$K$24</f>
-        <v>235.12209124997756</v>
+        <v>543.11668810882713</v>
       </c>
       <c r="E42">
         <f>'Todos los Datos (2)'!E42*Hoja1!$K$17+'Todos los Datos (2)'!J42*Hoja1!$K$18+'Todos los Datos (2)'!O42*Hoja1!$K$19+'Todos los Datos (2)'!T42*Hoja1!$K$20+'Todos los Datos (2)'!Y42*Hoja1!$K$21+'Todos los Datos (2)'!AD42*Hoja1!$K$22+'Todos los Datos (2)'!AI42*Hoja1!$K$23+'Todos los Datos (2)'!AN42*Hoja1!$K$24</f>
-        <v>221.62118520910707</v>
+        <v>494.29807356057415</v>
       </c>
       <c r="F42">
         <f>'Todos los Datos (2)'!F42*Hoja1!$K$17+'Todos los Datos (2)'!K42*Hoja1!$K$18+'Todos los Datos (2)'!P42*Hoja1!$K$19+'Todos los Datos (2)'!U42*Hoja1!$K$20+'Todos los Datos (2)'!Z42*Hoja1!$K$21+'Todos los Datos (2)'!AE42*Hoja1!$K$22+'Todos los Datos (2)'!AJ42*Hoja1!$K$23+'Todos los Datos (2)'!AO42*Hoja1!$K$24</f>
-        <v>283.96756194269517</v>
+        <v>577.75132754166998</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -16994,26 +17229,1076 @@
       </c>
       <c r="B43">
         <f>'Todos los Datos (2)'!B43*Hoja1!$K$17+'Todos los Datos (2)'!G43*Hoja1!$K$18+'Todos los Datos (2)'!L43*Hoja1!$K$19+'Todos los Datos (2)'!Q43*Hoja1!$K$20+'Todos los Datos (2)'!V43*Hoja1!$K$21+'Todos los Datos (2)'!AA43*Hoja1!$K$22+'Todos los Datos (2)'!AF43*Hoja1!$K$23+'Todos los Datos (2)'!AK43*Hoja1!$K$24</f>
-        <v>117.60596180717278</v>
+        <v>162.6465936178914</v>
       </c>
       <c r="C43">
         <f>'Todos los Datos (2)'!C43*Hoja1!$K$17+'Todos los Datos (2)'!H43*Hoja1!$K$18+'Todos los Datos (2)'!M43*Hoja1!$K$19+'Todos los Datos (2)'!R43*Hoja1!$K$20+'Todos los Datos (2)'!W43*Hoja1!$K$21+'Todos los Datos (2)'!AB43*Hoja1!$K$22+'Todos los Datos (2)'!AG43*Hoja1!$K$23+'Todos los Datos (2)'!AL43*Hoja1!$K$24</f>
-        <v>158.70982766651142</v>
+        <v>236.15169761161394</v>
       </c>
       <c r="D43">
         <f>'Todos los Datos (2)'!D43*Hoja1!$K$17+'Todos los Datos (2)'!I43*Hoja1!$K$18+'Todos los Datos (2)'!N43*Hoja1!$K$19+'Todos los Datos (2)'!S43*Hoja1!$K$20+'Todos los Datos (2)'!X43*Hoja1!$K$21+'Todos los Datos (2)'!AC43*Hoja1!$K$22+'Todos los Datos (2)'!AH43*Hoja1!$K$23+'Todos los Datos (2)'!AM43*Hoja1!$K$24</f>
-        <v>141.01071262226361</v>
+        <v>233.24642324154709</v>
       </c>
       <c r="E43">
         <f>'Todos los Datos (2)'!E43*Hoja1!$K$17+'Todos los Datos (2)'!J43*Hoja1!$K$18+'Todos los Datos (2)'!O43*Hoja1!$K$19+'Todos los Datos (2)'!T43*Hoja1!$K$20+'Todos los Datos (2)'!Y43*Hoja1!$K$21+'Todos los Datos (2)'!AD43*Hoja1!$K$22+'Todos los Datos (2)'!AI43*Hoja1!$K$23+'Todos los Datos (2)'!AN43*Hoja1!$K$24</f>
-        <v>120.16767582673498</v>
+        <v>201.8797324160945</v>
       </c>
       <c r="F43">
         <f>'Todos los Datos (2)'!F43*Hoja1!$K$17+'Todos los Datos (2)'!K43*Hoja1!$K$18+'Todos los Datos (2)'!P43*Hoja1!$K$19+'Todos los Datos (2)'!U43*Hoja1!$K$20+'Todos los Datos (2)'!Z43*Hoja1!$K$21+'Todos los Datos (2)'!AE43*Hoja1!$K$22+'Todos los Datos (2)'!AJ43*Hoja1!$K$23+'Todos los Datos (2)'!AO43*Hoja1!$K$24</f>
-        <v>147.76432231020027</v>
+        <v>214.50257306588048</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7DBDFF-1DF8-4C6F-B718-8D978C4D0786}">
+  <dimension ref="A1:R46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="24"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
+      <c r="B2" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="14">
+        <v>3.1752000000000002E-2</v>
+      </c>
+      <c r="C3" s="14">
+        <v>6.7621000000000001E-2</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0.32684299999999999</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0.150728</v>
+      </c>
+      <c r="F3" s="14">
+        <v>-2.8882999999999999E-2</v>
+      </c>
+      <c r="G3" s="14">
+        <v>-4.1564999999999998E-2</v>
+      </c>
+      <c r="H3" s="25">
+        <v>0.33965499999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="14">
+        <v>2.6481000000000001E-2</v>
+      </c>
+      <c r="C4" s="14">
+        <v>3.8716E-2</v>
+      </c>
+      <c r="D4" s="14">
+        <v>0.40227499999999999</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0.24354500000000001</v>
+      </c>
+      <c r="F4" s="14">
+        <v>-0.136463</v>
+      </c>
+      <c r="G4" s="14">
+        <v>-5.8527999999999997E-2</v>
+      </c>
+      <c r="H4" s="25">
+        <v>0.35244500000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="14">
+        <v>2.1559999999999999E-2</v>
+      </c>
+      <c r="C5" s="14">
+        <v>0.13717099999999999</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0.38317000000000001</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0.199936</v>
+      </c>
+      <c r="F5" s="14">
+        <v>-0.15739400000000001</v>
+      </c>
+      <c r="G5" s="14">
+        <v>-3.2506E-2</v>
+      </c>
+      <c r="H5" s="25">
+        <v>0.33768900000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1.7650000000000001E-3</v>
+      </c>
+      <c r="C6" s="14">
+        <v>0.102481</v>
+      </c>
+      <c r="D6" s="14">
+        <v>0.349885</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0.183861</v>
+      </c>
+      <c r="F6" s="14">
+        <v>-0.25766299999999998</v>
+      </c>
+      <c r="G6" s="14">
+        <v>-8.8278999999999996E-2</v>
+      </c>
+      <c r="H6" s="25">
+        <v>0.29774499999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="14">
+        <v>-3.8499999999999998E-4</v>
+      </c>
+      <c r="C7" s="14">
+        <v>2.317E-2</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0.31322499999999998</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0.13423299999999999</v>
+      </c>
+      <c r="F7" s="14">
+        <v>-6.5419000000000005E-2</v>
+      </c>
+      <c r="G7" s="14">
+        <v>-6.6115999999999994E-2</v>
+      </c>
+      <c r="H7" s="25">
+        <v>0.34297499999999997</v>
+      </c>
+      <c r="M7" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="M8" s="12" cm="1">
+        <f t="array" ref="M8">SUM(ABS(B9:H9))</f>
+        <v>1.1482716000000002</v>
+      </c>
+      <c r="N8" s="12" cm="1">
+        <f t="array" ref="N8">SUM(ABS(B10:H10))</f>
+        <v>1.2282109999999999</v>
+      </c>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="14">
+        <f>AVERAGE(B3:B7)</f>
+        <v>1.6234600000000002E-2</v>
+      </c>
+      <c r="C9" s="14">
+        <f>AVERAGE(C3:C7)</f>
+        <v>7.3831800000000003E-2</v>
+      </c>
+      <c r="D9" s="14">
+        <f>AVERAGE(D3:D7)</f>
+        <v>0.3550796</v>
+      </c>
+      <c r="E9" s="14">
+        <f>AVERAGE(E3:E7)</f>
+        <v>0.18246060000000003</v>
+      </c>
+      <c r="F9" s="14">
+        <f>AVERAGE(F3:F7)</f>
+        <v>-0.12916440000000001</v>
+      </c>
+      <c r="G9" s="14">
+        <f>AVERAGE(G3:G7)</f>
+        <v>-5.7398799999999993E-2</v>
+      </c>
+      <c r="H9" s="25">
+        <f>AVERAGE(H3:H7)</f>
+        <v>0.3341018</v>
+      </c>
+      <c r="L9" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="13" cm="1">
+        <f t="array" ref="M9:M15">TRANSPOSE(ABS(B9:H9)/M8)</f>
+        <v>1.4138292717506903E-2</v>
+      </c>
+      <c r="N9" s="13" cm="1">
+        <f t="array" ref="N9:N15">TRANSPOSE(ABS(B10:H10)/N8)</f>
+        <v>1.4321643430973996E-2</v>
+      </c>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="14">
+        <v>1.7590000000000001E-2</v>
+      </c>
+      <c r="C10" s="14">
+        <v>8.5203000000000001E-2</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0.374222</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0.19534599999999999</v>
+      </c>
+      <c r="F10" s="14">
+        <v>-0.15032000000000001</v>
+      </c>
+      <c r="G10" s="14">
+        <v>-6.0714999999999998E-2</v>
+      </c>
+      <c r="H10" s="25">
+        <v>0.34481499999999998</v>
+      </c>
+      <c r="L10" t="s">
+        <v>115</v>
+      </c>
+      <c r="M10" s="13">
+        <v>6.4298202620355668E-2</v>
+      </c>
+      <c r="N10" s="13">
+        <v>6.9371630770282966E-2</v>
+      </c>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="L11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M11" s="13">
+        <v>0.30922962825171324</v>
+      </c>
+      <c r="N11" s="13">
+        <v>0.30468868948413591</v>
+      </c>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+    </row>
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="26">
+        <v>-5.5710999999999997E-2</v>
+      </c>
+      <c r="C12" s="26">
+        <v>5.9236999999999998E-2</v>
+      </c>
+      <c r="D12" s="26">
+        <v>0.43781100000000001</v>
+      </c>
+      <c r="E12" s="26">
+        <v>0.20558199999999999</v>
+      </c>
+      <c r="F12" s="26">
+        <v>-3.8119E-2</v>
+      </c>
+      <c r="G12" s="26">
+        <v>0.11970600000000001</v>
+      </c>
+      <c r="H12" s="27">
+        <v>0.41468699999999997</v>
+      </c>
+      <c r="L12" t="s">
+        <v>113</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0.15890021141339733</v>
+      </c>
+      <c r="N12" s="13">
+        <v>0.15904921874173086</v>
+      </c>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13">
+        <v>-8.2948999999999995E-2</v>
+      </c>
+      <c r="C13">
+        <v>-3.0569999999999998E-3</v>
+      </c>
+      <c r="D13">
+        <v>0.41237699999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.174924</v>
+      </c>
+      <c r="F13">
+        <v>-0.15470999999999999</v>
+      </c>
+      <c r="G13">
+        <v>2.6252000000000001E-2</v>
+      </c>
+      <c r="H13">
+        <v>0.37839200000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0.11248593102886111</v>
+      </c>
+      <c r="N13" s="13">
+        <v>0.12238939400477607</v>
+      </c>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+    </row>
+    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" s="13">
+        <v>4.9987128480753144E-2</v>
+      </c>
+      <c r="N14" s="13">
+        <v>4.9433688511176015E-2</v>
+      </c>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" s="13">
+        <v>0.29096060548741254</v>
+      </c>
+      <c r="N15" s="13">
+        <v>0.28074573505692424</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="14">
+        <f>B3^2</f>
+        <v>1.0081895040000002E-3</v>
+      </c>
+      <c r="C16" s="14">
+        <f t="shared" ref="C16:H16" si="0">C3^2</f>
+        <v>4.5725996409999997E-3</v>
+      </c>
+      <c r="D16" s="14">
+        <f t="shared" si="0"/>
+        <v>0.106826346649</v>
+      </c>
+      <c r="E16" s="14">
+        <f t="shared" si="0"/>
+        <v>2.2718929984000002E-2</v>
+      </c>
+      <c r="F16" s="14">
+        <f t="shared" si="0"/>
+        <v>8.3422768899999995E-4</v>
+      </c>
+      <c r="G16" s="14">
+        <f t="shared" si="0"/>
+        <v>1.7276492249999999E-3</v>
+      </c>
+      <c r="H16" s="25">
+        <f t="shared" si="0"/>
+        <v>0.11536551902499999</v>
+      </c>
+      <c r="M16">
+        <f>SUM(_xlfn.ANCHORARRAY(M9))</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="N16">
+        <f>SUM(_xlfn.ANCHORARRAY(N9))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="14">
+        <f t="shared" ref="B17:H17" si="1">B4^2</f>
+        <v>7.0124336100000002E-4</v>
+      </c>
+      <c r="C17" s="14">
+        <f t="shared" si="1"/>
+        <v>1.498928656E-3</v>
+      </c>
+      <c r="D17" s="14">
+        <f t="shared" si="1"/>
+        <v>0.16182517562499998</v>
+      </c>
+      <c r="E17" s="14">
+        <f t="shared" si="1"/>
+        <v>5.9314167025000003E-2</v>
+      </c>
+      <c r="F17" s="14">
+        <f t="shared" si="1"/>
+        <v>1.8622150369000001E-2</v>
+      </c>
+      <c r="G17" s="14">
+        <f t="shared" si="1"/>
+        <v>3.4255267839999998E-3</v>
+      </c>
+      <c r="H17" s="25">
+        <f t="shared" si="1"/>
+        <v>0.12421747802500001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="14">
+        <f t="shared" ref="B18:H18" si="2">B5^2</f>
+        <v>4.6483359999999999E-4</v>
+      </c>
+      <c r="C18" s="14">
+        <f t="shared" si="2"/>
+        <v>1.8815883240999996E-2</v>
+      </c>
+      <c r="D18" s="14">
+        <f t="shared" si="2"/>
+        <v>0.1468192489</v>
+      </c>
+      <c r="E18" s="14">
+        <f t="shared" si="2"/>
+        <v>3.9974404095999998E-2</v>
+      </c>
+      <c r="F18" s="14">
+        <f t="shared" si="2"/>
+        <v>2.4772871236000003E-2</v>
+      </c>
+      <c r="G18" s="14">
+        <f t="shared" si="2"/>
+        <v>1.056640036E-3</v>
+      </c>
+      <c r="H18" s="25">
+        <f t="shared" si="2"/>
+        <v>0.11403386072100001</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="M18" s="20"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="14">
+        <f t="shared" ref="B19:H19" si="3">B6^2</f>
+        <v>3.1152250000000003E-6</v>
+      </c>
+      <c r="C19" s="14">
+        <f t="shared" si="3"/>
+        <v>1.0502355361E-2</v>
+      </c>
+      <c r="D19" s="14">
+        <f t="shared" si="3"/>
+        <v>0.122419513225</v>
+      </c>
+      <c r="E19" s="14">
+        <f t="shared" si="3"/>
+        <v>3.3804867321E-2</v>
+      </c>
+      <c r="F19" s="14">
+        <f t="shared" si="3"/>
+        <v>6.6390221568999985E-2</v>
+      </c>
+      <c r="G19" s="14">
+        <f t="shared" si="3"/>
+        <v>7.7931818409999994E-3</v>
+      </c>
+      <c r="H19" s="25">
+        <f t="shared" si="3"/>
+        <v>8.8652085024999994E-2</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="M19" s="16">
+        <v>1.4138292717506903E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="14">
+        <f t="shared" ref="B20:H20" si="4">B7^2</f>
+        <v>1.4822499999999999E-7</v>
+      </c>
+      <c r="C20" s="14">
+        <f t="shared" si="4"/>
+        <v>5.3684890000000002E-4</v>
+      </c>
+      <c r="D20" s="14">
+        <f t="shared" si="4"/>
+        <v>9.8109900624999982E-2</v>
+      </c>
+      <c r="E20" s="14">
+        <f t="shared" si="4"/>
+        <v>1.8018498288999998E-2</v>
+      </c>
+      <c r="F20" s="14">
+        <f t="shared" si="4"/>
+        <v>4.2796455610000003E-3</v>
+      </c>
+      <c r="G20" s="14">
+        <f t="shared" si="4"/>
+        <v>4.3713254559999996E-3</v>
+      </c>
+      <c r="H20" s="25">
+        <f t="shared" si="4"/>
+        <v>0.11763185062499998</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="M20" s="16">
+        <v>6.4298202620355668E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="15"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="25"/>
+      <c r="L21" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="M21" s="16">
+        <v>0.30922962825171324</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="14">
+        <f t="shared" ref="B22:H22" si="5">B9^2</f>
+        <v>2.6356223716000003E-4</v>
+      </c>
+      <c r="C22" s="14">
+        <f t="shared" si="5"/>
+        <v>5.4511346912400008E-3</v>
+      </c>
+      <c r="D22" s="14">
+        <f t="shared" si="5"/>
+        <v>0.12608152233615999</v>
+      </c>
+      <c r="E22" s="14">
+        <f t="shared" si="5"/>
+        <v>3.3291870552360013E-2</v>
+      </c>
+      <c r="F22" s="14">
+        <f t="shared" si="5"/>
+        <v>1.6683442227360002E-2</v>
+      </c>
+      <c r="G22" s="14">
+        <f t="shared" si="5"/>
+        <v>3.2946222414399992E-3</v>
+      </c>
+      <c r="H22" s="25">
+        <f t="shared" si="5"/>
+        <v>0.11162401276324001</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="M22" s="16">
+        <v>0.15890021141339733</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="14">
+        <f t="shared" ref="B23:H23" si="6">B10^2</f>
+        <v>3.0940810000000004E-4</v>
+      </c>
+      <c r="C23" s="14">
+        <f t="shared" si="6"/>
+        <v>7.259551209E-3</v>
+      </c>
+      <c r="D23" s="14">
+        <f t="shared" si="6"/>
+        <v>0.14004210528399999</v>
+      </c>
+      <c r="E23" s="14">
+        <f t="shared" si="6"/>
+        <v>3.8160059715999999E-2</v>
+      </c>
+      <c r="F23" s="14">
+        <f t="shared" si="6"/>
+        <v>2.2596102400000002E-2</v>
+      </c>
+      <c r="G23" s="14">
+        <f t="shared" si="6"/>
+        <v>3.6863112249999998E-3</v>
+      </c>
+      <c r="H23" s="25">
+        <f t="shared" si="6"/>
+        <v>0.11889738422499999</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="M23" s="16">
+        <v>0.11248593102886111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="25"/>
+      <c r="L24" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="M24" s="16">
+        <v>4.9987128480753144E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="14">
+        <f t="shared" ref="B25:H25" si="7">B12^2</f>
+        <v>3.1037155209999996E-3</v>
+      </c>
+      <c r="C25" s="14">
+        <f t="shared" si="7"/>
+        <v>3.5090221689999999E-3</v>
+      </c>
+      <c r="D25" s="14">
+        <f t="shared" si="7"/>
+        <v>0.191678471721</v>
+      </c>
+      <c r="E25" s="14">
+        <f t="shared" si="7"/>
+        <v>4.2263958723999996E-2</v>
+      </c>
+      <c r="F25" s="14">
+        <f t="shared" si="7"/>
+        <v>1.4530581609999999E-3</v>
+      </c>
+      <c r="G25" s="14">
+        <f t="shared" si="7"/>
+        <v>1.4329526436000002E-2</v>
+      </c>
+      <c r="H25" s="25">
+        <f t="shared" si="7"/>
+        <v>0.17196530796899998</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="M25" s="18">
+        <v>0.29096060548741254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="26">
+        <f t="shared" ref="B26:H26" si="8">B13^2</f>
+        <v>6.8805366009999994E-3</v>
+      </c>
+      <c r="C26" s="26">
+        <f t="shared" si="8"/>
+        <v>9.3452489999999989E-6</v>
+      </c>
+      <c r="D26" s="26">
+        <f t="shared" si="8"/>
+        <v>0.17005479012899999</v>
+      </c>
+      <c r="E26" s="26">
+        <f t="shared" si="8"/>
+        <v>3.0598405775999999E-2</v>
+      </c>
+      <c r="F26" s="26">
+        <f t="shared" si="8"/>
+        <v>2.3935184099999996E-2</v>
+      </c>
+      <c r="G26" s="26">
+        <f t="shared" si="8"/>
+        <v>6.8916750400000002E-4</v>
+      </c>
+      <c r="H26" s="27">
+        <f t="shared" si="8"/>
+        <v>0.14318050566400001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L27" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M28" t="s">
+        <v>111</v>
+      </c>
+      <c r="N28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M29" s="12" cm="1">
+        <f t="array" ref="M29">SUM(ABS(B22:H22))</f>
+        <v>0.29669016704896001</v>
+      </c>
+      <c r="N29" s="12" cm="1">
+        <f t="array" ref="N29">SUM(ABS(B23:H23))</f>
+        <v>0.33095092215900002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L30" t="s">
+        <v>97</v>
+      </c>
+      <c r="M30" s="13" cm="1">
+        <f t="array" ref="M30:M36">TRANSPOSE(ABS(B22:H22)/M29)</f>
+        <v>8.8834166558848858E-4</v>
+      </c>
+      <c r="N30" s="13" cm="1">
+        <f t="array" ref="N30:N36">TRANSPOSE(ABS(B23:H23)/N29)</f>
+        <v>9.3490629360249951E-4</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>97</v>
+      </c>
+      <c r="R30" s="13">
+        <v>8.8834166558848858E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>115</v>
+      </c>
+      <c r="M31" s="13">
+        <v>1.837315589343563E-2</v>
+      </c>
+      <c r="N31" s="13">
+        <v>2.1935431276762739E-2</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>115</v>
+      </c>
+      <c r="R31" s="13">
+        <v>1.837315589343563E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L32" t="s">
+        <v>114</v>
+      </c>
+      <c r="M32" s="13">
+        <v>0.42496023238732389</v>
+      </c>
+      <c r="N32" s="13">
+        <v>0.42315067252394306</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>114</v>
+      </c>
+      <c r="R32" s="13">
+        <v>0.42496023238732389</v>
+      </c>
+    </row>
+    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L33" t="s">
+        <v>113</v>
+      </c>
+      <c r="M33" s="13">
+        <v>0.11221089961793768</v>
+      </c>
+      <c r="N33" s="13">
+        <v>0.11530428580484998</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>113</v>
+      </c>
+      <c r="R33" s="13">
+        <v>0.11221089961793768</v>
+      </c>
+    </row>
+    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L34" t="s">
+        <v>98</v>
+      </c>
+      <c r="M34" s="13">
+        <v>5.6231867720128684E-2</v>
+      </c>
+      <c r="N34" s="13">
+        <v>6.8276293815987821E-2</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>98</v>
+      </c>
+      <c r="R34" s="13">
+        <v>5.6231867720128684E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L35" t="s">
+        <v>99</v>
+      </c>
+      <c r="M35" s="13">
+        <v>1.110458858212284E-2</v>
+      </c>
+      <c r="N35" s="13">
+        <v>1.1138543446115466E-2</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>99</v>
+      </c>
+      <c r="R35" s="13">
+        <v>1.110458858212284E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L36" t="s">
+        <v>100</v>
+      </c>
+      <c r="M36" s="13">
+        <v>0.37623091413346282</v>
+      </c>
+      <c r="N36" s="13">
+        <v>0.35925986683873828</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>100</v>
+      </c>
+      <c r="R36" s="13">
+        <v>0.37623091413346282</v>
+      </c>
+    </row>
+    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="M37">
+        <f>SUM(_xlfn.ANCHORARRAY(M30))</f>
+        <v>1</v>
+      </c>
+      <c r="N37" s="21">
+        <f>SUM(_xlfn.ANCHORARRAY(N30))</f>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="38" spans="12:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L39" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="M39" s="20"/>
+    </row>
+    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L40" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="M40" s="16">
+        <v>8.8834166558848858E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L41" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="M41" s="16">
+        <v>1.837315589343563E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L42" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="M42" s="16">
+        <v>0.42496023238732389</v>
+      </c>
+    </row>
+    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L43" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="M43" s="16">
+        <v>0.11221089961793768</v>
+      </c>
+    </row>
+    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L44" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="M44" s="16">
+        <v>5.6231867720128684E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L45" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="M45" s="16">
+        <v>1.110458858212284E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="12:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L46" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="M46" s="18">
+        <v>0.37623091413346282</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L39:M39"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17028,7 +18313,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -17248,7 +18533,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>32.441200324412002</v>
@@ -17904,7 +19189,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -18124,7 +19409,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>162.20600162206</v>
@@ -18775,7 +20060,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -18995,7 +20280,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>118.95106785617735</v>
@@ -19646,7 +20931,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -19866,7 +21151,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>75.696134090294677</v>
@@ -20517,7 +21802,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -20737,7 +22022,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>27.034333603676668</v>
@@ -21391,7 +22676,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -21611,7 +22896,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>113.54420113544201</v>
@@ -22262,7 +23547,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -22482,7 +23767,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>281.15706947823736</v>
@@ -23128,15 +24413,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5996FC2E-5C44-47E0-B074-63A4EFC5AE9E}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5">
         <v>2020</v>
@@ -23154,7 +24439,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -23173,8 +24458,12 @@
       <c r="F2">
         <v>0.48226429223111689</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <f>MAX(B2:D43)</f>
+        <v>8.0736315194574519</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -23194,7 +24483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
@@ -23214,7 +24503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -23234,7 +24523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -23254,7 +24543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -23274,7 +24563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -23294,7 +24583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -23314,7 +24603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -23334,7 +24623,7 @@
         <v>8.0736315194574519</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -23354,9 +24643,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -23374,7 +24663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -23394,7 +24683,7 @@
         <v>1.0480752098770607</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -23414,7 +24703,7 @@
         <v>0.71928991699394351</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -23434,7 +24723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>

--- a/Violencia Valle del Cauca Indices con Página con todo junto.xlsx
+++ b/Violencia Valle del Cauca Indices con Página con todo junto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Camilo Gómez\Desktop\universidad\Analítica Computacional\Módulo 1\Proyecto 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163BDB71-7574-41DF-9D96-2525BCDED7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5597892-0796-4018-9E4C-F286D4DE4F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Habitantes" sheetId="49" r:id="rId1"/>
